--- a/public/Data/HEMANPUNTERS.xlsx
+++ b/public/Data/HEMANPUNTERS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bturnor\source\repos\PersonalWork\seeMore\public\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bturnor\Repos\seeMore\public\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B1A2B4C-3913-49C3-AF13-D5D0746782B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB900C8-65A0-49F6-8575-5F9E5CDEF57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" firstSheet="6" activeTab="6" xr2:uid="{525E8989-1938-4309-A4CF-8F1D15E362FB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="6" activeTab="8" xr2:uid="{525E8989-1938-4309-A4CF-8F1D15E362FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Punters club" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,8 @@
     <sheet name="Punters 2024" sheetId="9" r:id="rId6"/>
     <sheet name="Punters 2025" sheetId="10" r:id="rId7"/>
     <sheet name="1 Leg Losses 2025" sheetId="11" r:id="rId8"/>
+    <sheet name="Punters 2026" sheetId="12" r:id="rId9"/>
+    <sheet name="1 Leg Losses 2026" sheetId="14" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -65,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="182">
   <si>
     <t>HE_MAN PUNTERS 2019</t>
   </si>
@@ -541,7 +543,7 @@
     <t>Julius Randle 5/19 points</t>
   </si>
   <si>
-    <t>Total over uner 174, total was 162</t>
+    <t>Total over under 174, total was 162</t>
   </si>
   <si>
     <t>Tommy Talau 1/2 tries scored</t>
@@ -606,18 +608,24 @@
   <si>
     <t>Naughton 2/3 goals vs Dorkers</t>
   </si>
+  <si>
+    <t>A.BAXTER</t>
+  </si>
+  <si>
+    <t>Adam</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.0"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.0"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -782,7 +790,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -1196,60 +1204,86 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1264,8 +1298,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1275,30 +1309,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1321,13 +1355,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1342,25 +1379,16 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1376,6 +1404,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1694,29 +1734,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{389AE74A-6876-4CFE-8387-EE4223AB8F41}">
   <dimension ref="A1:M221"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.41796875" customWidth="1"/>
-    <col min="2" max="2" width="6.83984375" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" customWidth="1"/>
+    <col min="2" max="2" width="6.88671875" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="8" max="8" width="4.68359375" customWidth="1"/>
+    <col min="8" max="8" width="4.6640625" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="10.83984375" customWidth="1"/>
-    <col min="12" max="12" width="11.578125" customWidth="1"/>
+    <col min="11" max="11" width="10.88671875" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
       <c r="I2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>2</v>
       </c>
@@ -1745,7 +1785,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>1</v>
       </c>
@@ -1786,7 +1826,7 @@
         <v>52.770000000000039</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -1823,7 +1863,7 @@
         <v>211.72000000000003</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -1864,7 +1904,7 @@
         <v>-142.5</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>2</v>
       </c>
@@ -1901,7 +1941,7 @@
         <v>-122.5</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>3</v>
       </c>
@@ -1942,7 +1982,7 @@
         <v>-161.70999999999998</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>3</v>
       </c>
@@ -1979,7 +2019,7 @@
         <v>-210</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>4</v>
       </c>
@@ -2020,7 +2060,7 @@
         <v>52.990000000000009</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>4</v>
       </c>
@@ -2057,7 +2097,7 @@
         <v>-56.569999999999993</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>5</v>
       </c>
@@ -2083,7 +2123,7 @@
         <v>-198.45000000000005</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>5</v>
       </c>
@@ -2113,7 +2153,7 @@
         <v>1436.27</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>6</v>
       </c>
@@ -2135,7 +2175,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>6</v>
       </c>
@@ -2157,7 +2197,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>7</v>
       </c>
@@ -2179,7 +2219,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>7</v>
       </c>
@@ -2201,7 +2241,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>8</v>
       </c>
@@ -2223,7 +2263,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
         <v>8</v>
       </c>
@@ -2245,7 +2285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <v>9</v>
       </c>
@@ -2267,7 +2307,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <v>9</v>
       </c>
@@ -2289,7 +2329,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <v>10</v>
       </c>
@@ -2311,7 +2351,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <v>10</v>
       </c>
@@ -2333,7 +2373,7 @@
         <v>1.9166666666666667</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
         <v>11</v>
       </c>
@@ -2355,7 +2395,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <v>11</v>
       </c>
@@ -2377,7 +2417,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
         <v>12</v>
       </c>
@@ -2399,7 +2439,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
         <v>12</v>
       </c>
@@ -2421,7 +2461,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
         <v>13</v>
       </c>
@@ -2443,7 +2483,7 @@
         <v>1.5750000000000063E-2</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
         <v>13</v>
       </c>
@@ -2465,7 +2505,7 @@
         <v>13.057333333333334</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30" s="2">
         <v>14</v>
       </c>
@@ -2487,7 +2527,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31" s="2">
         <v>14</v>
       </c>
@@ -2509,7 +2549,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32" s="2">
         <v>15</v>
       </c>
@@ -2531,7 +2571,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B33" s="2">
         <v>15</v>
       </c>
@@ -2553,7 +2593,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B34" s="2">
         <v>16</v>
       </c>
@@ -2575,7 +2615,7 @@
         <v>-8.9999999999999983E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B35" s="2">
         <v>16</v>
       </c>
@@ -2597,7 +2637,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B36" s="2">
         <v>17</v>
       </c>
@@ -2619,7 +2659,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
         <v>17</v>
       </c>
@@ -2641,7 +2681,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>43665</v>
       </c>
@@ -2666,7 +2706,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="9">
         <v>43665</v>
       </c>
@@ -2691,7 +2731,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="9">
         <v>43672</v>
       </c>
@@ -2716,7 +2756,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="9">
         <v>43672</v>
       </c>
@@ -2741,7 +2781,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>43679</v>
       </c>
@@ -2767,7 +2807,7 @@
         <v>8.4176666666666655</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="9">
         <v>43679</v>
       </c>
@@ -2792,7 +2832,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>43686</v>
       </c>
@@ -2818,7 +2858,7 @@
         <v>-0.32234185733512782</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="9">
         <v>43686</v>
       </c>
@@ -2843,7 +2883,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B46" s="2">
         <v>22</v>
       </c>
@@ -2865,7 +2905,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B47" s="2">
         <v>22</v>
       </c>
@@ -2887,7 +2927,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="s">
         <v>17</v>
       </c>
@@ -2912,7 +2952,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
         <v>22</v>
       </c>
@@ -2934,7 +2974,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
         <v>22</v>
       </c>
@@ -2956,7 +2996,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B51" s="2">
         <v>22</v>
       </c>
@@ -2978,7 +3018,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B52" s="2">
         <v>22</v>
       </c>
@@ -3000,7 +3040,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B53" s="2">
         <v>22</v>
       </c>
@@ -3022,7 +3062,7 @@
         <v>-0.51349999999999996</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B54" s="2">
         <v>22</v>
       </c>
@@ -3044,7 +3084,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B55" s="2">
         <v>23</v>
       </c>
@@ -3066,7 +3106,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B56" s="2">
         <v>23</v>
       </c>
@@ -3088,7 +3128,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="9">
         <v>43707</v>
       </c>
@@ -3111,7 +3151,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <v>43707</v>
       </c>
@@ -3134,7 +3174,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="9">
         <v>43714</v>
       </c>
@@ -3157,7 +3197,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>43714</v>
       </c>
@@ -3180,7 +3220,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="9">
         <v>43714</v>
       </c>
@@ -3197,7 +3237,7 @@
       <c r="F61" s="1"/>
       <c r="G61" s="3"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>43714</v>
       </c>
@@ -3220,7 +3260,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="9">
         <v>43714</v>
       </c>
@@ -3243,7 +3283,7 @@
         <v>-0.11400000000000006</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="9">
         <v>43714</v>
       </c>
@@ -3266,7 +3306,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="9">
         <v>43714</v>
       </c>
@@ -3289,7 +3329,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>43714</v>
       </c>
@@ -3312,776 +3352,1153 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B67" s="2"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B68" s="2"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B69" s="2"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B70" s="2"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B71" s="2"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B72" s="2"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B73" s="2"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B74" s="2"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B75" s="2"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B76" s="2"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B77" s="2"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B78" s="2"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B79" s="2"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B80" s="2"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B81" s="2"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B82" s="2"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B83" s="2"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B84" s="2"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B85" s="2"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B86" s="2"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B87" s="2"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B88" s="2"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B89" s="2"/>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B90" s="2"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B91" s="2"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B92" s="2"/>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B93" s="2"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B94" s="2"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B95" s="2"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B96" s="2"/>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B97" s="2"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B98" s="2"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B99" s="2"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B100" s="2"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B101" s="2"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B102" s="2"/>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B103" s="2"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B104" s="2"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B105" s="2"/>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B106" s="2"/>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B107" s="2"/>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
     </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B108" s="2"/>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
     </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B109" s="2"/>
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
     </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B110" s="2"/>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
     </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B111" s="2"/>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
     </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B112" s="2"/>
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
     </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B113" s="2"/>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
     </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B114" s="2"/>
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
     </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B115" s="2"/>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
     </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B116" s="2"/>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
     </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B117" s="2"/>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
     </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B118" s="2"/>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
     </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B119" s="2"/>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
     </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B120" s="2"/>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
     </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B121" s="2"/>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
     </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B122" s="2"/>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
     </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B123" s="2"/>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
     </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B124" s="2"/>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
     </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B125" s="2"/>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
     </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B126" s="2"/>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
     </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B127" s="2"/>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
     </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B128" s="2"/>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
     </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B129" s="2"/>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
     </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B130" s="2"/>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
     </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B131" s="2"/>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
     </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B132" s="2"/>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
     </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B133" s="2"/>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
     </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B134" s="2"/>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
     </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B135" s="2"/>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
     </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B136" s="2"/>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
     </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B137" s="2"/>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
     </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B138" s="2"/>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
     </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B139" s="2"/>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
     </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B140" s="2"/>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
     </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B141" s="2"/>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
     </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B142" s="2"/>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
     </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B143" s="2"/>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
     </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B144" s="2"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
     </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B145" s="2"/>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
     </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B146" s="2"/>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
     </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B147" s="2"/>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
     </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B148" s="2"/>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
     </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B149" s="2"/>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
     </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B150" s="2"/>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
     </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B151" s="2"/>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
     </row>
-    <row r="152" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B152" s="2"/>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
     </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B153" s="2"/>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
     </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B154" s="2"/>
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
     </row>
-    <row r="155" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B155" s="2"/>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
     </row>
-    <row r="156" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B156" s="2"/>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
     </row>
-    <row r="157" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B157" s="2"/>
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
     </row>
-    <row r="158" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B158" s="2"/>
       <c r="D158" s="1"/>
       <c r="E158" s="1"/>
     </row>
-    <row r="159" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B159" s="2"/>
       <c r="D159" s="1"/>
       <c r="E159" s="1"/>
     </row>
-    <row r="160" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B160" s="2"/>
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
     </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B161" s="2"/>
       <c r="D161" s="1"/>
       <c r="E161" s="1"/>
     </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B162" s="2"/>
       <c r="D162" s="1"/>
       <c r="E162" s="1"/>
     </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B163" s="2"/>
       <c r="D163" s="1"/>
       <c r="E163" s="1"/>
     </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B164" s="2"/>
       <c r="D164" s="1"/>
       <c r="E164" s="1"/>
     </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B165" s="2"/>
       <c r="D165" s="1"/>
       <c r="E165" s="1"/>
     </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B166" s="2"/>
       <c r="D166" s="1"/>
       <c r="E166" s="1"/>
     </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B167" s="2"/>
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
     </row>
-    <row r="168" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B168" s="2"/>
       <c r="D168" s="1"/>
       <c r="E168" s="1"/>
     </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B169" s="2"/>
       <c r="D169" s="1"/>
       <c r="E169" s="1"/>
     </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B170" s="2"/>
       <c r="D170" s="1"/>
       <c r="E170" s="1"/>
     </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B171" s="2"/>
       <c r="D171" s="1"/>
       <c r="E171" s="1"/>
     </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B172" s="2"/>
       <c r="D172" s="1"/>
       <c r="E172" s="1"/>
     </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B173" s="2"/>
       <c r="D173" s="1"/>
       <c r="E173" s="1"/>
     </row>
-    <row r="174" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B174" s="2"/>
       <c r="D174" s="1"/>
       <c r="E174" s="1"/>
     </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B175" s="2"/>
       <c r="D175" s="1"/>
       <c r="E175" s="1"/>
     </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B176" s="2"/>
       <c r="D176" s="1"/>
       <c r="E176" s="1"/>
     </row>
-    <row r="177" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B177" s="2"/>
       <c r="D177" s="1"/>
       <c r="E177" s="1"/>
     </row>
-    <row r="178" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B178" s="2"/>
       <c r="D178" s="1"/>
       <c r="E178" s="1"/>
     </row>
-    <row r="179" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B179" s="2"/>
       <c r="D179" s="1"/>
       <c r="E179" s="1"/>
     </row>
-    <row r="180" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B180" s="2"/>
       <c r="D180" s="1"/>
       <c r="E180" s="1"/>
     </row>
-    <row r="181" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B181" s="2"/>
       <c r="D181" s="1"/>
       <c r="E181" s="1"/>
     </row>
-    <row r="182" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B182" s="2"/>
       <c r="D182" s="1"/>
       <c r="E182" s="1"/>
     </row>
-    <row r="183" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B183" s="2"/>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
     </row>
-    <row r="184" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B184" s="2"/>
       <c r="D184" s="1"/>
       <c r="E184" s="1"/>
     </row>
-    <row r="185" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B185" s="2"/>
       <c r="D185" s="1"/>
       <c r="E185" s="1"/>
     </row>
-    <row r="186" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B186" s="2"/>
       <c r="D186" s="1"/>
       <c r="E186" s="1"/>
     </row>
-    <row r="187" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B187" s="2"/>
       <c r="D187" s="1"/>
       <c r="E187" s="1"/>
     </row>
-    <row r="188" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B188" s="2"/>
       <c r="D188" s="1"/>
       <c r="E188" s="1"/>
     </row>
-    <row r="189" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="189" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B189" s="2"/>
       <c r="D189" s="1"/>
       <c r="E189" s="1"/>
     </row>
-    <row r="190" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B190" s="2"/>
       <c r="D190" s="1"/>
       <c r="E190" s="1"/>
     </row>
-    <row r="191" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B191" s="2"/>
       <c r="D191" s="1"/>
       <c r="E191" s="1"/>
     </row>
-    <row r="192" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="192" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B192" s="2"/>
       <c r="D192" s="1"/>
       <c r="E192" s="1"/>
     </row>
-    <row r="193" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B193" s="2"/>
       <c r="D193" s="1"/>
       <c r="E193" s="1"/>
     </row>
-    <row r="194" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B194" s="2"/>
       <c r="D194" s="1"/>
       <c r="E194" s="1"/>
     </row>
-    <row r="195" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B195" s="2"/>
       <c r="D195" s="1"/>
       <c r="E195" s="1"/>
     </row>
-    <row r="196" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B196" s="2"/>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
     </row>
-    <row r="197" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B197" s="2"/>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
     </row>
-    <row r="198" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B198" s="2"/>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
     </row>
-    <row r="199" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="199" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B199" s="2"/>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
     </row>
-    <row r="200" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B200" s="2"/>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
     </row>
-    <row r="201" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B201" s="2"/>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
     </row>
-    <row r="202" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B202" s="2"/>
       <c r="D202" s="1"/>
       <c r="E202" s="1"/>
     </row>
-    <row r="203" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B203" s="2"/>
       <c r="D203" s="1"/>
       <c r="E203" s="1"/>
     </row>
-    <row r="204" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B204" s="2"/>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
     </row>
-    <row r="205" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B205" s="2"/>
       <c r="D205" s="1"/>
       <c r="E205" s="1"/>
     </row>
-    <row r="206" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="206" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B206" s="2"/>
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
     </row>
-    <row r="207" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="207" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B207" s="2"/>
       <c r="D207" s="1"/>
       <c r="E207" s="1"/>
     </row>
-    <row r="208" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="208" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B208" s="2"/>
       <c r="D208" s="1"/>
       <c r="E208" s="1"/>
     </row>
-    <row r="209" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="209" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B209" s="2"/>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
     </row>
-    <row r="210" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="210" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B210" s="2"/>
       <c r="D210" s="1"/>
       <c r="E210" s="1"/>
     </row>
-    <row r="211" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="211" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B211" s="2"/>
       <c r="D211" s="1"/>
       <c r="E211" s="1"/>
     </row>
-    <row r="212" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="212" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B212" s="2"/>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
     </row>
-    <row r="213" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="213" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B213" s="2"/>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
     </row>
-    <row r="214" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="214" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
     </row>
-    <row r="215" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="215" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
     </row>
-    <row r="216" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="216" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
     </row>
-    <row r="217" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="217" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
     </row>
-    <row r="218" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="218" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
     </row>
-    <row r="219" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="219" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
     </row>
-    <row r="220" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="220" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
     </row>
-    <row r="221" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="221" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E2851B2-92FF-4955-99CF-2C8DD50BAC4F}">
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" customWidth="1"/>
+    <col min="4" max="4" width="39.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" t="str">
+        <f t="shared" ref="F1:F13" si="0">IF(COUNTIF(A:A, E1)=0, "", SUMIF(A:A, E1, C:C))</f>
+        <v/>
+      </c>
+      <c r="G1">
+        <f>COUNTIF(A1:A81, E1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2" s="59"/>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>COUNTIF(A1:A81, E2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C3" s="59"/>
+      <c r="E3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>COUNTIF(A1:A81, E3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="60"/>
+      <c r="C4" s="59"/>
+      <c r="E4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G4">
+        <f t="shared" ref="G4" si="1">COUNTIF(A4:A84, E4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="E5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G5">
+        <f t="shared" ref="G5" si="2">COUNTIF(A4:A84, E5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="E6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6">
+        <f t="shared" ref="G6" si="3">COUNTIF(A4:A84, E6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="60"/>
+      <c r="C7" s="60"/>
+      <c r="E7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7">
+        <f t="shared" ref="G7" si="4">COUNTIF(A7:A87, E7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="60"/>
+      <c r="C8" s="60"/>
+      <c r="E8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8">
+        <f t="shared" ref="G8" si="5">COUNTIF(A7:A87, E8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="60"/>
+      <c r="C9" s="60"/>
+      <c r="E9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9">
+        <f t="shared" ref="G9" si="6">COUNTIF(A7:A87, E9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="60"/>
+      <c r="C10" s="60"/>
+      <c r="E10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10">
+        <f t="shared" ref="G10" si="7">COUNTIF(A10:A90, E10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="60"/>
+      <c r="C11" s="60"/>
+      <c r="E11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>COUNTIF(A10:A90, E11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="60"/>
+      <c r="C12" s="59"/>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12">
+        <f t="shared" ref="G12" si="8">COUNTIF(A10:A90, E12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="60"/>
+      <c r="C13" s="59"/>
+      <c r="E13" t="s">
+        <v>181</v>
+      </c>
+      <c r="F13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>COUNTIF(A2:A100, E13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="59"/>
+      <c r="C14" s="59"/>
+      <c r="F14" s="61">
+        <f>SUM(F1:F13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="60"/>
+      <c r="C17" s="59"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="60"/>
+      <c r="C18" s="59"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B21" s="60"/>
+      <c r="C21" s="60"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B22" s="60"/>
+      <c r="C22" s="59"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B23" s="60"/>
+      <c r="C23" s="59"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C24" s="59"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B25" s="60"/>
+      <c r="C25" s="59"/>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B26" s="60"/>
+      <c r="C26" s="60"/>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C27" s="59"/>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B28" s="60"/>
+      <c r="C28" s="60"/>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C29" s="59"/>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B30" s="60"/>
+      <c r="C30" s="59"/>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B31" s="60"/>
+      <c r="C31" s="60"/>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B32" s="60"/>
+      <c r="C32" s="60"/>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B33" s="60"/>
+      <c r="C33" s="59"/>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B34" s="60"/>
+      <c r="C34" s="59"/>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B35" s="60"/>
+      <c r="C35" s="59"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B36" s="60"/>
+      <c r="C36" s="59"/>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C37" s="59"/>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B38" s="60"/>
+      <c r="C38" s="60"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C39" s="60"/>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B40" s="59"/>
+      <c r="C40" s="59"/>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B41" s="60"/>
+      <c r="C41" s="59"/>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B42" s="60"/>
+      <c r="C42" s="59"/>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B43" s="60"/>
+      <c r="C43" s="60"/>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B44" s="60"/>
+      <c r="C44" s="59"/>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B45" s="59"/>
+      <c r="C45" s="60"/>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C46" s="59"/>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C47" s="59"/>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B48" s="60"/>
+      <c r="C48" s="59"/>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B49" s="59"/>
+      <c r="C49" s="59"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B50" s="60"/>
+      <c r="C50" s="60"/>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B51" s="60"/>
+      <c r="C51" s="59"/>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B52" s="60"/>
+      <c r="C52" s="59"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B53" s="60"/>
+      <c r="C53" s="59"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
@@ -4091,63 +4508,63 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:AA39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.68359375" customWidth="1"/>
-    <col min="2" max="2" width="5.68359375" customWidth="1"/>
-    <col min="3" max="22" width="7.83984375" customWidth="1"/>
-    <col min="23" max="23" width="9.41796875" customWidth="1"/>
-    <col min="24" max="24" width="9.68359375" customWidth="1"/>
+    <col min="1" max="1" width="1.6640625" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" customWidth="1"/>
+    <col min="3" max="22" width="7.88671875" customWidth="1"/>
+    <col min="23" max="23" width="9.44140625" customWidth="1"/>
+    <col min="24" max="24" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="2" spans="2:27" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="C2" s="68" t="s">
+    <row r="1" spans="2:27" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:27" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C2" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68" t="s">
+      <c r="D2" s="62"/>
+      <c r="E2" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68" t="s">
+      <c r="F2" s="62"/>
+      <c r="G2" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68" t="s">
+      <c r="H2" s="62"/>
+      <c r="I2" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68" t="s">
+      <c r="J2" s="62"/>
+      <c r="K2" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68" t="s">
+      <c r="L2" s="62"/>
+      <c r="M2" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68" t="s">
+      <c r="N2" s="62"/>
+      <c r="O2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="R2" s="68"/>
-      <c r="S2" s="68" t="s">
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="T2" s="68"/>
-      <c r="U2" s="68" t="s">
+      <c r="T2" s="62"/>
+      <c r="U2" s="62" t="s">
         <v>27</v>
       </c>
       <c r="V2" s="69"/>
-      <c r="W2" s="67" t="s">
+      <c r="W2" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="X2" s="68"/>
-    </row>
-    <row r="3" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="X2" s="62"/>
+    </row>
+    <row r="3" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="32" t="s">
         <v>29</v>
       </c>
@@ -4218,7 +4635,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="30" t="s">
         <v>32</v>
       </c>
@@ -4288,7 +4705,7 @@
         <v>25.25</v>
       </c>
     </row>
-    <row r="5" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="31" t="s">
         <v>33</v>
       </c>
@@ -4351,7 +4768,7 @@
         <v>-49.069999999999993</v>
       </c>
     </row>
-    <row r="6" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="30" t="s">
         <v>34</v>
       </c>
@@ -4408,7 +4825,7 @@
         <v>-154.07</v>
       </c>
     </row>
-    <row r="7" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="30" t="s">
         <v>35</v>
       </c>
@@ -4465,7 +4882,7 @@
         <v>-259.07</v>
       </c>
     </row>
-    <row r="8" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="30" t="s">
         <v>36</v>
       </c>
@@ -4522,7 +4939,7 @@
         <v>-49</v>
       </c>
     </row>
-    <row r="9" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="30" t="s">
         <v>37</v>
       </c>
@@ -4579,7 +4996,7 @@
         <v>139.75</v>
       </c>
     </row>
-    <row r="10" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="30" t="s">
         <v>38</v>
       </c>
@@ -4636,7 +5053,7 @@
         <v>31.75</v>
       </c>
     </row>
-    <row r="11" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="30" t="s">
         <v>39</v>
       </c>
@@ -4693,7 +5110,7 @@
         <v>147.88</v>
       </c>
     </row>
-    <row r="12" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="30" t="s">
         <v>40</v>
       </c>
@@ -4750,7 +5167,7 @@
         <v>7.8799999999999955</v>
       </c>
     </row>
-    <row r="13" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="13" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="30" t="s">
         <v>41</v>
       </c>
@@ -4807,7 +5224,7 @@
         <v>-97.12</v>
       </c>
     </row>
-    <row r="14" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="30" t="s">
         <v>42</v>
       </c>
@@ -4864,7 +5281,7 @@
         <v>-127.12000000000012</v>
       </c>
     </row>
-    <row r="15" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="15" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="30" t="s">
         <v>43</v>
       </c>
@@ -4921,7 +5338,7 @@
         <v>-227.12000000000012</v>
       </c>
     </row>
-    <row r="16" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="30" t="s">
         <v>44</v>
       </c>
@@ -4978,7 +5395,7 @@
         <v>-228.62000000000012</v>
       </c>
     </row>
-    <row r="17" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="30" t="s">
         <v>45</v>
       </c>
@@ -5035,7 +5452,7 @@
         <v>-328.62000000000012</v>
       </c>
     </row>
-    <row r="18" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="18" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="30" t="s">
         <v>46</v>
       </c>
@@ -5092,7 +5509,7 @@
         <v>-408.62000000000012</v>
       </c>
     </row>
-    <row r="19" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="30" t="s">
         <v>47</v>
       </c>
@@ -5149,7 +5566,7 @@
         <v>-493.02000000000021</v>
       </c>
     </row>
-    <row r="20" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="30" t="s">
         <v>48</v>
       </c>
@@ -5206,7 +5623,7 @@
         <v>-598.02000000000021</v>
       </c>
     </row>
-    <row r="21" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="30" t="s">
         <v>49</v>
       </c>
@@ -5264,7 +5681,7 @@
         <v>-541.98000000000025</v>
       </c>
     </row>
-    <row r="22" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="22" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="30" t="s">
         <v>50</v>
       </c>
@@ -5322,7 +5739,7 @@
         <v>-370.12000000000012</v>
       </c>
     </row>
-    <row r="23" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="23" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="30" t="s">
         <v>51</v>
       </c>
@@ -5379,7 +5796,7 @@
         <v>-384.62999999999988</v>
       </c>
     </row>
-    <row r="24" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="24" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="30" t="s">
         <v>52</v>
       </c>
@@ -5436,7 +5853,7 @@
         <v>-434.62999999999988</v>
       </c>
     </row>
-    <row r="25" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="25" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="30" t="s">
         <v>53</v>
       </c>
@@ -5493,7 +5910,7 @@
         <v>-539.72999999999979</v>
       </c>
     </row>
-    <row r="26" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="26" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="30" t="s">
         <v>54</v>
       </c>
@@ -5574,7 +5991,7 @@
         <v>-694.72999999999979</v>
       </c>
     </row>
-    <row r="27" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="27" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="11" t="s">
         <v>55</v>
       </c>
@@ -5667,7 +6084,7 @@
         <v>1774.6899999999998</v>
       </c>
     </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:27" x14ac:dyDescent="0.3">
       <c r="D28" s="22">
         <f>(D27-C27)/C27</f>
         <v>5.0343422145067457E-2</v>
@@ -5705,37 +6122,37 @@
         <v>-9.4449047224523811E-2</v>
       </c>
     </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="F29" s="64" t="s">
+    <row r="29" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="F29" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="65"/>
-      <c r="H29" s="66"/>
-      <c r="I29" s="62">
+      <c r="G29" s="66"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="63">
         <f>C27+E27+G27+I27+K27+M27+O27+Q27+S27+U27</f>
         <v>2469.42</v>
       </c>
-      <c r="J29" s="63"/>
-    </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="J29" s="64"/>
+    </row>
+    <row r="30" spans="2:27" x14ac:dyDescent="0.3">
       <c r="G30" s="70" t="s">
         <v>57</v>
       </c>
       <c r="H30" s="70"/>
-      <c r="I30" s="62">
+      <c r="I30" s="63">
         <f>+D27+F27+H27+J27+L27+N27+P27+R27+T27+V27</f>
         <v>1774.69</v>
       </c>
-      <c r="J30" s="63"/>
-    </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="I31" s="62">
+      <c r="J30" s="64"/>
+    </row>
+    <row r="31" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="I31" s="63">
         <f>I30-I29</f>
         <v>-694.73</v>
       </c>
-      <c r="J31" s="63"/>
-    </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="J31" s="64"/>
+    </row>
+    <row r="32" spans="2:27" x14ac:dyDescent="0.3">
       <c r="C32" s="1">
         <f>C27+E27+G27</f>
         <v>846.96</v>
@@ -5773,7 +6190,7 @@
         <v>-467.10000000000008</v>
       </c>
     </row>
-    <row r="33" spans="3:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="3:16" x14ac:dyDescent="0.3">
       <c r="G33" t="s">
         <v>58</v>
       </c>
@@ -5781,14 +6198,14 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="34" spans="3:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="I34" s="63">
+    <row r="34" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="I34" s="64">
         <f>I33+I31</f>
         <v>505.27</v>
       </c>
-      <c r="J34" s="63"/>
-    </row>
-    <row r="38" spans="3:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="J34" s="64"/>
+    </row>
+    <row r="38" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C38" s="1">
         <f>C27+E27+G27</f>
         <v>846.96</v>
@@ -5814,7 +6231,7 @@
         <v>400.96</v>
       </c>
     </row>
-    <row r="39" spans="3:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="3:16" x14ac:dyDescent="0.3">
       <c r="D39" s="1">
         <f>D38-C38</f>
         <v>-33.019999999999982</v>
@@ -5830,11 +6247,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
     <mergeCell ref="I30:J30"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="I31:J31"/>
@@ -5847,6 +6259,11 @@
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="I29:J29"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5860,66 +6277,66 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:AA39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.68359375" customWidth="1"/>
-    <col min="2" max="2" width="5.68359375" customWidth="1"/>
-    <col min="3" max="3" width="7.83984375" customWidth="1"/>
-    <col min="4" max="4" width="9.15625" customWidth="1"/>
-    <col min="5" max="20" width="7.83984375" customWidth="1"/>
-    <col min="21" max="22" width="7.83984375" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="9.41796875" customWidth="1"/>
-    <col min="24" max="24" width="9.68359375" customWidth="1"/>
+    <col min="1" max="1" width="1.6640625" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" customWidth="1"/>
+    <col min="5" max="20" width="7.88671875" customWidth="1"/>
+    <col min="21" max="22" width="7.88671875" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="9.44140625" customWidth="1"/>
+    <col min="24" max="24" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="2" spans="2:27" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="C2" s="68" t="s">
+    <row r="1" spans="2:27" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:27" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C2" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68" t="s">
+      <c r="D2" s="62"/>
+      <c r="E2" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="68"/>
-      <c r="G2" s="71" t="s">
+      <c r="F2" s="62"/>
+      <c r="G2" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="67"/>
-      <c r="I2" s="68" t="s">
+      <c r="H2" s="68"/>
+      <c r="I2" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68" t="s">
+      <c r="J2" s="62"/>
+      <c r="K2" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68" t="s">
+      <c r="L2" s="62"/>
+      <c r="M2" s="62" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="68" t="s">
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="68"/>
-      <c r="S2" s="68" t="s">
+      <c r="R2" s="62"/>
+      <c r="S2" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="T2" s="68"/>
-      <c r="U2" s="68" t="s">
+      <c r="T2" s="62"/>
+      <c r="U2" s="62" t="s">
         <v>27</v>
       </c>
       <c r="V2" s="69"/>
-      <c r="W2" s="67" t="s">
+      <c r="W2" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="X2" s="68"/>
-    </row>
-    <row r="3" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="X2" s="62"/>
+    </row>
+    <row r="3" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="32" t="s">
         <v>29</v>
       </c>
@@ -5990,7 +6407,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="30" t="s">
         <v>32</v>
       </c>
@@ -6062,7 +6479,7 @@
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
     </row>
-    <row r="5" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="30" t="s">
         <v>34</v>
       </c>
@@ -6134,7 +6551,7 @@
       <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
     </row>
-    <row r="6" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="30" t="s">
         <v>35</v>
       </c>
@@ -6182,7 +6599,7 @@
       <c r="Z6" s="1"/>
       <c r="AA6" s="1"/>
     </row>
-    <row r="7" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="30" t="s">
         <v>36</v>
       </c>
@@ -6230,7 +6647,7 @@
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
     </row>
-    <row r="8" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="30" t="s">
         <v>37</v>
       </c>
@@ -6278,7 +6695,7 @@
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
     </row>
-    <row r="9" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="30" t="s">
         <v>38</v>
       </c>
@@ -6326,7 +6743,7 @@
       <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
     </row>
-    <row r="10" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="30" t="s">
         <v>39</v>
       </c>
@@ -6374,7 +6791,7 @@
       <c r="Z10" s="1"/>
       <c r="AA10" s="1"/>
     </row>
-    <row r="11" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="30" t="s">
         <v>40</v>
       </c>
@@ -6422,7 +6839,7 @@
       <c r="Z11" s="1"/>
       <c r="AA11" s="1"/>
     </row>
-    <row r="12" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="30" t="s">
         <v>41</v>
       </c>
@@ -6470,7 +6887,7 @@
       <c r="Z12" s="1"/>
       <c r="AA12" s="1"/>
     </row>
-    <row r="13" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="13" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="30" t="s">
         <v>42</v>
       </c>
@@ -6518,7 +6935,7 @@
       <c r="Z13" s="1"/>
       <c r="AA13" s="1"/>
     </row>
-    <row r="14" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="30" t="s">
         <v>43</v>
       </c>
@@ -6566,7 +6983,7 @@
       <c r="Z14" s="1"/>
       <c r="AA14" s="1"/>
     </row>
-    <row r="15" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="15" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="30" t="s">
         <v>44</v>
       </c>
@@ -6615,7 +7032,7 @@
       <c r="Z15" s="1"/>
       <c r="AA15" s="1"/>
     </row>
-    <row r="16" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="30" t="s">
         <v>45</v>
       </c>
@@ -6663,7 +7080,7 @@
       <c r="Z16" s="1"/>
       <c r="AA16" s="1"/>
     </row>
-    <row r="17" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="30" t="s">
         <v>46</v>
       </c>
@@ -6711,7 +7128,7 @@
       <c r="Z17" s="1"/>
       <c r="AA17" s="1"/>
     </row>
-    <row r="18" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="18" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="30" t="s">
         <v>47</v>
       </c>
@@ -6759,7 +7176,7 @@
       <c r="Z18" s="1"/>
       <c r="AA18" s="1"/>
     </row>
-    <row r="19" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="30" t="s">
         <v>48</v>
       </c>
@@ -6807,7 +7224,7 @@
       <c r="Z19" s="1"/>
       <c r="AA19" s="1"/>
     </row>
-    <row r="20" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="30" t="s">
         <v>49</v>
       </c>
@@ -6855,7 +7272,7 @@
       <c r="Z20" s="1"/>
       <c r="AA20" s="1"/>
     </row>
-    <row r="21" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="30" t="s">
         <v>50</v>
       </c>
@@ -6903,7 +7320,7 @@
       <c r="Z21" s="1"/>
       <c r="AA21" s="1"/>
     </row>
-    <row r="22" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="22" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="30" t="s">
         <v>59</v>
       </c>
@@ -6951,7 +7368,7 @@
       <c r="Z22" s="1"/>
       <c r="AA22" s="1"/>
     </row>
-    <row r="23" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="23" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="30" t="s">
         <v>60</v>
       </c>
@@ -6999,7 +7416,7 @@
       <c r="Z23" s="1"/>
       <c r="AA23" s="1"/>
     </row>
-    <row r="24" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="24" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="30" t="s">
         <v>61</v>
       </c>
@@ -7047,7 +7464,7 @@
       <c r="Z24" s="1"/>
       <c r="AA24" s="1"/>
     </row>
-    <row r="25" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="25" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="30" t="s">
         <v>62</v>
       </c>
@@ -7096,7 +7513,7 @@
       <c r="Z25" s="1"/>
       <c r="AA25" s="1"/>
     </row>
-    <row r="26" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="26" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="30" t="s">
         <v>63</v>
       </c>
@@ -7145,7 +7562,7 @@
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
     </row>
-    <row r="27" spans="2:27" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="27" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="11" t="s">
         <v>55</v>
       </c>
@@ -7238,7 +7655,7 @@
         <v>2492.1999999999998</v>
       </c>
     </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:27" x14ac:dyDescent="0.3">
       <c r="D28" s="34">
         <f>(D27-C27)/C27</f>
         <v>4.666666666666667</v>
@@ -7276,37 +7693,37 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="F29" s="64" t="s">
+    <row r="29" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="F29" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="65"/>
-      <c r="H29" s="66"/>
-      <c r="I29" s="62">
+      <c r="G29" s="66"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="63">
         <f>C27+E27+G27+I27+K27+M27+O27+Q27+S27+U27</f>
         <v>1788.24</v>
       </c>
-      <c r="J29" s="63"/>
-    </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="J29" s="64"/>
+    </row>
+    <row r="30" spans="2:27" x14ac:dyDescent="0.3">
       <c r="G30" s="70" t="s">
         <v>57</v>
       </c>
       <c r="H30" s="70"/>
-      <c r="I30" s="62">
+      <c r="I30" s="63">
         <f>+D27+F27+H27+J27+L27+N27+P27+R27+T27+V27</f>
         <v>2492.1999999999998</v>
       </c>
-      <c r="J30" s="63"/>
-    </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.55000000000000004">
-      <c r="I31" s="62">
+      <c r="J30" s="64"/>
+    </row>
+    <row r="31" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="I31" s="63">
         <f>I30-I29</f>
         <v>703.95999999999981</v>
       </c>
-      <c r="J31" s="63"/>
-    </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+      <c r="J31" s="64"/>
+    </row>
+    <row r="32" spans="2:27" x14ac:dyDescent="0.3">
       <c r="C32" s="36">
         <f>C27+E27+G27</f>
         <v>591.5</v>
@@ -7344,7 +7761,7 @@
         <v>-415.6</v>
       </c>
     </row>
-    <row r="33" spans="3:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="3:16" x14ac:dyDescent="0.3">
       <c r="G33" t="s">
         <v>58</v>
       </c>
@@ -7353,19 +7770,19 @@
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="3:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="3:16" x14ac:dyDescent="0.3">
       <c r="G34" s="42" t="s">
         <v>64</v>
       </c>
       <c r="H34" s="42"/>
-      <c r="I34" s="72">
+      <c r="I34" s="71">
         <f>I33+I31</f>
         <v>1303.9599999999998</v>
       </c>
-      <c r="J34" s="72"/>
+      <c r="J34" s="71"/>
       <c r="M34" s="33"/>
     </row>
-    <row r="38" spans="3:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C38" s="1">
         <f>C27+E27+G27</f>
         <v>591.5</v>
@@ -7391,7 +7808,7 @@
         <v>185.64</v>
       </c>
     </row>
-    <row r="39" spans="3:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="3:16" x14ac:dyDescent="0.3">
       <c r="D39" s="1">
         <f>D38-C38</f>
         <v>1133.48</v>
@@ -7407,11 +7824,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="U2:V2"/>
@@ -7419,15 +7836,15 @@
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="M2:N2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="O2:P2"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="84" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7437,71 +7854,71 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:AH41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.68359375" customWidth="1"/>
-    <col min="2" max="2" width="5.68359375" customWidth="1"/>
-    <col min="3" max="3" width="7.83984375" customWidth="1"/>
-    <col min="4" max="4" width="9.15625" customWidth="1"/>
-    <col min="5" max="23" width="7.83984375" customWidth="1"/>
-    <col min="24" max="24" width="8.83984375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.41796875" customWidth="1"/>
-    <col min="26" max="26" width="9.68359375" customWidth="1"/>
+    <col min="1" max="1" width="1.6640625" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" customWidth="1"/>
+    <col min="5" max="23" width="7.88671875" customWidth="1"/>
+    <col min="24" max="24" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.44140625" customWidth="1"/>
+    <col min="26" max="26" width="9.6640625" customWidth="1"/>
     <col min="34" max="34" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:34" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="2" spans="2:34" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="C2" s="68" t="s">
+    <row r="1" spans="2:34" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:34" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C2" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68" t="s">
+      <c r="D2" s="62"/>
+      <c r="E2" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68" t="s">
+      <c r="F2" s="62"/>
+      <c r="G2" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68" t="s">
+      <c r="H2" s="62"/>
+      <c r="I2" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68" t="s">
+      <c r="J2" s="62"/>
+      <c r="K2" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68" t="s">
+      <c r="L2" s="62"/>
+      <c r="M2" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68" t="s">
+      <c r="N2" s="62"/>
+      <c r="O2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="R2" s="68"/>
-      <c r="S2" s="68" t="s">
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="68"/>
-      <c r="U2" s="68" t="s">
+      <c r="T2" s="62"/>
+      <c r="U2" s="62" t="s">
         <v>65</v>
       </c>
       <c r="V2" s="69"/>
-      <c r="W2" s="68" t="s">
+      <c r="W2" s="62" t="s">
         <v>66</v>
       </c>
       <c r="X2" s="69"/>
-      <c r="Y2" s="67" t="s">
+      <c r="Y2" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="Z2" s="68"/>
-    </row>
-    <row r="3" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Z2" s="62"/>
+    </row>
+    <row r="3" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="32" t="s">
         <v>29</v>
       </c>
@@ -7578,7 +7995,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="30" t="s">
         <v>32</v>
       </c>
@@ -7662,7 +8079,7 @@
       </c>
       <c r="AD4" s="1"/>
     </row>
-    <row r="5" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="30" t="s">
         <v>34</v>
       </c>
@@ -7722,7 +8139,7 @@
       </c>
       <c r="AD5" s="1"/>
     </row>
-    <row r="6" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="30" t="s">
         <v>35</v>
       </c>
@@ -7794,7 +8211,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="30" t="s">
         <v>36</v>
       </c>
@@ -7872,7 +8289,7 @@
         <v>-0.32233502538071068</v>
       </c>
     </row>
-    <row r="8" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="30" t="s">
         <v>37</v>
       </c>
@@ -7950,7 +8367,7 @@
         <v>0.10484290357529792</v>
       </c>
     </row>
-    <row r="9" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="30" t="s">
         <v>38</v>
       </c>
@@ -8028,7 +8445,7 @@
         <v>7.2416562555773778E-2</v>
       </c>
     </row>
-    <row r="10" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="30" t="s">
         <v>39</v>
       </c>
@@ -8110,7 +8527,7 @@
         <v>0.6222913657073007</v>
       </c>
     </row>
-    <row r="11" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="30" t="s">
         <v>40</v>
       </c>
@@ -8188,7 +8605,7 @@
         <v>-0.90797788309636651</v>
       </c>
     </row>
-    <row r="12" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="30" t="s">
         <v>41</v>
       </c>
@@ -8268,7 +8685,7 @@
         <v>-0.40905378235737633</v>
       </c>
     </row>
-    <row r="13" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="13" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="30" t="s">
         <v>42</v>
       </c>
@@ -8346,7 +8763,7 @@
         <v>-0.75236571584178635</v>
       </c>
     </row>
-    <row r="14" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="30" t="s">
         <v>43</v>
       </c>
@@ -8420,7 +8837,7 @@
         <v>-0.27806342015855035</v>
       </c>
     </row>
-    <row r="15" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="15" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="30" t="s">
         <v>44</v>
       </c>
@@ -8502,7 +8919,7 @@
         <v>0.63670886075949351</v>
       </c>
     </row>
-    <row r="16" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="30" t="s">
         <v>45</v>
       </c>
@@ -8596,7 +9013,7 @@
         <v>-0.56874999999999998</v>
       </c>
     </row>
-    <row r="17" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="30" t="s">
         <v>46</v>
       </c>
@@ -8656,7 +9073,7 @@
       </c>
       <c r="AD17" s="1"/>
     </row>
-    <row r="18" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="18" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="30" t="s">
         <v>47</v>
       </c>
@@ -8723,7 +9140,7 @@
       </c>
       <c r="AD18" s="1"/>
     </row>
-    <row r="19" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="30" t="s">
         <v>48</v>
       </c>
@@ -8791,7 +9208,7 @@
       </c>
       <c r="AD19" s="1"/>
     </row>
-    <row r="20" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="30" t="s">
         <v>49</v>
       </c>
@@ -8858,7 +9275,7 @@
       </c>
       <c r="AD20" s="1"/>
     </row>
-    <row r="21" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="30" t="s">
         <v>50</v>
       </c>
@@ -8925,7 +9342,7 @@
       </c>
       <c r="AD21" s="1"/>
     </row>
-    <row r="22" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="22" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="30" t="s">
         <v>59</v>
       </c>
@@ -8991,7 +9408,7 @@
       </c>
       <c r="AD22" s="1"/>
     </row>
-    <row r="23" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="23" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="30" t="s">
         <v>60</v>
       </c>
@@ -9047,7 +9464,7 @@
       </c>
       <c r="AD23" s="1"/>
     </row>
-    <row r="24" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="24" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="30" t="s">
         <v>61</v>
       </c>
@@ -9118,7 +9535,7 @@
       </c>
       <c r="AD24" s="1"/>
     </row>
-    <row r="25" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="25" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="30" t="s">
         <v>62</v>
       </c>
@@ -9191,7 +9608,7 @@
       </c>
       <c r="AD25" s="1"/>
     </row>
-    <row r="26" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="26" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="30" t="s">
         <v>63</v>
       </c>
@@ -9277,7 +9694,7 @@
       </c>
       <c r="AD26" s="1"/>
     </row>
-    <row r="27" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="27" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="30" t="s">
         <v>81</v>
       </c>
@@ -9361,7 +9778,7 @@
       </c>
       <c r="AD27" s="1"/>
     </row>
-    <row r="28" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="28" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="30" t="s">
         <v>82</v>
       </c>
@@ -9413,7 +9830,7 @@
       </c>
       <c r="AD28" s="1"/>
     </row>
-    <row r="29" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="29" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="11" t="s">
         <v>55</v>
       </c>
@@ -9514,7 +9931,7 @@
         <v>2997.5899999999997</v>
       </c>
     </row>
-    <row r="30" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="2:30" x14ac:dyDescent="0.3">
       <c r="D30" s="34">
         <f>(D29-C29)/C29</f>
         <v>-0.96125000000000005</v>
@@ -9552,37 +9969,37 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="31" spans="2:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="F31" s="64" t="s">
+    <row r="31" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="F31" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="65"/>
-      <c r="H31" s="66"/>
-      <c r="I31" s="62">
+      <c r="G31" s="66"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="63">
         <f>C29+E29+G29+I29+K29+M29+O29+Q29+S29+U29+W29</f>
         <v>2521.33</v>
       </c>
-      <c r="J31" s="63"/>
-    </row>
-    <row r="32" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="J31" s="64"/>
+    </row>
+    <row r="32" spans="2:30" x14ac:dyDescent="0.3">
       <c r="G32" s="70" t="s">
         <v>57</v>
       </c>
       <c r="H32" s="70"/>
-      <c r="I32" s="62">
+      <c r="I32" s="63">
         <f>+D29+F29+H29+J29+L29+N29+P29+R29+T29+V29+X29</f>
         <v>2997.5899999999997</v>
       </c>
-      <c r="J32" s="63"/>
-    </row>
-    <row r="33" spans="3:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="I33" s="62">
+      <c r="J32" s="64"/>
+    </row>
+    <row r="33" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="I33" s="63">
         <f>I32-I31</f>
         <v>476.25999999999976</v>
       </c>
-      <c r="J33" s="63"/>
-    </row>
-    <row r="34" spans="3:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="J33" s="64"/>
+    </row>
+    <row r="34" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C34" s="36">
         <f>C29+E29+G29</f>
         <v>620</v>
@@ -9620,7 +10037,7 @@
         <v>-291.55999999999995</v>
       </c>
     </row>
-    <row r="35" spans="3:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="3:17" x14ac:dyDescent="0.3">
       <c r="G35" t="s">
         <v>58</v>
       </c>
@@ -9628,19 +10045,19 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="36" spans="3:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="3:17" x14ac:dyDescent="0.3">
       <c r="G36" s="42" t="s">
         <v>64</v>
       </c>
       <c r="H36" s="42"/>
-      <c r="I36" s="72">
+      <c r="I36" s="71">
         <f>I35+I33</f>
         <v>2476.2599999999998</v>
       </c>
-      <c r="J36" s="72"/>
+      <c r="J36" s="71"/>
       <c r="M36" s="33"/>
     </row>
-    <row r="40" spans="3:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C40" s="1">
         <f>C29+E29+G29</f>
         <v>620</v>
@@ -9666,7 +10083,7 @@
         <v>338.44000000000005</v>
       </c>
     </row>
-    <row r="41" spans="3:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="3:17" x14ac:dyDescent="0.3">
       <c r="D41" s="1">
         <f>D40-C40</f>
         <v>10.789999999999964</v>
@@ -9682,11 +10099,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="U2:V2"/>
@@ -9695,14 +10112,14 @@
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="W2:X2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="O2:P2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="54" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="51" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9712,72 +10129,72 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:AH58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.68359375" customWidth="1"/>
-    <col min="2" max="2" width="5.68359375" customWidth="1"/>
-    <col min="3" max="3" width="7.83984375" customWidth="1"/>
-    <col min="4" max="4" width="9.15625" customWidth="1"/>
-    <col min="5" max="23" width="7.83984375" customWidth="1"/>
-    <col min="24" max="24" width="8.83984375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.41796875" customWidth="1"/>
-    <col min="26" max="26" width="9.68359375" customWidth="1"/>
-    <col min="29" max="29" width="10.41796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.6640625" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" customWidth="1"/>
+    <col min="5" max="23" width="7.88671875" customWidth="1"/>
+    <col min="24" max="24" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.44140625" customWidth="1"/>
+    <col min="26" max="26" width="9.6640625" customWidth="1"/>
+    <col min="29" max="29" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:34" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="2" spans="2:34" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="C2" s="68" t="s">
+    <row r="1" spans="2:34" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:34" ht="18" x14ac:dyDescent="0.35">
+      <c r="C2" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="71" t="s">
+      <c r="D2" s="62"/>
+      <c r="E2" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="68" t="s">
+      <c r="F2" s="68"/>
+      <c r="G2" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68" t="s">
+      <c r="H2" s="62"/>
+      <c r="I2" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68" t="s">
+      <c r="J2" s="62"/>
+      <c r="K2" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="68"/>
-      <c r="M2" s="71" t="s">
+      <c r="L2" s="62"/>
+      <c r="M2" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="67"/>
-      <c r="O2" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="68" t="s">
+      <c r="N2" s="68"/>
+      <c r="O2" s="62" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="R2" s="68"/>
-      <c r="S2" s="68" t="s">
+      <c r="R2" s="62"/>
+      <c r="S2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="T2" s="68"/>
-      <c r="U2" s="68" t="s">
+      <c r="T2" s="62"/>
+      <c r="U2" s="62" t="s">
         <v>65</v>
       </c>
       <c r="V2" s="69"/>
-      <c r="W2" s="68" t="s">
+      <c r="W2" s="62" t="s">
         <v>66</v>
       </c>
       <c r="X2" s="69"/>
-      <c r="Y2" s="67" t="s">
+      <c r="Y2" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="Z2" s="68"/>
-    </row>
-    <row r="3" spans="2:34" x14ac:dyDescent="0.55000000000000004">
+      <c r="Z2" s="62"/>
+    </row>
+    <row r="3" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B3" s="32" t="s">
         <v>29</v>
       </c>
@@ -9864,7 +10281,7 @@
       </c>
       <c r="AD3" s="25"/>
     </row>
-    <row r="4" spans="2:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B4" s="54" t="s">
         <v>32</v>
       </c>
@@ -9954,7 +10371,7 @@
       </c>
       <c r="AD4" s="1"/>
     </row>
-    <row r="5" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="52" t="s">
         <v>34</v>
       </c>
@@ -10021,7 +10438,7 @@
       </c>
       <c r="AD5" s="1"/>
     </row>
-    <row r="6" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="51" t="s">
         <v>35</v>
       </c>
@@ -10096,7 +10513,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="53" t="s">
         <v>36</v>
       </c>
@@ -10176,7 +10593,7 @@
         <v>-0.46759720837487539</v>
       </c>
     </row>
-    <row r="8" spans="2:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B8" s="52" t="s">
         <v>37</v>
       </c>
@@ -10261,7 +10678,7 @@
         <v>-0.12315563198624249</v>
       </c>
     </row>
-    <row r="9" spans="2:34" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B9" s="51" t="s">
         <v>38</v>
       </c>
@@ -10343,7 +10760,7 @@
         <v>-0.15405462480641985</v>
       </c>
     </row>
-    <row r="10" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="53" t="s">
         <v>39</v>
       </c>
@@ -10417,7 +10834,7 @@
         <v>0.33033599438547212</v>
       </c>
     </row>
-    <row r="11" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="52" t="s">
         <v>40</v>
       </c>
@@ -10503,7 +10920,7 @@
         <v>-0.93289170506912444</v>
       </c>
     </row>
-    <row r="12" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="51" t="s">
         <v>41</v>
       </c>
@@ -10577,7 +10994,7 @@
         <v>-0.29335709981924096</v>
       </c>
     </row>
-    <row r="13" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="13" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="53" t="s">
         <v>42</v>
       </c>
@@ -10655,7 +11072,7 @@
         <v>-0.55581714734157361</v>
       </c>
     </row>
-    <row r="14" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="52" t="s">
         <v>43</v>
       </c>
@@ -10737,7 +11154,7 @@
         <v>-0.4323508459483526</v>
       </c>
     </row>
-    <row r="15" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="15" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="51" t="s">
         <v>44</v>
       </c>
@@ -10815,7 +11232,7 @@
         <v>0.28991789529442913</v>
       </c>
     </row>
-    <row r="16" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="53" t="s">
         <v>45</v>
       </c>
@@ -10893,7 +11310,7 @@
         <v>-0.64578454332552693</v>
       </c>
     </row>
-    <row r="17" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="52" t="s">
         <v>46</v>
       </c>
@@ -10961,7 +11378,7 @@
       </c>
       <c r="AD17" s="1"/>
     </row>
-    <row r="18" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="18" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="51" t="s">
         <v>47</v>
       </c>
@@ -11021,7 +11438,7 @@
       </c>
       <c r="AD18" s="1"/>
     </row>
-    <row r="19" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="53" t="s">
         <v>48</v>
       </c>
@@ -11082,7 +11499,7 @@
       </c>
       <c r="AD19" s="1"/>
     </row>
-    <row r="20" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="52" t="s">
         <v>49</v>
       </c>
@@ -11146,7 +11563,7 @@
       </c>
       <c r="AD20" s="1"/>
     </row>
-    <row r="21" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="51" t="s">
         <v>50</v>
       </c>
@@ -11210,7 +11627,7 @@
       </c>
       <c r="AD21" s="1"/>
     </row>
-    <row r="22" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="22" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="53" t="s">
         <v>59</v>
       </c>
@@ -11271,7 +11688,7 @@
       </c>
       <c r="AD22" s="1"/>
     </row>
-    <row r="23" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="23" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="52" t="s">
         <v>60</v>
       </c>
@@ -11338,7 +11755,7 @@
       </c>
       <c r="AD23" s="1"/>
     </row>
-    <row r="24" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="24" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="51" t="s">
         <v>61</v>
       </c>
@@ -11399,7 +11816,7 @@
       </c>
       <c r="AD24" s="1"/>
     </row>
-    <row r="25" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="25" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="53" t="s">
         <v>62</v>
       </c>
@@ -11461,7 +11878,7 @@
       </c>
       <c r="AD25" s="1"/>
     </row>
-    <row r="26" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B26" s="54" t="s">
         <v>63</v>
       </c>
@@ -11546,7 +11963,7 @@
       </c>
       <c r="AD26" s="1"/>
     </row>
-    <row r="27" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B27" s="30" t="s">
         <v>84</v>
       </c>
@@ -11601,7 +12018,7 @@
       <c r="AC27" s="1"/>
       <c r="AD27" s="1"/>
     </row>
-    <row r="28" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B28" s="30" t="s">
         <v>81</v>
       </c>
@@ -11640,7 +12057,7 @@
       <c r="AC28" s="1"/>
       <c r="AD28" s="1"/>
     </row>
-    <row r="29" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="29" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="11" t="s">
         <v>55</v>
       </c>
@@ -11741,7 +12158,7 @@
         <v>1004.25</v>
       </c>
     </row>
-    <row r="30" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="2:30" x14ac:dyDescent="0.3">
       <c r="D30" s="56">
         <f>(D29-C29)/C29</f>
         <v>0.16699999999999993</v>
@@ -11783,41 +12200,41 @@
         <v>-0.71365638766519823</v>
       </c>
     </row>
-    <row r="31" spans="2:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="F31" s="64" t="s">
+    <row r="31" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="F31" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="65"/>
-      <c r="H31" s="66"/>
-      <c r="I31" s="62">
+      <c r="G31" s="66"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="63">
         <f>C29+E29+G29+I29+K29+M29+O29+Q29+S29+U29+W29</f>
         <v>2462.73</v>
       </c>
-      <c r="J31" s="63"/>
-    </row>
-    <row r="32" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="J31" s="64"/>
+    </row>
+    <row r="32" spans="2:30" x14ac:dyDescent="0.3">
       <c r="G32" s="70" t="s">
         <v>57</v>
       </c>
       <c r="H32" s="70"/>
-      <c r="I32" s="62">
+      <c r="I32" s="63">
         <f>+D29+F29+H29+J29+L29+N29+P29+R29+T29+V29+X29</f>
         <v>1004.25</v>
       </c>
-      <c r="J32" s="63"/>
-    </row>
-    <row r="33" spans="3:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="I33" s="62">
+      <c r="J32" s="64"/>
+    </row>
+    <row r="33" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="I33" s="63">
         <f>I32-I31</f>
         <v>-1458.48</v>
       </c>
-      <c r="J33" s="63"/>
+      <c r="J33" s="64"/>
       <c r="Y33">
         <f>2167+183+5*10</f>
         <v>2400</v>
       </c>
     </row>
-    <row r="34" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C34" s="36">
         <f>C29+E29+G29+I29</f>
         <v>935</v>
@@ -11860,7 +12277,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C35" s="36"/>
       <c r="D35" s="34">
         <f>(D34-C34)/C34</f>
@@ -11881,7 +12298,7 @@
       <c r="Q35" s="41"/>
       <c r="X35" s="55"/>
     </row>
-    <row r="36" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="3:25" x14ac:dyDescent="0.3">
       <c r="G36" t="s">
         <v>58</v>
       </c>
@@ -11893,7 +12310,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="37" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="3:25" x14ac:dyDescent="0.3">
       <c r="G37" t="s">
         <v>85</v>
       </c>
@@ -11902,19 +12319,19 @@
         <v>-2695</v>
       </c>
     </row>
-    <row r="38" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="3:25" x14ac:dyDescent="0.3">
       <c r="G38" s="42" t="s">
         <v>64</v>
       </c>
       <c r="H38" s="42"/>
-      <c r="I38" s="72">
+      <c r="I38" s="71">
         <f>I36+I33+J37</f>
         <v>322.7800000000002</v>
       </c>
-      <c r="J38" s="72"/>
+      <c r="J38" s="71"/>
       <c r="M38" s="33"/>
     </row>
-    <row r="40" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C40">
         <v>1</v>
       </c>
@@ -11954,13 +12371,13 @@
         <v>233</v>
       </c>
     </row>
-    <row r="41" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="3:25" x14ac:dyDescent="0.3">
       <c r="V41">
         <f>3260-720</f>
         <v>2540</v>
       </c>
     </row>
-    <row r="42" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C42" s="1">
         <f>C29+E29+G29+I29</f>
         <v>935</v>
@@ -11986,7 +12403,7 @@
         <v>401.38</v>
       </c>
     </row>
-    <row r="43" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="3:25" x14ac:dyDescent="0.3">
       <c r="D43" s="1">
         <f>D42-C42</f>
         <v>-654.92000000000007</v>
@@ -12000,12 +12417,12 @@
         <v>-305.62</v>
       </c>
     </row>
-    <row r="45" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="3:25" x14ac:dyDescent="0.3">
       <c r="V45" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="46" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="3:25" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
         <v>88</v>
       </c>
@@ -12016,7 +12433,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="3:25" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
         <v>90</v>
       </c>
@@ -12030,7 +12447,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="3:25" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
         <v>92</v>
       </c>
@@ -12045,7 +12462,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
         <v>12</v>
       </c>
@@ -12060,7 +12477,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
         <v>94</v>
       </c>
@@ -12075,7 +12492,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
         <v>95</v>
       </c>
@@ -12090,7 +12507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
         <v>93</v>
       </c>
@@ -12105,7 +12522,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
         <v>97</v>
       </c>
@@ -12120,7 +12537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
         <v>98</v>
       </c>
@@ -12135,7 +12552,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
         <v>89</v>
       </c>
@@ -12150,7 +12567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
         <v>96</v>
       </c>
@@ -12163,7 +12580,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
         <v>9</v>
       </c>
@@ -12172,7 +12589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
         <v>99</v>
       </c>
@@ -12183,6 +12600,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:V2"/>
     <mergeCell ref="W2:X2"/>
     <mergeCell ref="Y2:Z2"/>
     <mergeCell ref="C2:D2"/>
@@ -12191,19 +12618,9 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="M2:N2"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="54" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="51" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12213,76 +12630,76 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:AH58"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.68359375" customWidth="1"/>
-    <col min="2" max="2" width="5.68359375" customWidth="1"/>
-    <col min="3" max="3" width="7.83984375" customWidth="1"/>
-    <col min="4" max="4" width="9.15625" customWidth="1"/>
-    <col min="5" max="7" width="7.83984375" customWidth="1"/>
-    <col min="8" max="8" width="8.68359375" customWidth="1"/>
-    <col min="9" max="19" width="7.83984375" customWidth="1"/>
-    <col min="20" max="20" width="8.578125" customWidth="1"/>
-    <col min="21" max="23" width="7.83984375" customWidth="1"/>
-    <col min="24" max="24" width="8.83984375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.41796875" customWidth="1"/>
-    <col min="26" max="26" width="9.68359375" customWidth="1"/>
-    <col min="29" max="29" width="10.41796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.6640625" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" customWidth="1"/>
+    <col min="5" max="7" width="7.88671875" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" customWidth="1"/>
+    <col min="9" max="19" width="7.88671875" customWidth="1"/>
+    <col min="20" max="20" width="8.5546875" customWidth="1"/>
+    <col min="21" max="23" width="7.88671875" customWidth="1"/>
+    <col min="24" max="24" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.44140625" customWidth="1"/>
+    <col min="26" max="26" width="9.6640625" customWidth="1"/>
+    <col min="29" max="29" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:34" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="2" spans="2:34" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="C2" s="68" t="s">
+    <row r="1" spans="2:34" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:34" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C2" s="62" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="71" t="s">
+      <c r="D2" s="62"/>
+      <c r="E2" s="72" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="68" t="s">
+      <c r="F2" s="68"/>
+      <c r="G2" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68" t="s">
+      <c r="H2" s="62"/>
+      <c r="I2" s="62" t="s">
         <v>103</v>
       </c>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68" t="s">
+      <c r="J2" s="62"/>
+      <c r="K2" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="L2" s="68"/>
-      <c r="M2" s="71" t="s">
+      <c r="L2" s="62"/>
+      <c r="M2" s="72" t="s">
         <v>105</v>
       </c>
-      <c r="N2" s="67"/>
-      <c r="O2" s="68" t="s">
+      <c r="N2" s="68"/>
+      <c r="O2" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="68" t="s">
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="R2" s="68"/>
-      <c r="S2" s="68" t="s">
+      <c r="R2" s="62"/>
+      <c r="S2" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="T2" s="68"/>
-      <c r="U2" s="68" t="s">
+      <c r="T2" s="62"/>
+      <c r="U2" s="62" t="s">
         <v>108</v>
       </c>
       <c r="V2" s="69"/>
-      <c r="W2" s="68" t="s">
+      <c r="W2" s="62" t="s">
         <v>66</v>
       </c>
       <c r="X2" s="69"/>
-      <c r="Y2" s="67" t="s">
+      <c r="Y2" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="Z2" s="68"/>
-    </row>
-    <row r="3" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Z2" s="62"/>
+    </row>
+    <row r="3" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="32" t="s">
         <v>29</v>
       </c>
@@ -12369,7 +12786,7 @@
       </c>
       <c r="AD3" s="25"/>
     </row>
-    <row r="4" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="54" t="s">
         <v>109</v>
       </c>
@@ -12417,7 +12834,7 @@
       </c>
       <c r="AD4" s="1"/>
     </row>
-    <row r="5" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="54" t="s">
         <v>32</v>
       </c>
@@ -12506,7 +12923,7 @@
       </c>
       <c r="AD5" s="1"/>
     </row>
-    <row r="6" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="52" t="s">
         <v>34</v>
       </c>
@@ -12586,7 +13003,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="51" t="s">
         <v>35</v>
       </c>
@@ -12664,7 +13081,7 @@
         <v>-0.55082781456953644</v>
       </c>
     </row>
-    <row r="8" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="53" t="s">
         <v>36</v>
       </c>
@@ -12742,7 +13159,7 @@
         <v>-0.17974063400576371</v>
       </c>
     </row>
-    <row r="9" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="52" t="s">
         <v>37</v>
       </c>
@@ -12824,7 +13241,7 @@
         <v>-0.19947602599379421</v>
       </c>
     </row>
-    <row r="10" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="51" t="s">
         <v>38</v>
       </c>
@@ -12902,7 +13319,7 @@
         <v>0.11103377536815863</v>
       </c>
     </row>
-    <row r="11" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="53" t="s">
         <v>39</v>
       </c>
@@ -12980,7 +13397,7 @@
         <v>-0.9084342963653308</v>
       </c>
     </row>
-    <row r="12" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="52" t="s">
         <v>40</v>
       </c>
@@ -13062,7 +13479,7 @@
         <v>-0.35690561460258791</v>
       </c>
     </row>
-    <row r="13" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="13" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="51" t="s">
         <v>41</v>
       </c>
@@ -13140,7 +13557,7 @@
         <v>-0.5348574654247813</v>
       </c>
     </row>
-    <row r="14" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="53" t="s">
         <v>42</v>
       </c>
@@ -13219,7 +13636,7 @@
         <v>-0.52884700665188467</v>
       </c>
     </row>
-    <row r="15" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="15" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="52" t="s">
         <v>43</v>
       </c>
@@ -13301,7 +13718,7 @@
         <v>0.24465399574374394</v>
       </c>
     </row>
-    <row r="16" spans="2:34" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="51" t="s">
         <v>44</v>
       </c>
@@ -13379,7 +13796,7 @@
         <v>-0.75604838709677424</v>
       </c>
     </row>
-    <row r="17" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="53" t="s">
         <v>45</v>
       </c>
@@ -13439,7 +13856,7 @@
       </c>
       <c r="AD17" s="1"/>
     </row>
-    <row r="18" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="18" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="52" t="s">
         <v>46</v>
       </c>
@@ -13507,7 +13924,7 @@
       </c>
       <c r="AD18" s="1"/>
     </row>
-    <row r="19" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="51" t="s">
         <v>47</v>
       </c>
@@ -13567,7 +13984,7 @@
       </c>
       <c r="AD19" s="1"/>
     </row>
-    <row r="20" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="53" t="s">
         <v>48</v>
       </c>
@@ -13627,7 +14044,7 @@
       </c>
       <c r="AD20" s="1"/>
     </row>
-    <row r="21" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="52" t="s">
         <v>49</v>
       </c>
@@ -13687,7 +14104,7 @@
       </c>
       <c r="AD21" s="1"/>
     </row>
-    <row r="22" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="22" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="51" t="s">
         <v>50</v>
       </c>
@@ -13747,7 +14164,7 @@
       </c>
       <c r="AD22" s="1"/>
     </row>
-    <row r="23" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="23" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="53" t="s">
         <v>59</v>
       </c>
@@ -13807,7 +14224,7 @@
       </c>
       <c r="AD23" s="1"/>
     </row>
-    <row r="24" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="24" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="52" t="s">
         <v>60</v>
       </c>
@@ -13867,7 +14284,7 @@
       </c>
       <c r="AD24" s="1"/>
     </row>
-    <row r="25" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="25" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="51" t="s">
         <v>61</v>
       </c>
@@ -13931,7 +14348,7 @@
       </c>
       <c r="AD25" s="1"/>
     </row>
-    <row r="26" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="26" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="53" t="s">
         <v>62</v>
       </c>
@@ -13991,7 +14408,7 @@
       </c>
       <c r="AD26" s="1"/>
     </row>
-    <row r="27" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="27" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="30" t="s">
         <v>63</v>
       </c>
@@ -14059,7 +14476,7 @@
       </c>
       <c r="AD27" s="1"/>
     </row>
-    <row r="28" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="28" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="30" t="s">
         <v>84</v>
       </c>
@@ -14118,7 +14535,7 @@
       <c r="AC28" s="1"/>
       <c r="AD28" s="1"/>
     </row>
-    <row r="29" spans="2:30" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="29" spans="2:30" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="11" t="s">
         <v>55</v>
       </c>
@@ -14220,7 +14637,7 @@
       </c>
       <c r="AA29" s="1"/>
     </row>
-    <row r="30" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="2:30" x14ac:dyDescent="0.3">
       <c r="D30" s="56">
         <f>(D29-C29)/C29</f>
         <v>-1</v>
@@ -14262,41 +14679,41 @@
         <v>-0.75657894736842102</v>
       </c>
     </row>
-    <row r="31" spans="2:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="F31" s="64" t="s">
+    <row r="31" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="F31" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="65"/>
-      <c r="H31" s="66"/>
-      <c r="I31" s="62">
+      <c r="G31" s="66"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="63">
         <f>C29+E29+G29+I29+K29+M29+O29+Q29+S29+U29+W29</f>
         <v>2158</v>
       </c>
-      <c r="J31" s="63"/>
-    </row>
-    <row r="32" spans="2:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="J31" s="64"/>
+    </row>
+    <row r="32" spans="2:30" x14ac:dyDescent="0.3">
       <c r="G32" s="70" t="s">
         <v>57</v>
       </c>
       <c r="H32" s="70"/>
-      <c r="I32" s="62">
+      <c r="I32" s="63">
         <f>+D29+F29+H29+J29+L29+N29+P29+R29+T29+V29+X29</f>
         <v>709.26</v>
       </c>
-      <c r="J32" s="63"/>
-    </row>
-    <row r="33" spans="3:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="I33" s="62">
+      <c r="J32" s="64"/>
+    </row>
+    <row r="33" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="I33" s="63">
         <f>I32-I31</f>
         <v>-1448.74</v>
       </c>
-      <c r="J33" s="63"/>
+      <c r="J33" s="64"/>
       <c r="Y33">
         <f>2167+183+5*10</f>
         <v>2400</v>
       </c>
     </row>
-    <row r="34" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C34" s="36">
         <f>C29+E29+G29+I29</f>
         <v>828</v>
@@ -14339,7 +14756,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C35" s="36"/>
       <c r="D35" s="34">
         <f>(D34-C34)/C34</f>
@@ -14360,7 +14777,7 @@
       <c r="Q35" s="41"/>
       <c r="X35" s="55"/>
     </row>
-    <row r="36" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="3:25" x14ac:dyDescent="0.3">
       <c r="G36" t="s">
         <v>58</v>
       </c>
@@ -14369,27 +14786,27 @@
         <v>2001.59</v>
       </c>
     </row>
-    <row r="37" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="3:25" x14ac:dyDescent="0.3">
       <c r="G37" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="3:25" x14ac:dyDescent="0.3">
       <c r="G38" s="42" t="s">
         <v>64</v>
       </c>
       <c r="H38" s="42"/>
-      <c r="I38" s="72">
+      <c r="I38" s="71">
         <f>I36+I33</f>
         <v>552.84999999999991</v>
       </c>
-      <c r="J38" s="72"/>
+      <c r="J38" s="71"/>
       <c r="M38" s="33"/>
     </row>
-    <row r="40" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="3:25" x14ac:dyDescent="0.3">
       <c r="X40" s="55"/>
     </row>
-    <row r="42" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C42" s="1">
         <f>C29+E29+G29+I29</f>
         <v>828</v>
@@ -14415,7 +14832,7 @@
         <v>174.41</v>
       </c>
     </row>
-    <row r="43" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="3:25" x14ac:dyDescent="0.3">
       <c r="D43" s="1">
         <f>D42-C42</f>
         <v>-779.4</v>
@@ -14429,12 +14846,12 @@
         <v>-470.59000000000003</v>
       </c>
     </row>
-    <row r="45" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="3:25" x14ac:dyDescent="0.3">
       <c r="V45" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="3:25" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
         <v>88</v>
       </c>
@@ -14448,7 +14865,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="3:25" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
         <v>90</v>
       </c>
@@ -14468,7 +14885,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="3:25" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
         <v>92</v>
       </c>
@@ -14489,7 +14906,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
         <v>12</v>
       </c>
@@ -14510,7 +14927,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
         <v>94</v>
       </c>
@@ -14531,7 +14948,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
         <v>95</v>
       </c>
@@ -14552,7 +14969,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
         <v>93</v>
       </c>
@@ -14573,7 +14990,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
         <v>97</v>
       </c>
@@ -14594,7 +15011,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
         <v>98</v>
       </c>
@@ -14615,7 +15032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
         <v>89</v>
       </c>
@@ -14636,7 +15053,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
         <v>96</v>
       </c>
@@ -14655,7 +15072,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="57" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
         <v>9</v>
       </c>
@@ -14670,7 +15087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
         <v>99</v>
       </c>
@@ -14685,6 +15102,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:V2"/>
     <mergeCell ref="W2:X2"/>
     <mergeCell ref="Y2:Z2"/>
     <mergeCell ref="C2:D2"/>
@@ -14693,16 +15120,6 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="M2:N2"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="51" orientation="landscape" r:id="rId1"/>
@@ -14715,90 +15132,91 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:AL61"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.68359375" customWidth="1"/>
-    <col min="2" max="2" width="5.68359375" customWidth="1"/>
-    <col min="3" max="3" width="7.83984375" customWidth="1"/>
-    <col min="4" max="4" width="9.15625" customWidth="1"/>
-    <col min="5" max="5" width="9.83984375" customWidth="1"/>
-    <col min="6" max="7" width="7.83984375" customWidth="1"/>
-    <col min="8" max="8" width="8.68359375" customWidth="1"/>
-    <col min="9" max="19" width="7.83984375" customWidth="1"/>
-    <col min="20" max="20" width="8.578125" customWidth="1"/>
-    <col min="21" max="23" width="7.83984375" customWidth="1"/>
-    <col min="24" max="24" width="8.83984375" customWidth="1"/>
-    <col min="25" max="25" width="9.41796875" customWidth="1"/>
-    <col min="26" max="26" width="9.68359375" customWidth="1"/>
-    <col min="29" max="29" width="10.41796875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.15625" customWidth="1"/>
+    <col min="1" max="1" width="1.6640625" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" customWidth="1"/>
+    <col min="6" max="7" width="7.88671875" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" customWidth="1"/>
+    <col min="9" max="19" width="7.88671875" customWidth="1"/>
+    <col min="20" max="20" width="8.5546875" customWidth="1"/>
+    <col min="21" max="23" width="7.88671875" customWidth="1"/>
+    <col min="24" max="24" width="8.88671875" customWidth="1"/>
+    <col min="25" max="25" width="9.44140625" customWidth="1"/>
+    <col min="26" max="26" width="9.6640625" customWidth="1"/>
+    <col min="29" max="29" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.109375" customWidth="1"/>
     <col min="34" max="34" width="11" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="10.578125" customWidth="1"/>
+    <col min="37" max="37" width="11.109375" customWidth="1"/>
+    <col min="38" max="38" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:38" ht="7.5" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="W1" s="75"/>
-      <c r="X1" s="76"/>
-    </row>
-    <row r="2" spans="2:38" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="C2" s="68" t="s">
+    <row r="1" spans="2:38" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="W1" s="73"/>
+      <c r="X1" s="74"/>
+    </row>
+    <row r="2" spans="2:38" ht="18" x14ac:dyDescent="0.35">
+      <c r="C2" s="62" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="71" t="s">
+      <c r="D2" s="62"/>
+      <c r="E2" s="72" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="68" t="s">
+      <c r="F2" s="68"/>
+      <c r="G2" s="62" t="s">
         <v>114</v>
       </c>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68" t="s">
+      <c r="H2" s="62"/>
+      <c r="I2" s="62" t="s">
         <v>115</v>
       </c>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68" t="s">
+      <c r="J2" s="62"/>
+      <c r="K2" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="L2" s="68"/>
-      <c r="M2" s="71" t="s">
+      <c r="L2" s="62"/>
+      <c r="M2" s="72" t="s">
         <v>103</v>
       </c>
-      <c r="N2" s="67"/>
-      <c r="O2" s="68" t="s">
+      <c r="N2" s="68"/>
+      <c r="O2" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="P2" s="68"/>
-      <c r="Q2" s="68" t="s">
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="R2" s="68"/>
-      <c r="S2" s="68" t="s">
+      <c r="R2" s="62"/>
+      <c r="S2" s="62" t="s">
         <v>100</v>
       </c>
-      <c r="T2" s="68"/>
-      <c r="U2" s="68" t="s">
+      <c r="T2" s="62"/>
+      <c r="U2" s="62" t="s">
         <v>108</v>
       </c>
-      <c r="V2" s="71"/>
-      <c r="W2" s="77" t="s">
+      <c r="V2" s="72"/>
+      <c r="W2" s="75" t="s">
         <v>102</v>
       </c>
-      <c r="X2" s="78"/>
-      <c r="Y2" s="77" t="s">
+      <c r="X2" s="76"/>
+      <c r="Y2" s="75" t="s">
         <v>105</v>
       </c>
-      <c r="Z2" s="79"/>
-      <c r="AA2" s="73" t="s">
+      <c r="Z2" s="77"/>
+      <c r="AA2" s="78" t="s">
         <v>66</v>
       </c>
-      <c r="AB2" s="74"/>
-      <c r="AC2" s="67" t="s">
+      <c r="AB2" s="79"/>
+      <c r="AC2" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="AD2" s="68"/>
-    </row>
-    <row r="3" spans="2:38" x14ac:dyDescent="0.55000000000000004">
+      <c r="AD2" s="62"/>
+    </row>
+    <row r="3" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B3" s="32" t="s">
         <v>29</v>
       </c>
@@ -14897,7 +15315,7 @@
       </c>
       <c r="AH3" s="25"/>
     </row>
-    <row r="4" spans="2:38" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B4" s="54" t="s">
         <v>109</v>
       </c>
@@ -14953,7 +15371,7 @@
       </c>
       <c r="AH4" s="1"/>
     </row>
-    <row r="5" spans="2:38" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B5" s="54" t="s">
         <v>32</v>
       </c>
@@ -15050,7 +15468,7 @@
       </c>
       <c r="AH5" s="1"/>
     </row>
-    <row r="6" spans="2:38" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="52" t="s">
         <v>34</v>
       </c>
@@ -15134,7 +15552,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="2:38" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="51" t="s">
         <v>35</v>
       </c>
@@ -15212,23 +15630,23 @@
         <v>71</v>
       </c>
       <c r="AI7" s="44">
-        <f>+E30+'Punters 2023'!AE7</f>
-        <v>1223</v>
+        <f>+E30+'Punters 2024'!AE7</f>
+        <v>1428</v>
       </c>
       <c r="AJ7" s="44">
-        <f>+F30+'Punters 2023'!AF7</f>
-        <v>534</v>
+        <f>+F30+'Punters 2024'!AF7</f>
+        <v>542.6</v>
       </c>
       <c r="AK7" s="49">
         <f>+AJ7-AI7</f>
-        <v>-689</v>
+        <v>-885.4</v>
       </c>
       <c r="AL7" s="47">
         <f>(AJ7-AI7)/AI7</f>
-        <v>-0.56336876533115288</v>
-      </c>
-    </row>
-    <row r="8" spans="2:38" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+        <v>-0.62002801120448181</v>
+      </c>
+    </row>
+    <row r="8" spans="2:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="53" t="s">
         <v>36</v>
       </c>
@@ -15298,23 +15716,23 @@
         <v>72</v>
       </c>
       <c r="AI8" s="44">
-        <f>+K30+'Punters 2023'!AE8</f>
-        <v>1388</v>
+        <f>+K30+'Punters 2024'!AE8</f>
+        <v>1613</v>
       </c>
       <c r="AJ8" s="44">
-        <f>+L30+'Punters 2023'!AF8</f>
-        <v>1019.77</v>
+        <f>+L30+'Punters 2024'!AF8</f>
+        <v>1138.52</v>
       </c>
       <c r="AK8" s="50">
         <f t="shared" ref="AK8:AK16" si="5">+AJ8-AI8</f>
-        <v>-368.23</v>
+        <v>-474.48</v>
       </c>
       <c r="AL8" s="47">
         <f t="shared" ref="AL8:AL16" si="6">(AJ8-AI8)/AI8</f>
-        <v>-0.26529538904899136</v>
-      </c>
-    </row>
-    <row r="9" spans="2:38" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+        <v>-0.29415995040297582</v>
+      </c>
+    </row>
+    <row r="9" spans="2:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="52" t="s">
         <v>37</v>
       </c>
@@ -15384,23 +15802,23 @@
         <v>73</v>
       </c>
       <c r="AI9" s="44">
-        <f>+M30+'Punters 2023'!AE9</f>
-        <v>1356.48</v>
+        <f>+Y30+'Punters 2024'!AE9</f>
+        <v>1593.48</v>
       </c>
       <c r="AJ9" s="44">
-        <f>N30+'Punters 2023'!AF9</f>
-        <v>1029.4000000000001</v>
+        <f>Z30+'Punters 2024'!AF9</f>
+        <v>1278.68</v>
       </c>
       <c r="AK9" s="50">
         <f t="shared" si="5"/>
-        <v>-327.07999999999993</v>
+        <v>-314.79999999999995</v>
       </c>
       <c r="AL9" s="47">
         <f t="shared" si="6"/>
-        <v>-0.24112408586930875</v>
-      </c>
-    </row>
-    <row r="10" spans="2:38" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+        <v>-0.1975550367748575</v>
+      </c>
+    </row>
+    <row r="10" spans="2:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="51" t="s">
         <v>38</v>
       </c>
@@ -15471,23 +15889,23 @@
         <v>74</v>
       </c>
       <c r="AI10" s="44">
-        <f>+C30+'Punters 2023'!AE10</f>
-        <v>1364.9</v>
+        <f>+S30+'Punters 2024'!AE10</f>
+        <v>1589.9</v>
       </c>
       <c r="AJ10" s="44">
-        <f>+D30+'Punters 2023'!AF10</f>
-        <v>1641.4499999999998</v>
+        <f>+T30+'Punters 2024'!AF10</f>
+        <v>1785.06</v>
       </c>
       <c r="AK10" s="50">
         <f t="shared" si="5"/>
-        <v>276.54999999999973</v>
+        <v>195.15999999999985</v>
       </c>
       <c r="AL10" s="45">
         <f t="shared" si="6"/>
-        <v>0.20261557623269083</v>
-      </c>
-    </row>
-    <row r="11" spans="2:38" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+        <v>0.12274985848166542</v>
+      </c>
+    </row>
+    <row r="11" spans="2:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="53" t="s">
         <v>39</v>
       </c>
@@ -15558,23 +15976,23 @@
         <v>75</v>
       </c>
       <c r="AI11" s="44">
-        <f>+I30+'Punters 2023'!AE11</f>
-        <v>1093</v>
+        <f>+M30+'Punters 2024'!AE11</f>
+        <v>1293</v>
       </c>
       <c r="AJ11" s="44">
-        <f>+J30+'Punters 2023'!AF11</f>
-        <v>241.6</v>
+        <f>+N30+'Punters 2024'!AF11</f>
+        <v>166.25</v>
       </c>
       <c r="AK11" s="49">
         <f t="shared" si="5"/>
-        <v>-851.4</v>
+        <v>-1126.75</v>
       </c>
       <c r="AL11" s="47">
         <f t="shared" si="6"/>
-        <v>-0.77895699908508687</v>
-      </c>
-    </row>
-    <row r="12" spans="2:38" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+        <v>-0.8714230471771075</v>
+      </c>
+    </row>
+    <row r="12" spans="2:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="52" t="s">
         <v>40</v>
       </c>
@@ -15640,23 +16058,23 @@
         <v>76</v>
       </c>
       <c r="AI12" s="44">
-        <f>+U30+'Punters 2023'!AE12</f>
-        <v>1394.96</v>
+        <f>+U30+'Punters 2024'!AE12</f>
+        <v>1584.96</v>
       </c>
       <c r="AJ12" s="44">
-        <f>+V30+'Punters 2023'!AF12</f>
-        <v>844.40999999999985</v>
+        <f>+V30+'Punters 2024'!AF12</f>
+        <v>890.65999999999985</v>
       </c>
       <c r="AK12" s="49">
         <f t="shared" si="5"/>
-        <v>-550.55000000000018</v>
+        <v>-694.30000000000018</v>
       </c>
       <c r="AL12" s="47">
         <f t="shared" si="6"/>
-        <v>-0.39467081493376166</v>
-      </c>
-    </row>
-    <row r="13" spans="2:38" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+        <v>-0.43805521905915618</v>
+      </c>
+    </row>
+    <row r="13" spans="2:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="51" t="s">
         <v>41</v>
       </c>
@@ -15730,23 +16148,23 @@
         <v>77</v>
       </c>
       <c r="AI13" s="44">
-        <f>+S30+'Punters 2023'!AE13</f>
-        <v>1346.3400000000001</v>
+        <f>+I30+'Punters 2024'!AE13</f>
+        <v>1571.3400000000001</v>
       </c>
       <c r="AJ13" s="44">
-        <f>+T30+'Punters 2023'!AF13</f>
-        <v>766.69</v>
+        <f>+J30+'Punters 2024'!AF13</f>
+        <v>809.59</v>
       </c>
       <c r="AK13" s="49">
         <f t="shared" si="5"/>
-        <v>-579.65000000000009</v>
+        <v>-761.75000000000011</v>
       </c>
       <c r="AL13" s="47">
         <f t="shared" si="6"/>
-        <v>-0.43053760565681776</v>
-      </c>
-    </row>
-    <row r="14" spans="2:38" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+        <v>-0.48477732381279676</v>
+      </c>
+    </row>
+    <row r="14" spans="2:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="53" t="s">
         <v>42</v>
       </c>
@@ -15816,23 +16234,23 @@
         <v>78</v>
       </c>
       <c r="AI14" s="44">
-        <f>+Q30+'Punters 2023'!AE14</f>
-        <v>1348</v>
+        <f>+Q30+'Punters 2024'!AE14</f>
+        <v>1578</v>
       </c>
       <c r="AJ14" s="44">
-        <f>+R30+'Punters 2023'!AF14</f>
+        <f>+R30+'Punters 2024'!AF14</f>
         <v>772.12</v>
       </c>
       <c r="AK14" s="49">
         <f t="shared" si="5"/>
-        <v>-575.88</v>
+        <v>-805.88</v>
       </c>
       <c r="AL14" s="47">
         <f t="shared" si="6"/>
-        <v>-0.42721068249258159</v>
-      </c>
-    </row>
-    <row r="15" spans="2:38" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+        <v>-0.51069708491761723</v>
+      </c>
+    </row>
+    <row r="15" spans="2:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="52" t="s">
         <v>43</v>
       </c>
@@ -15902,23 +16320,23 @@
         <v>79</v>
       </c>
       <c r="AI15" s="44">
-        <f>+O30+'Punters 2023'!AE15</f>
-        <v>1357.7</v>
+        <f>+O30+'Punters 2024'!AE15</f>
+        <v>1587.7</v>
       </c>
       <c r="AJ15" s="44">
-        <f>+P30+'Punters 2023'!AF15</f>
-        <v>2054.85</v>
+        <f>+P30+'Punters 2024'!AF15</f>
+        <v>2289.85</v>
       </c>
       <c r="AK15" s="50">
         <f t="shared" si="5"/>
-        <v>697.14999999999986</v>
+        <v>702.14999999999986</v>
       </c>
       <c r="AL15" s="45">
         <f t="shared" si="6"/>
-        <v>0.51347867717463347</v>
-      </c>
-    </row>
-    <row r="16" spans="2:38" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+        <v>0.44224349688228243</v>
+      </c>
+    </row>
+    <row r="16" spans="2:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="51" t="s">
         <v>44</v>
       </c>
@@ -15988,23 +16406,23 @@
         <v>80</v>
       </c>
       <c r="AI16" s="44">
-        <f>+G30+'Punters 2023'!AE16</f>
-        <v>658</v>
+        <f>+W30+'Punters 2024'!AE16</f>
+        <v>820</v>
       </c>
       <c r="AJ16" s="44">
-        <f>+H30+'Punters 2023'!AF16</f>
-        <v>151.25</v>
+        <f>+X30+'Punters 2024'!AF16</f>
+        <v>287.33</v>
       </c>
       <c r="AK16" s="49">
         <f t="shared" si="5"/>
-        <v>-506.75</v>
+        <v>-532.67000000000007</v>
       </c>
       <c r="AL16" s="47">
         <f t="shared" si="6"/>
-        <v>-0.77013677811550152</v>
-      </c>
-    </row>
-    <row r="17" spans="2:38" x14ac:dyDescent="0.55000000000000004">
+        <v>-0.64959756097560983</v>
+      </c>
+    </row>
+    <row r="17" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B17" s="53" t="s">
         <v>45</v>
       </c>
@@ -16094,7 +16512,7 @@
         <v>-0.44444444444444442</v>
       </c>
     </row>
-    <row r="18" spans="2:38" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B18" s="52" t="s">
         <v>46</v>
       </c>
@@ -16181,7 +16599,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="19" spans="2:38" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="19" spans="2:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="51" t="s">
         <v>47</v>
       </c>
@@ -16249,7 +16667,7 @@
       </c>
       <c r="AH19" s="1"/>
     </row>
-    <row r="20" spans="2:38" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="53" t="s">
         <v>48</v>
       </c>
@@ -16325,7 +16743,7 @@
       </c>
       <c r="AH20" s="1"/>
     </row>
-    <row r="21" spans="2:38" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="52" t="s">
         <v>49</v>
       </c>
@@ -16396,7 +16814,7 @@
       </c>
       <c r="AH21" s="1"/>
     </row>
-    <row r="22" spans="2:38" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B22" s="51" t="s">
         <v>50</v>
       </c>
@@ -16468,7 +16886,7 @@
       </c>
       <c r="AH22" s="1"/>
     </row>
-    <row r="23" spans="2:38" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B23" s="53" t="s">
         <v>59</v>
       </c>
@@ -16544,7 +16962,7 @@
       </c>
       <c r="AH23" s="1"/>
     </row>
-    <row r="24" spans="2:38" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B24" s="52" t="s">
         <v>60</v>
       </c>
@@ -16613,7 +17031,7 @@
       </c>
       <c r="AH24" s="1"/>
     </row>
-    <row r="25" spans="2:38" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B25" s="51" t="s">
         <v>61</v>
       </c>
@@ -16681,7 +17099,7 @@
       </c>
       <c r="AH25" s="1"/>
     </row>
-    <row r="26" spans="2:38" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B26" s="53" t="s">
         <v>62</v>
       </c>
@@ -16749,7 +17167,7 @@
       </c>
       <c r="AH26" s="1"/>
     </row>
-    <row r="27" spans="2:38" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B27" s="30" t="s">
         <v>63</v>
       </c>
@@ -16817,7 +17235,7 @@
       </c>
       <c r="AH27" s="1"/>
     </row>
-    <row r="28" spans="2:38" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B28" s="30" t="s">
         <v>84</v>
       </c>
@@ -16893,7 +17311,7 @@
       </c>
       <c r="AH28" s="1"/>
     </row>
-    <row r="29" spans="2:38" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B29" s="30" t="s">
         <v>51</v>
       </c>
@@ -16961,7 +17379,7 @@
       </c>
       <c r="AH29" s="1"/>
     </row>
-    <row r="30" spans="2:38" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="30" spans="2:38" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="11" t="s">
         <v>55</v>
       </c>
@@ -17079,7 +17497,7 @@
       </c>
       <c r="AE30" s="1"/>
     </row>
-    <row r="31" spans="2:38" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="2:38" x14ac:dyDescent="0.3">
       <c r="D31" s="56">
         <f>(D30-C30)/C30</f>
         <v>-0.44444444444444442</v>
@@ -17129,41 +17547,41 @@
         <v>-0.18599118942731277</v>
       </c>
     </row>
-    <row r="32" spans="2:38" x14ac:dyDescent="0.55000000000000004">
-      <c r="F32" s="64" t="s">
+    <row r="32" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="F32" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="G32" s="65"/>
-      <c r="H32" s="66"/>
-      <c r="I32" s="62">
+      <c r="G32" s="66"/>
+      <c r="H32" s="67"/>
+      <c r="I32" s="63">
         <f>C30+E30+G30+I30+K30+M30+O30+Q30+S30+U30+AA30+W30+Y30</f>
         <v>2648</v>
       </c>
-      <c r="J32" s="63"/>
-    </row>
-    <row r="33" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="J32" s="64"/>
+    </row>
+    <row r="33" spans="3:25" x14ac:dyDescent="0.3">
       <c r="G33" s="70" t="s">
         <v>57</v>
       </c>
       <c r="H33" s="70"/>
-      <c r="I33" s="62">
+      <c r="I33" s="63">
         <f>+D30+F30+H30+J30+L30+N30+P30+R30+T30+V30+AB30+X30+Z30</f>
         <v>1694.2299999999998</v>
       </c>
-      <c r="J33" s="63"/>
-    </row>
-    <row r="34" spans="3:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="I34" s="62">
+      <c r="J33" s="64"/>
+    </row>
+    <row r="34" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="I34" s="63">
         <f>I33-I32</f>
         <v>-953.77000000000021</v>
       </c>
-      <c r="J34" s="63"/>
+      <c r="J34" s="64"/>
       <c r="Y34">
         <f>2167+183+5*10</f>
         <v>2400</v>
       </c>
     </row>
-    <row r="35" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C35" s="36">
         <f>C30+E30+G30+I30</f>
         <v>901</v>
@@ -17206,7 +17624,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C36" s="36"/>
       <c r="D36" s="34">
         <f>(D35-C35)/C35</f>
@@ -17227,7 +17645,7 @@
       <c r="Q36" s="41"/>
       <c r="X36" s="55"/>
     </row>
-    <row r="37" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="3:25" x14ac:dyDescent="0.3">
       <c r="G37" t="s">
         <v>58</v>
       </c>
@@ -17235,22 +17653,22 @@
         <v>2400.0500000000002</v>
       </c>
     </row>
-    <row r="39" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="3:25" x14ac:dyDescent="0.3">
       <c r="G39" s="42" t="s">
         <v>64</v>
       </c>
       <c r="H39" s="42"/>
-      <c r="I39" s="72">
+      <c r="I39" s="71">
         <f>I37+I34</f>
         <v>1446.28</v>
       </c>
-      <c r="J39" s="72"/>
+      <c r="J39" s="71"/>
       <c r="M39" s="33"/>
     </row>
-    <row r="41" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="3:25" x14ac:dyDescent="0.3">
       <c r="X41" s="55"/>
     </row>
-    <row r="43" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C43" s="1">
         <f>C30+E30+G30+I30</f>
         <v>901</v>
@@ -17276,7 +17694,7 @@
         <v>403.26</v>
       </c>
     </row>
-    <row r="44" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="3:25" x14ac:dyDescent="0.3">
       <c r="D44" s="1">
         <f>D43-C43</f>
         <v>-592.65</v>
@@ -17290,12 +17708,12 @@
         <v>-246.74</v>
       </c>
     </row>
-    <row r="46" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="3:25" x14ac:dyDescent="0.3">
       <c r="V46" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="47" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="3:25" x14ac:dyDescent="0.3">
       <c r="D47" t="s">
         <v>88</v>
       </c>
@@ -17309,7 +17727,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="3:25" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="3:25" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
         <v>90</v>
       </c>
@@ -17329,7 +17747,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
         <v>92</v>
       </c>
@@ -17350,7 +17768,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
         <v>12</v>
       </c>
@@ -17371,7 +17789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
         <v>94</v>
       </c>
@@ -17392,7 +17810,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
         <v>95</v>
       </c>
@@ -17413,7 +17831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
         <v>93</v>
       </c>
@@ -17434,7 +17852,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
         <v>97</v>
       </c>
@@ -17455,7 +17873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
         <v>98</v>
       </c>
@@ -17476,7 +17894,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D56" t="s">
         <v>89</v>
       </c>
@@ -17497,7 +17915,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
         <v>96</v>
       </c>
@@ -17518,7 +17936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
         <v>120</v>
       </c>
@@ -17539,7 +17957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
         <v>121</v>
       </c>
@@ -17561,7 +17979,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="60" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
         <v>9</v>
       </c>
@@ -17576,7 +17994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="4:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
         <v>99</v>
       </c>
@@ -17594,6 +18012,19 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="O2:P2"/>
     <mergeCell ref="W1:X1"/>
     <mergeCell ref="W2:X2"/>
     <mergeCell ref="Y2:Z2"/>
@@ -17602,37 +18033,24 @@
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="U2:V2"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="AA2:AB2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="51" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="63" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9A81C0-C60A-48E0-A96A-1599E0795A8C}">
   <dimension ref="A1:G52"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="13.26171875" customWidth="1"/>
-    <col min="3" max="3" width="20.41796875" customWidth="1"/>
-    <col min="4" max="4" width="39.26171875" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" customWidth="1"/>
+    <col min="4" max="4" width="39.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>122</v>
       </c>
@@ -17657,7 +18075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>97</v>
       </c>
@@ -17682,7 +18100,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>93</v>
       </c>
@@ -17707,7 +18125,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>97</v>
       </c>
@@ -17732,7 +18150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>96</v>
       </c>
@@ -17757,7 +18175,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -17782,7 +18200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>89</v>
       </c>
@@ -17807,7 +18225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>89</v>
       </c>
@@ -17832,7 +18250,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -17857,7 +18275,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>97</v>
       </c>
@@ -17882,7 +18300,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>97</v>
       </c>
@@ -17907,7 +18325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -17932,7 +18350,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -17950,7 +18368,7 @@
         <v>7128.45</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>89</v>
       </c>
@@ -17964,7 +18382,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -17978,7 +18396,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>120</v>
       </c>
@@ -17992,7 +18410,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>93</v>
       </c>
@@ -18006,7 +18424,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>95</v>
       </c>
@@ -18020,7 +18438,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -18034,7 +18452,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>96</v>
       </c>
@@ -18048,7 +18466,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>89</v>
       </c>
@@ -18062,7 +18480,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>92</v>
       </c>
@@ -18076,7 +18494,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -18090,7 +18508,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>98</v>
       </c>
@@ -18104,7 +18522,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>97</v>
       </c>
@@ -18118,7 +18536,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>94</v>
       </c>
@@ -18132,7 +18550,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>89</v>
       </c>
@@ -18146,7 +18564,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>94</v>
       </c>
@@ -18160,7 +18578,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>120</v>
       </c>
@@ -18174,7 +18592,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>121</v>
       </c>
@@ -18188,7 +18606,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -18202,7 +18620,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>94</v>
       </c>
@@ -18216,7 +18634,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>92</v>
       </c>
@@ -18230,7 +18648,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>98</v>
       </c>
@@ -18244,7 +18662,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>89</v>
       </c>
@@ -18258,7 +18676,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>93</v>
       </c>
@@ -18272,7 +18690,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>120</v>
       </c>
@@ -18286,7 +18704,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>94</v>
       </c>
@@ -18300,7 +18718,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>12</v>
       </c>
@@ -18314,7 +18732,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -18328,7 +18746,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>11</v>
       </c>
@@ -18342,7 +18760,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -18356,7 +18774,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>94</v>
       </c>
@@ -18370,7 +18788,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>12</v>
       </c>
@@ -18384,7 +18802,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>93</v>
       </c>
@@ -18398,7 +18816,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>93</v>
       </c>
@@ -18412,7 +18830,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>97</v>
       </c>
@@ -18426,7 +18844,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -18440,7 +18858,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>12</v>
       </c>
@@ -18454,7 +18872,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>89</v>
       </c>
@@ -18468,7 +18886,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>93</v>
       </c>
@@ -18482,7 +18900,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>9</v>
       </c>
@@ -18498,10 +18916,2469 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DAED5EC-BAE9-465F-8060-DBBAE52AB8C8}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:AL62"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="1.6640625" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" customWidth="1"/>
+    <col min="6" max="7" width="7.88671875" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" customWidth="1"/>
+    <col min="9" max="19" width="7.88671875" customWidth="1"/>
+    <col min="20" max="20" width="8.5546875" customWidth="1"/>
+    <col min="21" max="23" width="7.88671875" customWidth="1"/>
+    <col min="24" max="24" width="8.88671875" customWidth="1"/>
+    <col min="25" max="25" width="9.44140625" customWidth="1"/>
+    <col min="26" max="26" width="9.6640625" customWidth="1"/>
+    <col min="29" max="29" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.109375" customWidth="1"/>
+    <col min="34" max="34" width="11" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.109375" customWidth="1"/>
+    <col min="38" max="38" width="10.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:38" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="W1" s="73"/>
+      <c r="X1" s="74"/>
+    </row>
+    <row r="2" spans="2:38" ht="18" x14ac:dyDescent="0.35">
+      <c r="C2" s="62" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="62"/>
+      <c r="E2" s="72" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="68"/>
+      <c r="G2" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62" t="s">
+        <v>115</v>
+      </c>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="L2" s="62"/>
+      <c r="M2" s="72" t="s">
+        <v>103</v>
+      </c>
+      <c r="N2" s="68"/>
+      <c r="O2" s="62" t="s">
+        <v>106</v>
+      </c>
+      <c r="P2" s="62"/>
+      <c r="Q2" s="62" t="s">
+        <v>107</v>
+      </c>
+      <c r="R2" s="62"/>
+      <c r="S2" s="62" t="s">
+        <v>100</v>
+      </c>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62" t="s">
+        <v>108</v>
+      </c>
+      <c r="V2" s="72"/>
+      <c r="W2" s="75" t="s">
+        <v>102</v>
+      </c>
+      <c r="X2" s="76"/>
+      <c r="Y2" s="75" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z2" s="76"/>
+      <c r="AA2" s="80" t="s">
+        <v>180</v>
+      </c>
+      <c r="AB2" s="81"/>
+      <c r="AC2" s="78" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD2" s="79"/>
+      <c r="AE2" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF2" s="62"/>
+    </row>
+    <row r="3" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B3" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="P3" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="T3" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="U3" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="V3" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="W3" s="57" t="s">
+        <v>30</v>
+      </c>
+      <c r="X3" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y3" s="57" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z3" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA3" s="57" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB3" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC3" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD3" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE3" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF3" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG3" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH3" s="25"/>
+    </row>
+    <row r="4" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B4" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="12"/>
+      <c r="V4" s="19"/>
+      <c r="W4" s="12"/>
+      <c r="X4" s="19"/>
+      <c r="Y4" s="12"/>
+      <c r="Z4" s="19"/>
+      <c r="AA4" s="12"/>
+      <c r="AB4" s="19"/>
+      <c r="AC4" s="17">
+        <f>U4+S4+Q4+O4+M4+K4+I4+G4+E4+C4+W4+Y4</f>
+        <v>0</v>
+      </c>
+      <c r="AD4" s="48">
+        <f t="shared" ref="AD4" si="0">V4+T4+R4+P4+N4+L4+J4+H4+F4+D4</f>
+        <v>0</v>
+      </c>
+      <c r="AE4" s="1">
+        <f>AC4</f>
+        <v>0</v>
+      </c>
+      <c r="AF4" s="1">
+        <f>AD4</f>
+        <v>0</v>
+      </c>
+      <c r="AG4" s="1">
+        <f>AF4-AE4</f>
+        <v>0</v>
+      </c>
+      <c r="AH4" s="1"/>
+    </row>
+    <row r="5" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B5" s="54" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="17"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="15"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="15"/>
+      <c r="Z5" s="20"/>
+      <c r="AA5" s="15"/>
+      <c r="AB5" s="20"/>
+      <c r="AC5" s="17">
+        <f>U5+S5+Q5+O5+M5+K5+I5+G5+E5+C5+W5+Y5</f>
+        <v>0</v>
+      </c>
+      <c r="AD5" s="35">
+        <f>V5+T5+R5+P5+N5+L5+J5+H5+F5+D5+X5+Z5</f>
+        <v>0</v>
+      </c>
+      <c r="AE5" s="1">
+        <f>AE4+AC5</f>
+        <v>0</v>
+      </c>
+      <c r="AF5" s="1">
+        <f>AF4+AD5</f>
+        <v>0</v>
+      </c>
+      <c r="AG5" s="1">
+        <f t="shared" ref="AG5:AG29" si="1">AF5-AE5</f>
+        <v>0</v>
+      </c>
+      <c r="AH5" s="1"/>
+    </row>
+    <row r="6" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B6" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="16"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="16"/>
+      <c r="U6" s="15"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="15"/>
+      <c r="X6" s="20"/>
+      <c r="Y6" s="15"/>
+      <c r="Z6" s="20"/>
+      <c r="AA6" s="15"/>
+      <c r="AB6" s="20"/>
+      <c r="AC6" s="17">
+        <f t="shared" ref="AC6:AD27" si="2">U6+S6+Q6+O6+M6+K6+I6+G6+E6+C6+W6+Y6</f>
+        <v>0</v>
+      </c>
+      <c r="AD6" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE6" s="1">
+        <f t="shared" ref="AE6:AF21" si="3">AE5+AC6</f>
+        <v>0</v>
+      </c>
+      <c r="AF6" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG6" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6" s="1"/>
+      <c r="AI6" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ6" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="AK6" s="43" t="s">
+        <v>69</v>
+      </c>
+      <c r="AL6" s="43" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B7" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="16"/>
+      <c r="U7" s="15"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="15"/>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="15"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="15"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD7" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE7" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF7" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG7" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH7" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI7" s="44">
+        <f>+E30+'Punters 2024'!AE7</f>
+        <v>1208</v>
+      </c>
+      <c r="AJ7" s="44">
+        <f>+F30+'Punters 2024'!AF7</f>
+        <v>542.6</v>
+      </c>
+      <c r="AK7" s="49">
+        <f>+AJ7-AI7</f>
+        <v>-665.4</v>
+      </c>
+      <c r="AL7" s="47">
+        <f>(AJ7-AI7)/AI7</f>
+        <v>-0.55082781456953644</v>
+      </c>
+    </row>
+    <row r="8" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B8" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="15"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="15"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="15"/>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="15"/>
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD8" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE8" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF8" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG8" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH8" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI8" s="44">
+        <f>+K30+'Punters 2024'!AE8</f>
+        <v>1388</v>
+      </c>
+      <c r="AJ8" s="44">
+        <f>+L30+'Punters 2024'!AF8</f>
+        <v>1138.52</v>
+      </c>
+      <c r="AK8" s="50">
+        <f t="shared" ref="AK8:AK18" si="4">+AJ8-AI8</f>
+        <v>-249.48000000000002</v>
+      </c>
+      <c r="AL8" s="47">
+        <f t="shared" ref="AL8:AL18" si="5">(AJ8-AI8)/AI8</f>
+        <v>-0.17974063400576371</v>
+      </c>
+    </row>
+    <row r="9" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B9" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="15"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="15"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="15"/>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="15"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD9" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE9" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF9" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG9" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH9" s="44" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI9" s="44">
+        <f>+Y30+'Punters 2024'!AE9</f>
+        <v>1366.48</v>
+      </c>
+      <c r="AJ9" s="44">
+        <f>Z30+'Punters 2024'!AF9</f>
+        <v>1093.9000000000001</v>
+      </c>
+      <c r="AK9" s="50">
+        <f t="shared" si="4"/>
+        <v>-272.57999999999993</v>
+      </c>
+      <c r="AL9" s="47">
+        <f t="shared" si="5"/>
+        <v>-0.19947602599379421</v>
+      </c>
+    </row>
+    <row r="10" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B10" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="15"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="15"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD10" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE10" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF10" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG10" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH10" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI10" s="44">
+        <f>+S30+'Punters 2024'!AE10</f>
+        <v>1364.9</v>
+      </c>
+      <c r="AJ10" s="44">
+        <f>+T30+'Punters 2024'!AF10</f>
+        <v>1516.4499999999998</v>
+      </c>
+      <c r="AK10" s="50">
+        <f t="shared" si="4"/>
+        <v>151.54999999999973</v>
+      </c>
+      <c r="AL10" s="45">
+        <f t="shared" si="5"/>
+        <v>0.11103377536815863</v>
+      </c>
+    </row>
+    <row r="11" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B11" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="16"/>
+      <c r="U11" s="15"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="15"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="15"/>
+      <c r="Z11" s="20"/>
+      <c r="AA11" s="15"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE11" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG11" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH11" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI11" s="44">
+        <f>+M30+'Punters 2024'!AE11</f>
+        <v>1073</v>
+      </c>
+      <c r="AJ11" s="44">
+        <f>+N30+'Punters 2024'!AF11</f>
+        <v>98.25</v>
+      </c>
+      <c r="AK11" s="49">
+        <f t="shared" si="4"/>
+        <v>-974.75</v>
+      </c>
+      <c r="AL11" s="47">
+        <f t="shared" si="5"/>
+        <v>-0.9084342963653308</v>
+      </c>
+    </row>
+    <row r="12" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B12" s="52" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="15"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="15"/>
+      <c r="X12" s="20"/>
+      <c r="Y12" s="15"/>
+      <c r="Z12" s="20"/>
+      <c r="AA12" s="15"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD12" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE12" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF12" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG12" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH12" s="44" t="s">
+        <v>76</v>
+      </c>
+      <c r="AI12" s="44">
+        <f>+U30+'Punters 2024'!AE12</f>
+        <v>1384.96</v>
+      </c>
+      <c r="AJ12" s="44">
+        <f>+V30+'Punters 2024'!AF12</f>
+        <v>890.65999999999985</v>
+      </c>
+      <c r="AK12" s="49">
+        <f t="shared" si="4"/>
+        <v>-494.30000000000018</v>
+      </c>
+      <c r="AL12" s="47">
+        <f t="shared" si="5"/>
+        <v>-0.35690561460258791</v>
+      </c>
+    </row>
+    <row r="13" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B13" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="16"/>
+      <c r="U13" s="15"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="15"/>
+      <c r="X13" s="20"/>
+      <c r="Y13" s="15"/>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="15"/>
+      <c r="AB13" s="20"/>
+      <c r="AC13" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD13" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE13" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF13" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG13" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH13" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI13" s="44">
+        <f>+I30+'Punters 2024'!AE13</f>
+        <v>1346.3400000000001</v>
+      </c>
+      <c r="AJ13" s="44">
+        <f>+J30+'Punters 2024'!AF13</f>
+        <v>626.24</v>
+      </c>
+      <c r="AK13" s="49">
+        <f t="shared" si="4"/>
+        <v>-720.10000000000014</v>
+      </c>
+      <c r="AL13" s="47">
+        <f t="shared" si="5"/>
+        <v>-0.5348574654247813</v>
+      </c>
+    </row>
+    <row r="14" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B14" s="53" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="16"/>
+      <c r="U14" s="15"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="15"/>
+      <c r="X14" s="20"/>
+      <c r="Y14" s="15"/>
+      <c r="Z14" s="20"/>
+      <c r="AA14" s="15"/>
+      <c r="AB14" s="20"/>
+      <c r="AC14" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD14" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE14" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF14" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG14" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH14" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI14" s="44">
+        <f>+Q30+'Punters 2024'!AE14</f>
+        <v>1353</v>
+      </c>
+      <c r="AJ14" s="44">
+        <f>+R30+'Punters 2024'!AF14</f>
+        <v>637.47</v>
+      </c>
+      <c r="AK14" s="49">
+        <f t="shared" si="4"/>
+        <v>-715.53</v>
+      </c>
+      <c r="AL14" s="47">
+        <f t="shared" si="5"/>
+        <v>-0.52884700665188467</v>
+      </c>
+    </row>
+    <row r="15" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B15" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="15"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="15"/>
+      <c r="X15" s="20"/>
+      <c r="Y15" s="15"/>
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="15"/>
+      <c r="AB15" s="20"/>
+      <c r="AC15" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD15" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE15" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF15" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG15" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH15" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI15" s="44">
+        <f>+O30+'Punters 2024'!AE15</f>
+        <v>1362.7</v>
+      </c>
+      <c r="AJ15" s="44">
+        <f>+P30+'Punters 2024'!AF15</f>
+        <v>1696.09</v>
+      </c>
+      <c r="AK15" s="50">
+        <f t="shared" si="4"/>
+        <v>333.38999999999987</v>
+      </c>
+      <c r="AL15" s="45">
+        <f t="shared" si="5"/>
+        <v>0.24465399574374394</v>
+      </c>
+    </row>
+    <row r="16" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B16" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="15"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="16"/>
+      <c r="U16" s="15"/>
+      <c r="V16" s="20"/>
+      <c r="W16" s="15"/>
+      <c r="X16" s="20"/>
+      <c r="Y16" s="15"/>
+      <c r="Z16" s="20"/>
+      <c r="AA16" s="15"/>
+      <c r="AB16" s="20"/>
+      <c r="AC16" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE16" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF16" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG16" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH16" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI16" s="44">
+        <f>+W30+'Punters 2024'!AE16</f>
+        <v>620</v>
+      </c>
+      <c r="AJ16" s="44">
+        <f>+X30+'Punters 2024'!AF16</f>
+        <v>151.25</v>
+      </c>
+      <c r="AK16" s="49">
+        <f t="shared" si="4"/>
+        <v>-468.75</v>
+      </c>
+      <c r="AL16" s="47">
+        <f t="shared" si="5"/>
+        <v>-0.75604838709677424</v>
+      </c>
+    </row>
+    <row r="17" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B17" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="15"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="16"/>
+      <c r="U17" s="15"/>
+      <c r="V17" s="20"/>
+      <c r="W17" s="15"/>
+      <c r="X17" s="20"/>
+      <c r="Y17" s="15"/>
+      <c r="Z17" s="20"/>
+      <c r="AA17" s="15"/>
+      <c r="AB17" s="20"/>
+      <c r="AC17" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD17" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE17" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF17" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG17" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH17" s="44" t="s">
+        <v>116</v>
+      </c>
+      <c r="AI17" s="44">
+        <f>+C30</f>
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="44">
+        <f>+D30</f>
+        <v>0</v>
+      </c>
+      <c r="AK17" s="49">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AL17" s="47" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B18" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="15"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="16"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="16"/>
+      <c r="U18" s="15"/>
+      <c r="V18" s="20"/>
+      <c r="W18" s="15"/>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="15"/>
+      <c r="Z18" s="20"/>
+      <c r="AA18" s="15"/>
+      <c r="AB18" s="20"/>
+      <c r="AC18" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD18" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE18" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG18" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH18" s="44" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI18" s="44">
+        <f>+G30</f>
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="44">
+        <f>+H30</f>
+        <v>0</v>
+      </c>
+      <c r="AK18" s="49">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AL18" s="47" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B19" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="16"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="16"/>
+      <c r="U19" s="15"/>
+      <c r="V19" s="20"/>
+      <c r="W19" s="15"/>
+      <c r="X19" s="20"/>
+      <c r="Y19" s="15"/>
+      <c r="Z19" s="20"/>
+      <c r="AA19" s="15"/>
+      <c r="AB19" s="20"/>
+      <c r="AC19" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD19" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE19" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF19" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG19" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH19" s="1"/>
+    </row>
+    <row r="20" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B20" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="15"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="16"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="16"/>
+      <c r="U20" s="15"/>
+      <c r="V20" s="20"/>
+      <c r="W20" s="15"/>
+      <c r="X20" s="20"/>
+      <c r="Y20" s="15"/>
+      <c r="Z20" s="20"/>
+      <c r="AA20" s="15"/>
+      <c r="AB20" s="20"/>
+      <c r="AC20" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD20" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE20" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF20" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG20" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH20" s="1"/>
+    </row>
+    <row r="21" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B21" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="15"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="16"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="16"/>
+      <c r="U21" s="15"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="15"/>
+      <c r="X21" s="20"/>
+      <c r="Y21" s="15"/>
+      <c r="Z21" s="20"/>
+      <c r="AA21" s="15"/>
+      <c r="AB21" s="20"/>
+      <c r="AC21" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD21" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE21" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF21" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG21" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH21" s="1"/>
+    </row>
+    <row r="22" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B22" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="15"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="16"/>
+      <c r="U22" s="15"/>
+      <c r="V22" s="20"/>
+      <c r="W22" s="15"/>
+      <c r="X22" s="20"/>
+      <c r="Y22" s="15"/>
+      <c r="Z22" s="20"/>
+      <c r="AA22" s="15"/>
+      <c r="AB22" s="20"/>
+      <c r="AC22" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD22" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE22" s="1">
+        <f t="shared" ref="AE22:AF29" si="6">AE21+AC22</f>
+        <v>0</v>
+      </c>
+      <c r="AF22" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AG22" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH22" s="1"/>
+    </row>
+    <row r="23" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B23" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="15"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="16"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="16"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="16"/>
+      <c r="S23" s="17"/>
+      <c r="T23" s="16"/>
+      <c r="U23" s="15"/>
+      <c r="V23" s="20"/>
+      <c r="W23" s="15"/>
+      <c r="X23" s="20"/>
+      <c r="Y23" s="15"/>
+      <c r="Z23" s="20"/>
+      <c r="AA23" s="15"/>
+      <c r="AB23" s="20"/>
+      <c r="AC23" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD23" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE23" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AF23" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AG23" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH23" s="1"/>
+    </row>
+    <row r="24" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B24" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="15"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="17"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="16"/>
+      <c r="S24" s="17"/>
+      <c r="T24" s="16"/>
+      <c r="U24" s="15"/>
+      <c r="V24" s="20"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="15"/>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="15"/>
+      <c r="AB24" s="20"/>
+      <c r="AC24" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD24" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE24" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AF24" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AG24" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH24" s="1"/>
+    </row>
+    <row r="25" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B25" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="15"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="16"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="16"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="16"/>
+      <c r="S25" s="17"/>
+      <c r="T25" s="16"/>
+      <c r="U25" s="15"/>
+      <c r="V25" s="20"/>
+      <c r="W25" s="15"/>
+      <c r="X25" s="20"/>
+      <c r="Y25" s="15"/>
+      <c r="Z25" s="20"/>
+      <c r="AA25" s="15"/>
+      <c r="AB25" s="20"/>
+      <c r="AC25" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD25" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE25" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AF25" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AG25" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH25" s="1"/>
+    </row>
+    <row r="26" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B26" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="15"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="16"/>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="16"/>
+      <c r="S26" s="17"/>
+      <c r="T26" s="16"/>
+      <c r="U26" s="15"/>
+      <c r="V26" s="20"/>
+      <c r="W26" s="15"/>
+      <c r="X26" s="20"/>
+      <c r="Y26" s="15"/>
+      <c r="Z26" s="20"/>
+      <c r="AA26" s="15"/>
+      <c r="AB26" s="20"/>
+      <c r="AC26" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD26" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE26" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AF26" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AG26" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH26" s="1"/>
+    </row>
+    <row r="27" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B27" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="15"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="17"/>
+      <c r="N27" s="16"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="16"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="16"/>
+      <c r="S27" s="17"/>
+      <c r="T27" s="16"/>
+      <c r="U27" s="15"/>
+      <c r="V27" s="20"/>
+      <c r="W27" s="15"/>
+      <c r="X27" s="20"/>
+      <c r="Y27" s="15"/>
+      <c r="Z27" s="20"/>
+      <c r="AA27" s="15"/>
+      <c r="AB27" s="20"/>
+      <c r="AC27" s="17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD27" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE27" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AF27" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AG27" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH27" s="1"/>
+    </row>
+    <row r="28" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B28" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" s="15"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="17"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="16"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="16"/>
+      <c r="U28" s="15"/>
+      <c r="V28" s="20"/>
+      <c r="W28" s="15"/>
+      <c r="X28" s="20"/>
+      <c r="Y28" s="15"/>
+      <c r="Z28" s="20"/>
+      <c r="AA28" s="15"/>
+      <c r="AB28" s="20"/>
+      <c r="AC28" s="17">
+        <f t="shared" ref="AC28:AD29" si="7">U28+S28+Q28+O28+M28+K28+I28+G28+E28+C28+W28+Y28</f>
+        <v>0</v>
+      </c>
+      <c r="AD28" s="35">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AE28" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AF28" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AG28" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH28" s="1"/>
+    </row>
+    <row r="29" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B29" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="15"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="16"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="16"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="16"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="16"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="16"/>
+      <c r="U29" s="15"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="15"/>
+      <c r="X29" s="20"/>
+      <c r="Y29" s="15"/>
+      <c r="Z29" s="20"/>
+      <c r="AA29" s="15"/>
+      <c r="AB29" s="20"/>
+      <c r="AC29" s="17">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AD29" s="35">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AE29" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AF29" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AG29" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH29" s="1"/>
+    </row>
+    <row r="30" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B30" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="18">
+        <f t="shared" ref="C30:AD30" si="8">SUM(C4:C29)</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="E30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="N30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="O30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="P30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="R30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="18">
+        <f>SUM(T4:T29)</f>
+        <v>0</v>
+      </c>
+      <c r="U30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="21">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X30" s="21">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Z30" s="21">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AA30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AB30" s="21">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AC30" s="29">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AD30" s="18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AE30" s="1"/>
+    </row>
+    <row r="31" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="D31" s="56" t="e">
+        <f>(D30-C30)/C30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F31" s="34" t="e">
+        <f>(F30-E30)/E30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H31" s="34" t="e">
+        <f>(H30-G30)/G30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J31" s="34" t="e">
+        <f>(J30-I30)/I30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L31" s="28" t="e">
+        <f>(L30-K30)/K30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N31" s="28" t="e">
+        <f>(N30-M30)/M30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P31" s="28" t="e">
+        <f>(P30-O30)/O30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R31" s="28" t="e">
+        <f>(R30-Q30)/Q30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T31" s="22" t="e">
+        <f>(T30-S30)/S30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V31" s="28" t="e">
+        <f>(V30-U30)/U30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X31" s="28" t="e">
+        <f>(X30-W30)/W30</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z31" s="28" t="e">
+        <f>(Z30-Y30)/Y30</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="32" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="F32" s="65" t="s">
+        <v>56</v>
+      </c>
+      <c r="G32" s="66"/>
+      <c r="H32" s="67"/>
+      <c r="I32" s="63">
+        <f>C30+E30+G30+I30+K30+M30+O30+Q30+S30+U30+AA30+W30+Y30</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="64"/>
+    </row>
+    <row r="33" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="G33" s="70" t="s">
+        <v>57</v>
+      </c>
+      <c r="H33" s="70"/>
+      <c r="I33" s="63">
+        <f>+D30+F30+H30+J30+L30+N30+P30+R30+T30+V30+AB30+X30+Z30</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="64"/>
+    </row>
+    <row r="34" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="I34" s="63">
+        <f>I33-I32</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="64"/>
+      <c r="Y34">
+        <f>2167+183+5*10</f>
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="35" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C35" s="36">
+        <f>C30+E30+G30+I30</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="36">
+        <f>D30+F30+H30+J30</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="37">
+        <f>D35-C35</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="38">
+        <f>O30+K30+M30+Q30</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="38">
+        <f>P30+L30+N30</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="39">
+        <f>J35-I35</f>
+        <v>0</v>
+      </c>
+      <c r="O35" s="40">
+        <f>U30+W30+Y30+S30</f>
+        <v>0</v>
+      </c>
+      <c r="P35" s="40">
+        <f>V30+X30+T30+Z30</f>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="41">
+        <f>P35-O35</f>
+        <v>0</v>
+      </c>
+      <c r="X35" s="55"/>
+      <c r="Y35">
+        <f>15*10</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="36" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C36" s="36"/>
+      <c r="D36" s="34" t="e">
+        <f>(D35-C35)/C35</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E36" s="37"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="34" t="e">
+        <f>(J35-I35)/I35</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K36" s="39"/>
+      <c r="O36" s="40"/>
+      <c r="P36" s="34" t="e">
+        <f>(P35-O35)/O35</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q36" s="41"/>
+      <c r="X36" s="55"/>
+    </row>
+    <row r="37" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="G37" t="s">
+        <v>58</v>
+      </c>
+      <c r="I37">
+        <v>2400.0500000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="G39" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="H39" s="42"/>
+      <c r="I39" s="71">
+        <f>I37+I34</f>
+        <v>2400.0500000000002</v>
+      </c>
+      <c r="J39" s="71"/>
+      <c r="M39" s="33"/>
+    </row>
+    <row r="41" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="X41" s="55"/>
+    </row>
+    <row r="43" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C43" s="1">
+        <f>C30+E30+G30+I30</f>
+        <v>0</v>
+      </c>
+      <c r="D43" s="1">
+        <f>D30+F30+H30+J30</f>
+        <v>0</v>
+      </c>
+      <c r="I43" s="1">
+        <f>O30+K30+M30</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="1">
+        <f>P30+L30+N30</f>
+        <v>0</v>
+      </c>
+      <c r="O43" s="1">
+        <f>U30+Q30+S30</f>
+        <v>0</v>
+      </c>
+      <c r="P43" s="1">
+        <f>V30+R30+T30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="D44" s="1">
+        <f>D43-C43</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="33">
+        <f>J43-I43</f>
+        <v>0</v>
+      </c>
+      <c r="P44" s="33">
+        <f>P43-O43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="V46" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="47" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="D47" t="s">
+        <v>88</v>
+      </c>
+      <c r="J47" t="s">
+        <v>119</v>
+      </c>
+      <c r="V47" t="s">
+        <v>89</v>
+      </c>
+      <c r="W47">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="D48" t="s">
+        <v>90</v>
+      </c>
+      <c r="E48" t="s">
+        <v>91</v>
+      </c>
+      <c r="J48" t="s">
+        <v>90</v>
+      </c>
+      <c r="K48" t="s">
+        <v>112</v>
+      </c>
+      <c r="V48" t="s">
+        <v>12</v>
+      </c>
+      <c r="W48">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D49" t="s">
+        <v>92</v>
+      </c>
+      <c r="E49" s="1">
+        <f>SUM(V30)</f>
+        <v>0</v>
+      </c>
+      <c r="J49" t="s">
+        <v>92</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="V49" t="s">
+        <v>93</v>
+      </c>
+      <c r="W49">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" s="1">
+        <f>SUM(L30)</f>
+        <v>0</v>
+      </c>
+      <c r="J50" t="s">
+        <v>12</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="V50" t="s">
+        <v>92</v>
+      </c>
+      <c r="W50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D51" t="s">
+        <v>94</v>
+      </c>
+      <c r="E51" s="1">
+        <f>SUM(T30)</f>
+        <v>0</v>
+      </c>
+      <c r="J51" t="s">
+        <v>94</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="V51" t="s">
+        <v>9</v>
+      </c>
+      <c r="W51">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D52" t="s">
+        <v>95</v>
+      </c>
+      <c r="E52" s="1">
+        <f>SUM(F30)</f>
+        <v>0</v>
+      </c>
+      <c r="J52" t="s">
+        <v>95</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="V52" t="s">
+        <v>11</v>
+      </c>
+      <c r="W52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D53" t="s">
+        <v>93</v>
+      </c>
+      <c r="E53" s="1">
+        <f>SUM(J30)</f>
+        <v>0</v>
+      </c>
+      <c r="J53" t="s">
+        <v>93</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="V53" t="s">
+        <v>96</v>
+      </c>
+      <c r="W53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D54" t="s">
+        <v>97</v>
+      </c>
+      <c r="E54" s="1">
+        <f>SUM(R30)</f>
+        <v>0</v>
+      </c>
+      <c r="J54" t="s">
+        <v>97</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="V54" t="s">
+        <v>98</v>
+      </c>
+      <c r="W54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D55" t="s">
+        <v>98</v>
+      </c>
+      <c r="E55" s="1">
+        <f>SUM(N30)</f>
+        <v>0</v>
+      </c>
+      <c r="J55" t="s">
+        <v>98</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="V55" t="s">
+        <v>97</v>
+      </c>
+      <c r="W55">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D56" t="s">
+        <v>89</v>
+      </c>
+      <c r="E56" s="1">
+        <f>SUM(X30)</f>
+        <v>0</v>
+      </c>
+      <c r="J56" t="s">
+        <v>89</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="V56" t="s">
+        <v>94</v>
+      </c>
+      <c r="W56">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D57" t="s">
+        <v>96</v>
+      </c>
+      <c r="E57" s="1">
+        <f>SUM(Z30)</f>
+        <v>0</v>
+      </c>
+      <c r="J57" t="s">
+        <v>96</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="V57" t="s">
+        <v>120</v>
+      </c>
+      <c r="W57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D58" t="s">
+        <v>120</v>
+      </c>
+      <c r="E58" s="1">
+        <f>SUM(H30)</f>
+        <v>0</v>
+      </c>
+      <c r="J58" t="s">
+        <v>120</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="V58" t="s">
+        <v>121</v>
+      </c>
+      <c r="W58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D59" t="s">
+        <v>121</v>
+      </c>
+      <c r="E59" s="1">
+        <f>SUM(D30)</f>
+        <v>0</v>
+      </c>
+      <c r="J59" t="s">
+        <v>121</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="V59" t="s">
+        <v>99</v>
+      </c>
+      <c r="W59">
+        <f>SUM(W47:W58)</f>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="60" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D60" t="s">
+        <v>181</v>
+      </c>
+      <c r="E60" s="1">
+        <f>SUM(D30)</f>
+        <v>0</v>
+      </c>
+      <c r="J60" t="s">
+        <v>181</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D61" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" s="1">
+        <f>SUM(P30)</f>
+        <v>0</v>
+      </c>
+      <c r="J61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="4:23" x14ac:dyDescent="0.3">
+      <c r="D62" t="s">
+        <v>99</v>
+      </c>
+      <c r="E62" s="1">
+        <f>SUM(E49:E61)</f>
+        <v>0</v>
+      </c>
+      <c r="J62" t="s">
+        <v>99</v>
+      </c>
+      <c r="K62">
+        <f>SUM(K49:K61)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AE2:AF2"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="Y2:Z2"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="8" scale="63" orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002D8393059904904F9DB82DE4B9AFABF6" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f7bafc8adbaca2e93ffc3a1da3fd32d5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3e1ffae5-f160-4019-9720-1b11bf1b81a3" xmlns:ns4="21753bd8-bffc-4cd2-a328-982ee854c895" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8f821f56a5d2247de677e71e73e5a99e" ns3:_="" ns4:_="">
     <xsd:import namespace="3e1ffae5-f160-4019-9720-1b11bf1b81a3"/>
@@ -18722,15 +21599,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -18740,6 +21608,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{948817D4-7F3F-493D-9D4C-B473DA03CC7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22BA772B-ABF0-4278-9CEF-D9160BBA9E07}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18758,14 +21634,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{948817D4-7F3F-493D-9D4C-B473DA03CC7E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4D7A62A-0CB5-48B0-A73A-0A91BCC8EAEF}">
   <ds:schemaRefs>
@@ -18778,6 +21646,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{0f7d30c2-cad0-4405-8153-25a6a3313da4}" enabled="1" method="Privileged" siteId="{6c637512-c417-4e78-9d62-b61258e4b619}" removed="0"/>
+  <clbl:label id="{0f7d30c2-cad0-4405-8153-25a6a3313da4}" enabled="1" method="Privileged" siteId="{6c637512-c417-4e78-9d62-b61258e4b619}" contentBits="0" removed="0"/>
 </clbl:labelList>
 </file>
--- a/public/Data/HEMANPUNTERS.xlsx
+++ b/public/Data/HEMANPUNTERS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bturnor\Repos\seeMore\public\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB900C8-65A0-49F6-8575-5F9E5CDEF57C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAEF0170-E0A5-46D2-B033-19D78F6C50F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="6" activeTab="8" xr2:uid="{525E8989-1938-4309-A4CF-8F1D15E362FB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="8" activeTab="8" xr2:uid="{525E8989-1938-4309-A4CF-8F1D15E362FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Punters club" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="191">
   <si>
     <t>HE_MAN PUNTERS 2019</t>
   </si>
@@ -612,7 +612,34 @@
     <t>A.BAXTER</t>
   </si>
   <si>
+    <t>Total bet and return for all seasons</t>
+  </si>
+  <si>
+    <t>adam</t>
+  </si>
+  <si>
+    <t>1 leg losses as at 09/03/2026</t>
+  </si>
+  <si>
+    <t>Strikes for 2026 Season at 09/03/2026</t>
+  </si>
+  <si>
     <t>Adam</t>
+  </si>
+  <si>
+    <t>Jamie Elliot needed 2 goals, got 1 goal 1 point</t>
+  </si>
+  <si>
+    <t>Worpel needed 20 or more, got 17</t>
+  </si>
+  <si>
+    <t>Max Verstappen needed to podium finish</t>
+  </si>
+  <si>
+    <t>Wanganeen-Milera needed 25 or more, got 19</t>
+  </si>
+  <si>
+    <t>Wanganeen-Milera Needed 30 or more, got 19</t>
   </si>
 </sst>
 </file>
@@ -790,7 +817,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -1230,12 +1257,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1358,6 +1409,11 @@
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1416,6 +1472,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4133,7 +4192,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
     <col min="3" max="3" width="20.44140625" customWidth="1"/>
-    <col min="4" max="4" width="39.33203125" customWidth="1"/>
+    <col min="4" max="4" width="41.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -4162,7 +4221,18 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C2" s="59"/>
+      <c r="A2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="60">
+        <v>10</v>
+      </c>
+      <c r="C2" s="59">
+        <v>358</v>
+      </c>
+      <c r="D2" t="s">
+        <v>186</v>
+      </c>
       <c r="E2" t="s">
         <v>12</v>
       </c>
@@ -4176,22 +4246,43 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C3" s="59"/>
+      <c r="A3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="60">
+        <v>10</v>
+      </c>
+      <c r="C3" s="59">
+        <v>95</v>
+      </c>
+      <c r="D3" t="s">
+        <v>187</v>
+      </c>
       <c r="E3" t="s">
         <v>94</v>
       </c>
-      <c r="F3" t="str">
+      <c r="F3">
         <f t="shared" si="0"/>
-        <v/>
+        <v>95</v>
       </c>
       <c r="G3">
         <f>COUNTIF(A1:A81, E3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="60"/>
-      <c r="C4" s="59"/>
+      <c r="A4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="60">
+        <v>10</v>
+      </c>
+      <c r="C4" s="59">
+        <v>61.8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>188</v>
+      </c>
       <c r="E4" t="s">
         <v>95</v>
       </c>
@@ -4200,13 +4291,23 @@
         <v/>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4" si="1">COUNTIF(A4:A84, E4)</f>
+        <f>COUNTIF(A2:A84, E4)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
+      <c r="A5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="59">
+        <v>10</v>
+      </c>
+      <c r="C5" s="59">
+        <v>95</v>
+      </c>
+      <c r="D5" t="s">
+        <v>189</v>
+      </c>
       <c r="E5" t="s">
         <v>93</v>
       </c>
@@ -4215,23 +4316,33 @@
         <v/>
       </c>
       <c r="G5">
-        <f t="shared" ref="G5" si="2">COUNTIF(A4:A84, E5)</f>
+        <f>COUNTIF(A2:A84, E5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
+      <c r="A6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="59">
+        <v>10</v>
+      </c>
+      <c r="C6" s="59">
+        <v>97.5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>190</v>
+      </c>
       <c r="E6" t="s">
         <v>97</v>
       </c>
-      <c r="F6" t="str">
+      <c r="F6">
         <f t="shared" si="0"/>
-        <v/>
+        <v>95</v>
       </c>
       <c r="G6">
-        <f t="shared" ref="G6" si="3">COUNTIF(A4:A84, E6)</f>
-        <v>0</v>
+        <f>COUNTIF(A2:A84, E6)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -4245,7 +4356,7 @@
         <v/>
       </c>
       <c r="G7">
-        <f t="shared" ref="G7" si="4">COUNTIF(A7:A87, E7)</f>
+        <f>COUNTIF(A2:A87, E7)</f>
         <v>0</v>
       </c>
     </row>
@@ -4255,13 +4366,13 @@
       <c r="E8" t="s">
         <v>89</v>
       </c>
-      <c r="F8" t="str">
+      <c r="F8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>97.5</v>
       </c>
       <c r="G8">
-        <f t="shared" ref="G8" si="5">COUNTIF(A7:A87, E8)</f>
-        <v>0</v>
+        <f>COUNTIF(A2:A87, E8)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -4275,7 +4386,7 @@
         <v/>
       </c>
       <c r="G9">
-        <f t="shared" ref="G9" si="6">COUNTIF(A7:A87, E9)</f>
+        <f>COUNTIF(A2:A87, E9)</f>
         <v>0</v>
       </c>
     </row>
@@ -4290,7 +4401,7 @@
         <v/>
       </c>
       <c r="G10">
-        <f t="shared" ref="G10" si="7">COUNTIF(A10:A90, E10)</f>
+        <f>COUNTIF(A2:A90, E10)</f>
         <v>0</v>
       </c>
     </row>
@@ -4300,13 +4411,13 @@
       <c r="E11" t="s">
         <v>121</v>
       </c>
-      <c r="F11" t="str">
+      <c r="F11">
         <f t="shared" si="0"/>
-        <v/>
+        <v>358</v>
       </c>
       <c r="G11">
-        <f>COUNTIF(A10:A90, E11)</f>
-        <v>0</v>
+        <f>COUNTIF(A2:A90, E11)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -4320,7 +4431,7 @@
         <v/>
       </c>
       <c r="G12">
-        <f t="shared" ref="G12" si="8">COUNTIF(A10:A90, E12)</f>
+        <f>COUNTIF(A2:A90, E12)</f>
         <v>0</v>
       </c>
     </row>
@@ -4328,15 +4439,15 @@
       <c r="B13" s="60"/>
       <c r="C13" s="59"/>
       <c r="E13" t="s">
-        <v>181</v>
-      </c>
-      <c r="F13" t="str">
+        <v>185</v>
+      </c>
+      <c r="F13">
         <f t="shared" si="0"/>
-        <v/>
+        <v>61.8</v>
       </c>
       <c r="G13">
         <f>COUNTIF(A2:A100, E13)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -4344,7 +4455,11 @@
       <c r="C14" s="59"/>
       <c r="F14" s="61">
         <f>SUM(F1:F13)</f>
-        <v>0</v>
+        <v>707.3</v>
+      </c>
+      <c r="G14">
+        <f>SUM(G1:G13)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -4519,50 +4634,50 @@
   <sheetData>
     <row r="1" spans="2:27" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:27" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62" t="s">
+      <c r="D2" s="67"/>
+      <c r="E2" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62" t="s">
+      <c r="F2" s="67"/>
+      <c r="G2" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62" t="s">
+      <c r="H2" s="67"/>
+      <c r="I2" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62" t="s">
+      <c r="J2" s="67"/>
+      <c r="K2" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62" t="s">
+      <c r="L2" s="67"/>
+      <c r="M2" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62" t="s">
+      <c r="N2" s="67"/>
+      <c r="O2" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62" t="s">
-        <v>25</v>
-      </c>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62" t="s">
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62" t="s">
+      <c r="T2" s="67"/>
+      <c r="U2" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="V2" s="69"/>
-      <c r="W2" s="68" t="s">
+      <c r="V2" s="74"/>
+      <c r="W2" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="X2" s="62"/>
+      <c r="X2" s="67"/>
     </row>
     <row r="3" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="32" t="s">
@@ -6123,34 +6238,34 @@
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="F29" s="65" t="s">
+      <c r="F29" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="66"/>
-      <c r="H29" s="67"/>
-      <c r="I29" s="63">
+      <c r="G29" s="71"/>
+      <c r="H29" s="72"/>
+      <c r="I29" s="68">
         <f>C27+E27+G27+I27+K27+M27+O27+Q27+S27+U27</f>
         <v>2469.42</v>
       </c>
-      <c r="J29" s="64"/>
+      <c r="J29" s="69"/>
     </row>
     <row r="30" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="G30" s="70" t="s">
+      <c r="G30" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="H30" s="70"/>
-      <c r="I30" s="63">
+      <c r="H30" s="75"/>
+      <c r="I30" s="68">
         <f>+D27+F27+H27+J27+L27+N27+P27+R27+T27+V27</f>
         <v>1774.69</v>
       </c>
-      <c r="J30" s="64"/>
+      <c r="J30" s="69"/>
     </row>
     <row r="31" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="I31" s="63">
+      <c r="I31" s="68">
         <f>I30-I29</f>
         <v>-694.73</v>
       </c>
-      <c r="J31" s="64"/>
+      <c r="J31" s="69"/>
     </row>
     <row r="32" spans="2:27" x14ac:dyDescent="0.3">
       <c r="C32" s="1">
@@ -6199,11 +6314,11 @@
       </c>
     </row>
     <row r="34" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="I34" s="64">
+      <c r="I34" s="69">
         <f>I33+I31</f>
         <v>505.27</v>
       </c>
-      <c r="J34" s="64"/>
+      <c r="J34" s="69"/>
     </row>
     <row r="38" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C38" s="1">
@@ -6291,50 +6406,50 @@
   <sheetData>
     <row r="1" spans="2:27" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:27" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62" t="s">
+      <c r="D2" s="67"/>
+      <c r="E2" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="62"/>
-      <c r="G2" s="72" t="s">
+      <c r="F2" s="67"/>
+      <c r="G2" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="68"/>
-      <c r="I2" s="62" t="s">
+      <c r="H2" s="73"/>
+      <c r="I2" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62" t="s">
+      <c r="J2" s="67"/>
+      <c r="K2" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62" t="s">
+      <c r="L2" s="67"/>
+      <c r="M2" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62" t="s">
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62" t="s">
+      <c r="R2" s="67"/>
+      <c r="S2" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62" t="s">
+      <c r="T2" s="67"/>
+      <c r="U2" s="67" t="s">
         <v>27</v>
       </c>
-      <c r="V2" s="69"/>
-      <c r="W2" s="68" t="s">
+      <c r="V2" s="74"/>
+      <c r="W2" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="X2" s="62"/>
+      <c r="X2" s="67"/>
     </row>
     <row r="3" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="32" t="s">
@@ -7694,34 +7809,34 @@
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="F29" s="65" t="s">
+      <c r="F29" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="66"/>
-      <c r="H29" s="67"/>
-      <c r="I29" s="63">
+      <c r="G29" s="71"/>
+      <c r="H29" s="72"/>
+      <c r="I29" s="68">
         <f>C27+E27+G27+I27+K27+M27+O27+Q27+S27+U27</f>
         <v>1788.24</v>
       </c>
-      <c r="J29" s="64"/>
+      <c r="J29" s="69"/>
     </row>
     <row r="30" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="G30" s="70" t="s">
+      <c r="G30" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="H30" s="70"/>
-      <c r="I30" s="63">
+      <c r="H30" s="75"/>
+      <c r="I30" s="68">
         <f>+D27+F27+H27+J27+L27+N27+P27+R27+T27+V27</f>
         <v>2492.1999999999998</v>
       </c>
-      <c r="J30" s="64"/>
+      <c r="J30" s="69"/>
     </row>
     <row r="31" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="I31" s="63">
+      <c r="I31" s="68">
         <f>I30-I29</f>
         <v>703.95999999999981</v>
       </c>
-      <c r="J31" s="64"/>
+      <c r="J31" s="69"/>
     </row>
     <row r="32" spans="2:27" x14ac:dyDescent="0.3">
       <c r="C32" s="36">
@@ -7775,11 +7890,11 @@
         <v>64</v>
       </c>
       <c r="H34" s="42"/>
-      <c r="I34" s="71">
+      <c r="I34" s="76">
         <f>I33+I31</f>
         <v>1303.9599999999998</v>
       </c>
-      <c r="J34" s="71"/>
+      <c r="J34" s="76"/>
       <c r="M34" s="33"/>
     </row>
     <row r="38" spans="3:16" x14ac:dyDescent="0.3">
@@ -7869,54 +7984,54 @@
   <sheetData>
     <row r="1" spans="2:34" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:34" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62" t="s">
+      <c r="D2" s="67"/>
+      <c r="E2" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62" t="s">
+      <c r="F2" s="67"/>
+      <c r="G2" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62" t="s">
+      <c r="H2" s="67"/>
+      <c r="I2" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62" t="s">
+      <c r="J2" s="67"/>
+      <c r="K2" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62" t="s">
+      <c r="L2" s="67"/>
+      <c r="M2" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62" t="s">
+      <c r="N2" s="67"/>
+      <c r="O2" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62" t="s">
-        <v>25</v>
-      </c>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62" t="s">
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62" t="s">
+      <c r="T2" s="67"/>
+      <c r="U2" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="V2" s="69"/>
-      <c r="W2" s="62" t="s">
+      <c r="V2" s="74"/>
+      <c r="W2" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="X2" s="69"/>
-      <c r="Y2" s="68" t="s">
+      <c r="X2" s="74"/>
+      <c r="Y2" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="Z2" s="62"/>
+      <c r="Z2" s="67"/>
     </row>
     <row r="3" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="32" t="s">
@@ -9970,34 +10085,34 @@
       </c>
     </row>
     <row r="31" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="F31" s="65" t="s">
+      <c r="F31" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="66"/>
-      <c r="H31" s="67"/>
-      <c r="I31" s="63">
+      <c r="G31" s="71"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="68">
         <f>C29+E29+G29+I29+K29+M29+O29+Q29+S29+U29+W29</f>
         <v>2521.33</v>
       </c>
-      <c r="J31" s="64"/>
+      <c r="J31" s="69"/>
     </row>
     <row r="32" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="G32" s="70" t="s">
+      <c r="G32" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="H32" s="70"/>
-      <c r="I32" s="63">
+      <c r="H32" s="75"/>
+      <c r="I32" s="68">
         <f>+D29+F29+H29+J29+L29+N29+P29+R29+T29+V29+X29</f>
         <v>2997.5899999999997</v>
       </c>
-      <c r="J32" s="64"/>
+      <c r="J32" s="69"/>
     </row>
     <row r="33" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="I33" s="63">
+      <c r="I33" s="68">
         <f>I32-I31</f>
         <v>476.25999999999976</v>
       </c>
-      <c r="J33" s="64"/>
+      <c r="J33" s="69"/>
     </row>
     <row r="34" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C34" s="36">
@@ -10050,11 +10165,11 @@
         <v>64</v>
       </c>
       <c r="H36" s="42"/>
-      <c r="I36" s="71">
+      <c r="I36" s="76">
         <f>I35+I33</f>
         <v>2476.2599999999998</v>
       </c>
-      <c r="J36" s="71"/>
+      <c r="J36" s="76"/>
       <c r="M36" s="33"/>
     </row>
     <row r="40" spans="3:17" x14ac:dyDescent="0.3">
@@ -10145,54 +10260,54 @@
   <sheetData>
     <row r="1" spans="2:34" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:34" ht="18" x14ac:dyDescent="0.35">
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="62"/>
-      <c r="E2" s="72" t="s">
+      <c r="D2" s="67"/>
+      <c r="E2" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="68"/>
-      <c r="G2" s="62" t="s">
+      <c r="F2" s="73"/>
+      <c r="G2" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62" t="s">
+      <c r="H2" s="67"/>
+      <c r="I2" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62" t="s">
+      <c r="J2" s="67"/>
+      <c r="K2" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="62"/>
-      <c r="M2" s="72" t="s">
+      <c r="L2" s="67"/>
+      <c r="M2" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="68"/>
-      <c r="O2" s="62" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62" t="s">
+      <c r="N2" s="73"/>
+      <c r="O2" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62" t="s">
+      <c r="R2" s="67"/>
+      <c r="S2" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62" t="s">
+      <c r="T2" s="67"/>
+      <c r="U2" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="V2" s="69"/>
-      <c r="W2" s="62" t="s">
+      <c r="V2" s="74"/>
+      <c r="W2" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="X2" s="69"/>
-      <c r="Y2" s="68" t="s">
+      <c r="X2" s="74"/>
+      <c r="Y2" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="Z2" s="62"/>
+      <c r="Z2" s="67"/>
     </row>
     <row r="3" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B3" s="32" t="s">
@@ -12201,34 +12316,34 @@
       </c>
     </row>
     <row r="31" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="F31" s="65" t="s">
+      <c r="F31" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="66"/>
-      <c r="H31" s="67"/>
-      <c r="I31" s="63">
+      <c r="G31" s="71"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="68">
         <f>C29+E29+G29+I29+K29+M29+O29+Q29+S29+U29+W29</f>
         <v>2462.73</v>
       </c>
-      <c r="J31" s="64"/>
+      <c r="J31" s="69"/>
     </row>
     <row r="32" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="G32" s="70" t="s">
+      <c r="G32" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="H32" s="70"/>
-      <c r="I32" s="63">
+      <c r="H32" s="75"/>
+      <c r="I32" s="68">
         <f>+D29+F29+H29+J29+L29+N29+P29+R29+T29+V29+X29</f>
         <v>1004.25</v>
       </c>
-      <c r="J32" s="64"/>
+      <c r="J32" s="69"/>
     </row>
     <row r="33" spans="3:25" x14ac:dyDescent="0.3">
-      <c r="I33" s="63">
+      <c r="I33" s="68">
         <f>I32-I31</f>
         <v>-1458.48</v>
       </c>
-      <c r="J33" s="64"/>
+      <c r="J33" s="69"/>
       <c r="Y33">
         <f>2167+183+5*10</f>
         <v>2400</v>
@@ -12324,11 +12439,11 @@
         <v>64</v>
       </c>
       <c r="H38" s="42"/>
-      <c r="I38" s="71">
+      <c r="I38" s="76">
         <f>I36+I33+J37</f>
         <v>322.7800000000002</v>
       </c>
-      <c r="J38" s="71"/>
+      <c r="J38" s="76"/>
       <c r="M38" s="33"/>
     </row>
     <row r="40" spans="3:25" x14ac:dyDescent="0.3">
@@ -12650,54 +12765,54 @@
   <sheetData>
     <row r="1" spans="2:34" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:34" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="62"/>
-      <c r="E2" s="72" t="s">
+      <c r="D2" s="67"/>
+      <c r="E2" s="77" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="68"/>
-      <c r="G2" s="62" t="s">
+      <c r="F2" s="73"/>
+      <c r="G2" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62" t="s">
+      <c r="H2" s="67"/>
+      <c r="I2" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62" t="s">
+      <c r="J2" s="67"/>
+      <c r="K2" s="67" t="s">
         <v>104</v>
       </c>
-      <c r="L2" s="62"/>
-      <c r="M2" s="72" t="s">
+      <c r="L2" s="67"/>
+      <c r="M2" s="77" t="s">
         <v>105</v>
       </c>
-      <c r="N2" s="68"/>
-      <c r="O2" s="62" t="s">
+      <c r="N2" s="73"/>
+      <c r="O2" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62" t="s">
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62" t="s">
+      <c r="R2" s="67"/>
+      <c r="S2" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62" t="s">
+      <c r="T2" s="67"/>
+      <c r="U2" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="V2" s="69"/>
-      <c r="W2" s="62" t="s">
+      <c r="V2" s="74"/>
+      <c r="W2" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="X2" s="69"/>
-      <c r="Y2" s="68" t="s">
+      <c r="X2" s="74"/>
+      <c r="Y2" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="Z2" s="62"/>
+      <c r="Z2" s="67"/>
     </row>
     <row r="3" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="32" t="s">
@@ -14680,34 +14795,34 @@
       </c>
     </row>
     <row r="31" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="F31" s="65" t="s">
+      <c r="F31" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="66"/>
-      <c r="H31" s="67"/>
-      <c r="I31" s="63">
+      <c r="G31" s="71"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="68">
         <f>C29+E29+G29+I29+K29+M29+O29+Q29+S29+U29+W29</f>
         <v>2158</v>
       </c>
-      <c r="J31" s="64"/>
+      <c r="J31" s="69"/>
     </row>
     <row r="32" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="G32" s="70" t="s">
+      <c r="G32" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="H32" s="70"/>
-      <c r="I32" s="63">
+      <c r="H32" s="75"/>
+      <c r="I32" s="68">
         <f>+D29+F29+H29+J29+L29+N29+P29+R29+T29+V29+X29</f>
         <v>709.26</v>
       </c>
-      <c r="J32" s="64"/>
+      <c r="J32" s="69"/>
     </row>
     <row r="33" spans="3:25" x14ac:dyDescent="0.3">
-      <c r="I33" s="63">
+      <c r="I33" s="68">
         <f>I32-I31</f>
         <v>-1448.74</v>
       </c>
-      <c r="J33" s="64"/>
+      <c r="J33" s="69"/>
       <c r="Y33">
         <f>2167+183+5*10</f>
         <v>2400</v>
@@ -14796,11 +14911,11 @@
         <v>64</v>
       </c>
       <c r="H38" s="42"/>
-      <c r="I38" s="71">
+      <c r="I38" s="76">
         <f>I36+I33</f>
         <v>552.84999999999991</v>
       </c>
-      <c r="J38" s="71"/>
+      <c r="J38" s="76"/>
       <c r="M38" s="33"/>
     </row>
     <row r="40" spans="3:25" x14ac:dyDescent="0.3">
@@ -15155,66 +15270,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:38" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="W1" s="73"/>
-      <c r="X1" s="74"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="79"/>
     </row>
     <row r="2" spans="2:38" ht="18" x14ac:dyDescent="0.35">
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="62"/>
-      <c r="E2" s="72" t="s">
+      <c r="D2" s="67"/>
+      <c r="E2" s="77" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="68"/>
-      <c r="G2" s="62" t="s">
+      <c r="F2" s="73"/>
+      <c r="G2" s="67" t="s">
         <v>114</v>
       </c>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62" t="s">
+      <c r="H2" s="67"/>
+      <c r="I2" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62" t="s">
+      <c r="J2" s="67"/>
+      <c r="K2" s="67" t="s">
         <v>104</v>
       </c>
-      <c r="L2" s="62"/>
-      <c r="M2" s="72" t="s">
+      <c r="L2" s="67"/>
+      <c r="M2" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="N2" s="68"/>
-      <c r="O2" s="62" t="s">
+      <c r="N2" s="73"/>
+      <c r="O2" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62" t="s">
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62" t="s">
+      <c r="R2" s="67"/>
+      <c r="S2" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62" t="s">
+      <c r="T2" s="67"/>
+      <c r="U2" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="V2" s="72"/>
-      <c r="W2" s="75" t="s">
+      <c r="V2" s="77"/>
+      <c r="W2" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="X2" s="76"/>
-      <c r="Y2" s="75" t="s">
+      <c r="X2" s="81"/>
+      <c r="Y2" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="Z2" s="77"/>
-      <c r="AA2" s="78" t="s">
+      <c r="Z2" s="82"/>
+      <c r="AA2" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="AB2" s="79"/>
-      <c r="AC2" s="68" t="s">
+      <c r="AB2" s="84"/>
+      <c r="AC2" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="AD2" s="62"/>
+      <c r="AD2" s="67"/>
     </row>
     <row r="3" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B3" s="32" t="s">
@@ -17548,34 +17663,34 @@
       </c>
     </row>
     <row r="32" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="F32" s="65" t="s">
+      <c r="F32" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="G32" s="66"/>
-      <c r="H32" s="67"/>
-      <c r="I32" s="63">
+      <c r="G32" s="71"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="68">
         <f>C30+E30+G30+I30+K30+M30+O30+Q30+S30+U30+AA30+W30+Y30</f>
         <v>2648</v>
       </c>
-      <c r="J32" s="64"/>
+      <c r="J32" s="69"/>
     </row>
     <row r="33" spans="3:25" x14ac:dyDescent="0.3">
-      <c r="G33" s="70" t="s">
+      <c r="G33" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="H33" s="70"/>
-      <c r="I33" s="63">
+      <c r="H33" s="75"/>
+      <c r="I33" s="68">
         <f>+D30+F30+H30+J30+L30+N30+P30+R30+T30+V30+AB30+X30+Z30</f>
         <v>1694.2299999999998</v>
       </c>
-      <c r="J33" s="64"/>
+      <c r="J33" s="69"/>
     </row>
     <row r="34" spans="3:25" x14ac:dyDescent="0.3">
-      <c r="I34" s="63">
+      <c r="I34" s="68">
         <f>I33-I32</f>
         <v>-953.77000000000021</v>
       </c>
-      <c r="J34" s="64"/>
+      <c r="J34" s="69"/>
       <c r="Y34">
         <f>2167+183+5*10</f>
         <v>2400</v>
@@ -17658,11 +17773,11 @@
         <v>64</v>
       </c>
       <c r="H39" s="42"/>
-      <c r="I39" s="71">
+      <c r="I39" s="76">
         <f>I37+I34</f>
         <v>1446.28</v>
       </c>
-      <c r="J39" s="71"/>
+      <c r="J39" s="76"/>
       <c r="M39" s="33"/>
     </row>
     <row r="41" spans="3:25" x14ac:dyDescent="0.3">
@@ -18949,70 +19064,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:38" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="W1" s="73"/>
-      <c r="X1" s="74"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="79"/>
     </row>
     <row r="2" spans="2:38" ht="18" x14ac:dyDescent="0.35">
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="67" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="62"/>
-      <c r="E2" s="72" t="s">
+      <c r="D2" s="67"/>
+      <c r="E2" s="77" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="68"/>
-      <c r="G2" s="62" t="s">
+      <c r="F2" s="73"/>
+      <c r="G2" s="67" t="s">
         <v>114</v>
       </c>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62" t="s">
+      <c r="H2" s="67"/>
+      <c r="I2" s="67" t="s">
         <v>115</v>
       </c>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62" t="s">
+      <c r="J2" s="67"/>
+      <c r="K2" s="67" t="s">
         <v>104</v>
       </c>
-      <c r="L2" s="62"/>
-      <c r="M2" s="72" t="s">
+      <c r="L2" s="67"/>
+      <c r="M2" s="77" t="s">
         <v>103</v>
       </c>
-      <c r="N2" s="68"/>
-      <c r="O2" s="62" t="s">
+      <c r="N2" s="73"/>
+      <c r="O2" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62" t="s">
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67" t="s">
         <v>107</v>
       </c>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62" t="s">
+      <c r="R2" s="67"/>
+      <c r="S2" s="67" t="s">
         <v>100</v>
       </c>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62" t="s">
+      <c r="T2" s="67"/>
+      <c r="U2" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="V2" s="72"/>
-      <c r="W2" s="75" t="s">
+      <c r="V2" s="77"/>
+      <c r="W2" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="X2" s="76"/>
-      <c r="Y2" s="75" t="s">
+      <c r="X2" s="81"/>
+      <c r="Y2" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="Z2" s="76"/>
-      <c r="AA2" s="80" t="s">
+      <c r="Z2" s="81"/>
+      <c r="AA2" s="85" t="s">
         <v>180</v>
       </c>
-      <c r="AB2" s="81"/>
-      <c r="AC2" s="78" t="s">
+      <c r="AB2" s="86"/>
+      <c r="AC2" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="AD2" s="79"/>
-      <c r="AE2" s="68" t="s">
+      <c r="AD2" s="84"/>
+      <c r="AE2" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="AF2" s="62"/>
+      <c r="AF2" s="67"/>
     </row>
     <row r="3" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B3" s="32" t="s">
@@ -19117,51 +19232,103 @@
       <c r="B4" s="54" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="13"/>
-      <c r="U4" s="12"/>
-      <c r="V4" s="19"/>
-      <c r="W4" s="12"/>
-      <c r="X4" s="19"/>
-      <c r="Y4" s="12"/>
-      <c r="Z4" s="19"/>
-      <c r="AA4" s="12"/>
-      <c r="AB4" s="19"/>
+      <c r="C4" s="12">
+        <v>15</v>
+      </c>
+      <c r="D4" s="13">
+        <v>0</v>
+      </c>
+      <c r="E4" s="14">
+        <v>15</v>
+      </c>
+      <c r="F4" s="13">
+        <v>0</v>
+      </c>
+      <c r="G4" s="14">
+        <v>15</v>
+      </c>
+      <c r="H4" s="13">
+        <v>0</v>
+      </c>
+      <c r="I4" s="14">
+        <v>10</v>
+      </c>
+      <c r="J4" s="13">
+        <v>0</v>
+      </c>
+      <c r="K4" s="14">
+        <v>15</v>
+      </c>
+      <c r="L4" s="13">
+        <v>0</v>
+      </c>
+      <c r="M4" s="14">
+        <v>15</v>
+      </c>
+      <c r="N4" s="13">
+        <v>64</v>
+      </c>
+      <c r="O4" s="14">
+        <v>15</v>
+      </c>
+      <c r="P4" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="14">
+        <v>15</v>
+      </c>
+      <c r="R4" s="13">
+        <v>0</v>
+      </c>
+      <c r="S4" s="14">
+        <v>15</v>
+      </c>
+      <c r="T4" s="13">
+        <v>0</v>
+      </c>
+      <c r="U4" s="12">
+        <v>10</v>
+      </c>
+      <c r="V4" s="19">
+        <v>0</v>
+      </c>
+      <c r="W4" s="12">
+        <v>10</v>
+      </c>
+      <c r="X4" s="19">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="12">
+        <v>5</v>
+      </c>
+      <c r="Z4" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="12">
+        <v>15</v>
+      </c>
+      <c r="AB4" s="19">
+        <v>0</v>
+      </c>
       <c r="AC4" s="17">
         <f>U4+S4+Q4+O4+M4+K4+I4+G4+E4+C4+W4+Y4</f>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AD4" s="48">
         <f t="shared" ref="AD4" si="0">V4+T4+R4+P4+N4+L4+J4+H4+F4+D4</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AE4" s="1">
         <f>AC4</f>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF4" s="1">
         <f>AD4</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG4" s="1">
         <f>AF4-AE4</f>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH4" s="1"/>
     </row>
@@ -19205,17 +19372,23 @@
       </c>
       <c r="AE5" s="1">
         <f>AE4+AC5</f>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF5" s="1">
         <f>AF4+AD5</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG5" s="1">
         <f t="shared" ref="AG5:AG29" si="1">AF5-AE5</f>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH5" s="1"/>
+      <c r="AI5" s="87" t="s">
+        <v>181</v>
+      </c>
+      <c r="AJ5" s="87"/>
+      <c r="AK5" s="87"/>
+      <c r="AL5" s="87"/>
     </row>
     <row r="6" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B6" s="52" t="s">
@@ -19257,15 +19430,15 @@
       </c>
       <c r="AE6" s="1">
         <f t="shared" ref="AE6:AF21" si="3">AE5+AC6</f>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF6" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG6" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH6" s="1"/>
       <c r="AI6" s="43" t="s">
@@ -19321,22 +19494,22 @@
       </c>
       <c r="AE7" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF7" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG7" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH7" s="44" t="s">
         <v>71</v>
       </c>
       <c r="AI7" s="44">
         <f>+E30+'Punters 2024'!AE7</f>
-        <v>1208</v>
+        <v>1223</v>
       </c>
       <c r="AJ7" s="44">
         <f>+F30+'Punters 2024'!AF7</f>
@@ -19344,11 +19517,11 @@
       </c>
       <c r="AK7" s="49">
         <f>+AJ7-AI7</f>
-        <v>-665.4</v>
+        <v>-680.4</v>
       </c>
       <c r="AL7" s="47">
         <f>(AJ7-AI7)/AI7</f>
-        <v>-0.55082781456953644</v>
+        <v>-0.55633687653311525</v>
       </c>
     </row>
     <row r="8" spans="2:38" x14ac:dyDescent="0.3">
@@ -19391,22 +19564,22 @@
       </c>
       <c r="AE8" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF8" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG8" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH8" s="44" t="s">
         <v>72</v>
       </c>
       <c r="AI8" s="44">
         <f>+K30+'Punters 2024'!AE8</f>
-        <v>1388</v>
+        <v>1403</v>
       </c>
       <c r="AJ8" s="44">
         <f>+L30+'Punters 2024'!AF8</f>
@@ -19414,11 +19587,11 @@
       </c>
       <c r="AK8" s="50">
         <f t="shared" ref="AK8:AK18" si="4">+AJ8-AI8</f>
-        <v>-249.48000000000002</v>
+        <v>-264.48</v>
       </c>
       <c r="AL8" s="47">
         <f t="shared" ref="AL8:AL18" si="5">(AJ8-AI8)/AI8</f>
-        <v>-0.17974063400576371</v>
+        <v>-0.18851033499643621</v>
       </c>
     </row>
     <row r="9" spans="2:38" x14ac:dyDescent="0.3">
@@ -19461,22 +19634,22 @@
       </c>
       <c r="AE9" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF9" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG9" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH9" s="44" t="s">
         <v>73</v>
       </c>
       <c r="AI9" s="44">
         <f>+Y30+'Punters 2024'!AE9</f>
-        <v>1366.48</v>
+        <v>1371.48</v>
       </c>
       <c r="AJ9" s="44">
         <f>Z30+'Punters 2024'!AF9</f>
@@ -19484,11 +19657,11 @@
       </c>
       <c r="AK9" s="50">
         <f t="shared" si="4"/>
-        <v>-272.57999999999993</v>
+        <v>-277.57999999999993</v>
       </c>
       <c r="AL9" s="47">
         <f t="shared" si="5"/>
-        <v>-0.19947602599379421</v>
+        <v>-0.20239449353982553</v>
       </c>
     </row>
     <row r="10" spans="2:38" x14ac:dyDescent="0.3">
@@ -19531,22 +19704,22 @@
       </c>
       <c r="AE10" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF10" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG10" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH10" s="44" t="s">
         <v>74</v>
       </c>
       <c r="AI10" s="44">
         <f>+S30+'Punters 2024'!AE10</f>
-        <v>1364.9</v>
+        <v>1379.9</v>
       </c>
       <c r="AJ10" s="44">
         <f>+T30+'Punters 2024'!AF10</f>
@@ -19554,11 +19727,11 @@
       </c>
       <c r="AK10" s="50">
         <f t="shared" si="4"/>
-        <v>151.54999999999973</v>
+        <v>136.54999999999973</v>
       </c>
       <c r="AL10" s="45">
         <f t="shared" si="5"/>
-        <v>0.11103377536815863</v>
+        <v>9.8956446119283809E-2</v>
       </c>
     </row>
     <row r="11" spans="2:38" x14ac:dyDescent="0.3">
@@ -19601,34 +19774,34 @@
       </c>
       <c r="AE11" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF11" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG11" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH11" s="44" t="s">
         <v>75</v>
       </c>
       <c r="AI11" s="44">
         <f>+M30+'Punters 2024'!AE11</f>
-        <v>1073</v>
+        <v>1088</v>
       </c>
       <c r="AJ11" s="44">
         <f>+N30+'Punters 2024'!AF11</f>
-        <v>98.25</v>
+        <v>162.25</v>
       </c>
       <c r="AK11" s="49">
         <f t="shared" si="4"/>
-        <v>-974.75</v>
+        <v>-925.75</v>
       </c>
       <c r="AL11" s="47">
         <f t="shared" si="5"/>
-        <v>-0.9084342963653308</v>
+        <v>-0.85087316176470584</v>
       </c>
     </row>
     <row r="12" spans="2:38" x14ac:dyDescent="0.3">
@@ -19671,22 +19844,22 @@
       </c>
       <c r="AE12" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF12" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG12" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH12" s="44" t="s">
         <v>76</v>
       </c>
       <c r="AI12" s="44">
         <f>+U30+'Punters 2024'!AE12</f>
-        <v>1384.96</v>
+        <v>1394.96</v>
       </c>
       <c r="AJ12" s="44">
         <f>+V30+'Punters 2024'!AF12</f>
@@ -19694,11 +19867,11 @@
       </c>
       <c r="AK12" s="49">
         <f t="shared" si="4"/>
-        <v>-494.30000000000018</v>
+        <v>-504.30000000000018</v>
       </c>
       <c r="AL12" s="47">
         <f t="shared" si="5"/>
-        <v>-0.35690561460258791</v>
+        <v>-0.36151574238687861</v>
       </c>
     </row>
     <row r="13" spans="2:38" x14ac:dyDescent="0.3">
@@ -19741,22 +19914,22 @@
       </c>
       <c r="AE13" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF13" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG13" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH13" s="44" t="s">
         <v>77</v>
       </c>
       <c r="AI13" s="44">
         <f>+I30+'Punters 2024'!AE13</f>
-        <v>1346.3400000000001</v>
+        <v>1356.3400000000001</v>
       </c>
       <c r="AJ13" s="44">
         <f>+J30+'Punters 2024'!AF13</f>
@@ -19764,11 +19937,11 @@
       </c>
       <c r="AK13" s="49">
         <f t="shared" si="4"/>
-        <v>-720.10000000000014</v>
+        <v>-730.10000000000014</v>
       </c>
       <c r="AL13" s="47">
         <f t="shared" si="5"/>
-        <v>-0.5348574654247813</v>
+        <v>-0.53828686022678685</v>
       </c>
     </row>
     <row r="14" spans="2:38" x14ac:dyDescent="0.3">
@@ -19811,22 +19984,22 @@
       </c>
       <c r="AE14" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF14" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG14" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH14" s="44" t="s">
         <v>78</v>
       </c>
       <c r="AI14" s="44">
         <f>+Q30+'Punters 2024'!AE14</f>
-        <v>1353</v>
+        <v>1368</v>
       </c>
       <c r="AJ14" s="44">
         <f>+R30+'Punters 2024'!AF14</f>
@@ -19834,11 +20007,11 @@
       </c>
       <c r="AK14" s="49">
         <f t="shared" si="4"/>
-        <v>-715.53</v>
+        <v>-730.53</v>
       </c>
       <c r="AL14" s="47">
         <f t="shared" si="5"/>
-        <v>-0.52884700665188467</v>
+        <v>-0.5340131578947368</v>
       </c>
     </row>
     <row r="15" spans="2:38" x14ac:dyDescent="0.3">
@@ -19881,22 +20054,22 @@
       </c>
       <c r="AE15" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF15" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG15" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH15" s="44" t="s">
         <v>79</v>
       </c>
       <c r="AI15" s="44">
         <f>+O30+'Punters 2024'!AE15</f>
-        <v>1362.7</v>
+        <v>1377.7</v>
       </c>
       <c r="AJ15" s="44">
         <f>+P30+'Punters 2024'!AF15</f>
@@ -19904,11 +20077,11 @@
       </c>
       <c r="AK15" s="50">
         <f t="shared" si="4"/>
-        <v>333.38999999999987</v>
+        <v>318.38999999999987</v>
       </c>
       <c r="AL15" s="45">
         <f t="shared" si="5"/>
-        <v>0.24465399574374394</v>
+        <v>0.23110256224141676</v>
       </c>
     </row>
     <row r="16" spans="2:38" x14ac:dyDescent="0.3">
@@ -19951,22 +20124,22 @@
       </c>
       <c r="AE16" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF16" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG16" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH16" s="44" t="s">
         <v>80</v>
       </c>
       <c r="AI16" s="44">
         <f>+W30+'Punters 2024'!AE16</f>
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="AJ16" s="44">
         <f>+X30+'Punters 2024'!AF16</f>
@@ -19974,11 +20147,11 @@
       </c>
       <c r="AK16" s="49">
         <f t="shared" si="4"/>
-        <v>-468.75</v>
+        <v>-478.75</v>
       </c>
       <c r="AL16" s="47">
         <f t="shared" si="5"/>
-        <v>-0.75604838709677424</v>
+        <v>-0.75992063492063489</v>
       </c>
     </row>
     <row r="17" spans="2:38" x14ac:dyDescent="0.3">
@@ -20021,22 +20194,22 @@
       </c>
       <c r="AE17" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF17" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG17" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH17" s="44" t="s">
         <v>116</v>
       </c>
       <c r="AI17" s="44">
         <f>+C30</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ17" s="44">
         <f>+D30</f>
@@ -20044,11 +20217,11 @@
       </c>
       <c r="AK17" s="49">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AL17" s="47" t="e">
+        <v>-15</v>
+      </c>
+      <c r="AL17" s="47">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18" spans="2:38" x14ac:dyDescent="0.3">
@@ -20091,34 +20264,34 @@
       </c>
       <c r="AE18" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF18" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG18" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AH18" s="44" t="s">
+        <v>-91</v>
+      </c>
+      <c r="AH18" s="64" t="s">
         <v>117</v>
       </c>
-      <c r="AI18" s="44">
+      <c r="AI18" s="64">
         <f>+G30</f>
-        <v>0</v>
-      </c>
-      <c r="AJ18" s="44">
+        <v>15</v>
+      </c>
+      <c r="AJ18" s="64">
         <f>+H30</f>
         <v>0</v>
       </c>
-      <c r="AK18" s="49">
+      <c r="AK18" s="65">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AL18" s="47" t="e">
+        <v>-15</v>
+      </c>
+      <c r="AL18" s="66">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="19" spans="2:38" x14ac:dyDescent="0.3">
@@ -20161,17 +20334,23 @@
       </c>
       <c r="AE19" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF19" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG19" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AH19" s="1"/>
+        <v>-91</v>
+      </c>
+      <c r="AH19" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="AI19" s="63"/>
+      <c r="AJ19" s="63"/>
+      <c r="AK19" s="63"/>
+      <c r="AL19" s="63"/>
     </row>
     <row r="20" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B20" s="53" t="s">
@@ -20213,15 +20392,15 @@
       </c>
       <c r="AE20" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF20" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG20" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH20" s="1"/>
     </row>
@@ -20265,15 +20444,15 @@
       </c>
       <c r="AE21" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF21" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG21" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH21" s="1"/>
     </row>
@@ -20317,15 +20496,15 @@
       </c>
       <c r="AE22" s="1">
         <f t="shared" ref="AE22:AF29" si="6">AE21+AC22</f>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF22" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG22" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH22" s="1"/>
     </row>
@@ -20369,15 +20548,15 @@
       </c>
       <c r="AE23" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF23" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG23" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH23" s="1"/>
     </row>
@@ -20421,15 +20600,15 @@
       </c>
       <c r="AE24" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF24" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG24" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH24" s="1"/>
     </row>
@@ -20473,15 +20652,15 @@
       </c>
       <c r="AE25" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF25" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG25" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH25" s="1"/>
     </row>
@@ -20525,15 +20704,15 @@
       </c>
       <c r="AE26" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF26" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG26" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH26" s="1"/>
     </row>
@@ -20577,15 +20756,15 @@
       </c>
       <c r="AE27" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF27" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG27" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH27" s="1"/>
     </row>
@@ -20629,15 +20808,15 @@
       </c>
       <c r="AE28" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF28" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG28" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH28" s="1"/>
     </row>
@@ -20681,15 +20860,15 @@
       </c>
       <c r="AE29" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AF29" s="1">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AG29" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-91</v>
       </c>
       <c r="AH29" s="1"/>
     </row>
@@ -20699,7 +20878,7 @@
       </c>
       <c r="C30" s="18">
         <f t="shared" ref="C30:AD30" si="8">SUM(C4:C29)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D30" s="18">
         <f t="shared" si="8"/>
@@ -20707,7 +20886,7 @@
       </c>
       <c r="E30" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F30" s="18">
         <f t="shared" si="8"/>
@@ -20715,7 +20894,7 @@
       </c>
       <c r="G30" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H30" s="18">
         <f t="shared" si="8"/>
@@ -20723,7 +20902,7 @@
       </c>
       <c r="I30" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J30" s="18">
         <f t="shared" si="8"/>
@@ -20731,7 +20910,7 @@
       </c>
       <c r="K30" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L30" s="18">
         <f t="shared" si="8"/>
@@ -20739,15 +20918,15 @@
       </c>
       <c r="M30" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N30" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="O30" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P30" s="18">
         <f t="shared" si="8"/>
@@ -20755,7 +20934,7 @@
       </c>
       <c r="Q30" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R30" s="18">
         <f t="shared" si="8"/>
@@ -20763,7 +20942,7 @@
       </c>
       <c r="S30" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="T30" s="18">
         <f>SUM(T4:T29)</f>
@@ -20771,7 +20950,7 @@
       </c>
       <c r="U30" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V30" s="21">
         <f t="shared" si="8"/>
@@ -20779,7 +20958,7 @@
       </c>
       <c r="W30" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="X30" s="21">
         <f t="shared" si="8"/>
@@ -20787,7 +20966,7 @@
       </c>
       <c r="Y30" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z30" s="21">
         <f t="shared" si="8"/>
@@ -20795,101 +20974,105 @@
       </c>
       <c r="AA30" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AB30" s="21">
-        <f t="shared" si="8"/>
+        <f>SUM(AB4:AB29)</f>
         <v>0</v>
       </c>
       <c r="AC30" s="29">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="AD30" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AE30" s="1"/>
     </row>
     <row r="31" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="D31" s="56" t="e">
+      <c r="D31" s="56">
         <f>(D30-C30)/C30</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F31" s="34" t="e">
+        <v>-1</v>
+      </c>
+      <c r="F31" s="34">
         <f>(F30-E30)/E30</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H31" s="34" t="e">
+        <v>-1</v>
+      </c>
+      <c r="H31" s="34">
         <f>(H30-G30)/G30</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J31" s="34" t="e">
+        <v>-1</v>
+      </c>
+      <c r="J31" s="34">
         <f>(J30-I30)/I30</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L31" s="28" t="e">
+        <v>-1</v>
+      </c>
+      <c r="L31" s="28">
         <f>(L30-K30)/K30</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N31" s="28" t="e">
+        <v>-1</v>
+      </c>
+      <c r="N31" s="28">
         <f>(N30-M30)/M30</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P31" s="28" t="e">
+        <v>3.2666666666666666</v>
+      </c>
+      <c r="P31" s="28">
         <f>(P30-O30)/O30</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R31" s="28" t="e">
+        <v>-1</v>
+      </c>
+      <c r="R31" s="28">
         <f>(R30-Q30)/Q30</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T31" s="22" t="e">
+        <v>-1</v>
+      </c>
+      <c r="T31" s="22">
         <f>(T30-S30)/S30</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V31" s="28" t="e">
+        <v>-1</v>
+      </c>
+      <c r="V31" s="28">
         <f>(V30-U30)/U30</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X31" s="28" t="e">
+        <v>-1</v>
+      </c>
+      <c r="X31" s="28">
         <f>(X30-W30)/W30</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z31" s="28" t="e">
+        <v>-1</v>
+      </c>
+      <c r="Z31" s="28">
         <f>(Z30-Y30)/Y30</f>
-        <v>#DIV/0!</v>
+        <v>-1</v>
+      </c>
+      <c r="AB31">
+        <f>(AB30-AA30)/AA30</f>
+        <v>-1</v>
       </c>
     </row>
     <row r="32" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="F32" s="65" t="s">
+      <c r="F32" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="G32" s="66"/>
-      <c r="H32" s="67"/>
-      <c r="I32" s="63">
+      <c r="G32" s="71"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="68">
         <f>C30+E30+G30+I30+K30+M30+O30+Q30+S30+U30+AA30+W30+Y30</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="64"/>
+        <v>170</v>
+      </c>
+      <c r="J32" s="69"/>
     </row>
     <row r="33" spans="3:25" x14ac:dyDescent="0.3">
-      <c r="G33" s="70" t="s">
+      <c r="G33" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="H33" s="70"/>
-      <c r="I33" s="63">
+      <c r="H33" s="75"/>
+      <c r="I33" s="68">
         <f>+D30+F30+H30+J30+L30+N30+P30+R30+T30+V30+AB30+X30+Z30</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="64"/>
+        <v>64</v>
+      </c>
+      <c r="J33" s="69"/>
     </row>
     <row r="34" spans="3:25" x14ac:dyDescent="0.3">
-      <c r="I34" s="63">
+      <c r="I34" s="68">
         <f>I33-I32</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="64"/>
+        <v>-106</v>
+      </c>
+      <c r="J34" s="69"/>
       <c r="Y34">
         <f>2167+183+5*10</f>
         <v>2400</v>
@@ -20898,7 +21081,7 @@
     <row r="35" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C35" s="36">
         <f>C30+E30+G30+I30</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D35" s="36">
         <f>D30+F30+H30+J30</f>
@@ -20906,23 +21089,23 @@
       </c>
       <c r="E35" s="37">
         <f>D35-C35</f>
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="I35" s="38">
         <f>O30+K30+M30+Q30</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J35" s="38">
         <f>P30+L30+N30</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="K35" s="39">
         <f>J35-I35</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O35" s="40">
         <f>U30+W30+Y30+S30</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="P35" s="40">
         <f>V30+X30+T30+Z30</f>
@@ -20930,7 +21113,7 @@
       </c>
       <c r="Q35" s="41">
         <f>P35-O35</f>
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="X35" s="55"/>
       <c r="Y35">
@@ -20940,21 +21123,21 @@
     </row>
     <row r="36" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C36" s="36"/>
-      <c r="D36" s="34" t="e">
+      <c r="D36" s="34">
         <f>(D35-C35)/C35</f>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="E36" s="37"/>
       <c r="I36" s="38"/>
-      <c r="J36" s="34" t="e">
+      <c r="J36" s="34">
         <f>(J35-I35)/I35</f>
-        <v>#DIV/0!</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="K36" s="39"/>
       <c r="O36" s="40"/>
-      <c r="P36" s="34" t="e">
+      <c r="P36" s="34">
         <f>(P35-O35)/O35</f>
-        <v>#DIV/0!</v>
+        <v>-1</v>
       </c>
       <c r="Q36" s="41"/>
       <c r="X36" s="55"/>
@@ -20972,11 +21155,11 @@
         <v>64</v>
       </c>
       <c r="H39" s="42"/>
-      <c r="I39" s="71">
+      <c r="I39" s="76">
         <f>I37+I34</f>
-        <v>2400.0500000000002</v>
-      </c>
-      <c r="J39" s="71"/>
+        <v>2294.0500000000002</v>
+      </c>
+      <c r="J39" s="76"/>
       <c r="M39" s="33"/>
     </row>
     <row r="41" spans="3:25" x14ac:dyDescent="0.3">
@@ -20985,7 +21168,7 @@
     <row r="43" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C43" s="1">
         <f>C30+E30+G30+I30</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D43" s="1">
         <f>D30+F30+H30+J30</f>
@@ -20993,15 +21176,15 @@
       </c>
       <c r="I43" s="1">
         <f>O30+K30+M30</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J43" s="1">
         <f>P30+L30+N30</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="O43" s="1">
         <f>U30+Q30+S30</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="P43" s="1">
         <f>V30+R30+T30</f>
@@ -21011,20 +21194,20 @@
     <row r="44" spans="3:25" x14ac:dyDescent="0.3">
       <c r="D44" s="1">
         <f>D43-C43</f>
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="J44" s="33">
         <f>J43-I43</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="P44" s="33">
         <f>P43-O43</f>
-        <v>0</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="46" spans="3:25" x14ac:dyDescent="0.3">
       <c r="V46" t="s">
-        <v>118</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47" spans="3:25" x14ac:dyDescent="0.3">
@@ -21032,13 +21215,14 @@
         <v>88</v>
       </c>
       <c r="J47" t="s">
-        <v>119</v>
+        <v>184</v>
       </c>
       <c r="V47" t="s">
         <v>89</v>
       </c>
       <c r="W47">
-        <v>9</v>
+        <f>SUM('1 Leg Losses 2026'!G8)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="3:25" x14ac:dyDescent="0.3">
@@ -21058,7 +21242,8 @@
         <v>12</v>
       </c>
       <c r="W48">
-        <v>6</v>
+        <f>SUM('1 Leg Losses 2026'!G2)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="4:23" x14ac:dyDescent="0.3">
@@ -21079,7 +21264,8 @@
         <v>93</v>
       </c>
       <c r="W49">
-        <v>7</v>
+        <f>SUM('1 Leg Losses 2026'!G5)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="4:23" x14ac:dyDescent="0.3">
@@ -21100,7 +21286,8 @@
         <v>92</v>
       </c>
       <c r="W50">
-        <v>2</v>
+        <f>SUM('1 Leg Losses 2026'!G1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="4:23" x14ac:dyDescent="0.3">
@@ -21121,7 +21308,8 @@
         <v>9</v>
       </c>
       <c r="W51">
-        <v>4</v>
+        <f>SUM('1 Leg Losses 2026'!G12)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="4:23" x14ac:dyDescent="0.3">
@@ -21142,7 +21330,8 @@
         <v>11</v>
       </c>
       <c r="W52">
-        <v>2</v>
+        <f>SUM('1 Leg Losses 2026'!G4)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="4:23" x14ac:dyDescent="0.3">
@@ -21163,7 +21352,8 @@
         <v>96</v>
       </c>
       <c r="W53">
-        <v>4</v>
+        <f>SUM('1 Leg Losses 2026'!G9)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="4:23" x14ac:dyDescent="0.3">
@@ -21184,7 +21374,8 @@
         <v>98</v>
       </c>
       <c r="W54">
-        <v>2</v>
+        <f>SUM('1 Leg Losses 2026'!G7)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="4:23" x14ac:dyDescent="0.3">
@@ -21193,7 +21384,7 @@
       </c>
       <c r="E55" s="1">
         <f>SUM(N30)</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="J55" t="s">
         <v>98</v>
@@ -21205,7 +21396,8 @@
         <v>97</v>
       </c>
       <c r="W55">
-        <v>6</v>
+        <f>SUM('1 Leg Losses 2026'!G6)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="4:23" x14ac:dyDescent="0.3">
@@ -21226,7 +21418,8 @@
         <v>94</v>
       </c>
       <c r="W56">
-        <v>5</v>
+        <f>SUM('1 Leg Losses 2026'!G3)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="4:23" x14ac:dyDescent="0.3">
@@ -21247,7 +21440,8 @@
         <v>120</v>
       </c>
       <c r="W57">
-        <v>3</v>
+        <f>SUM('1 Leg Losses 2026'!G10)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="4:23" x14ac:dyDescent="0.3">
@@ -21265,9 +21459,10 @@
         <v>0</v>
       </c>
       <c r="V58" t="s">
-        <v>121</v>
+        <v>185</v>
       </c>
       <c r="W58">
+        <f>SUM('1 Leg Losses 2026'!G13)</f>
         <v>1</v>
       </c>
     </row>
@@ -21286,38 +21481,44 @@
         <v>0</v>
       </c>
       <c r="V59" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="W59">
-        <f>SUM(W47:W58)</f>
-        <v>51</v>
+        <f>SUM('1 Leg Losses 2026'!G11)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>181</v>
+        <v>9</v>
       </c>
       <c r="E60" s="1">
-        <f>SUM(D30)</f>
+        <f>SUM(P30)</f>
         <v>0</v>
       </c>
       <c r="J60" t="s">
-        <v>181</v>
+        <v>9</v>
       </c>
       <c r="K60">
         <v>0</v>
+      </c>
+      <c r="V60" t="s">
+        <v>99</v>
+      </c>
+      <c r="W60">
+        <f>SUM(W47:W59)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>9</v>
+        <v>185</v>
       </c>
       <c r="E61" s="1">
-        <f>SUM(P30)</f>
         <v>0</v>
       </c>
       <c r="J61" t="s">
-        <v>9</v>
+        <v>185</v>
       </c>
       <c r="K61">
         <v>0</v>
@@ -21328,19 +21529,20 @@
         <v>99</v>
       </c>
       <c r="E62" s="1">
-        <f>SUM(E49:E61)</f>
-        <v>0</v>
+        <f>SUM(E49:E60)</f>
+        <v>64</v>
       </c>
       <c r="J62" t="s">
         <v>99</v>
       </c>
       <c r="K62">
-        <f>SUM(K49:K61)</f>
+        <f>SUM(K49:K60)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
+    <mergeCell ref="AI5:AL5"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:H2"/>
@@ -21348,8 +21550,6 @@
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="AC2:AD2"/>
     <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I32:J32"/>
     <mergeCell ref="W1:X1"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="O2:P2"/>
@@ -21363,6 +21563,8 @@
     <mergeCell ref="U2:V2"/>
     <mergeCell ref="W2:X2"/>
     <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:J32"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="63" orientation="landscape"/>
@@ -21370,6 +21572,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3e1ffae5-f160-4019-9720-1b11bf1b81a3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -21378,7 +21588,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002D8393059904904F9DB82DE4B9AFABF6" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f7bafc8adbaca2e93ffc3a1da3fd32d5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3e1ffae5-f160-4019-9720-1b11bf1b81a3" xmlns:ns4="21753bd8-bffc-4cd2-a328-982ee854c895" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8f821f56a5d2247de677e71e73e5a99e" ns3:_="" ns4:_="">
     <xsd:import namespace="3e1ffae5-f160-4019-9720-1b11bf1b81a3"/>
@@ -21599,15 +21809,17 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3e1ffae5-f160-4019-9720-1b11bf1b81a3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4D7A62A-0CB5-48B0-A73A-0A91BCC8EAEF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3e1ffae5-f160-4019-9720-1b11bf1b81a3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{948817D4-7F3F-493D-9D4C-B473DA03CC7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -21615,7 +21827,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22BA772B-ABF0-4278-9CEF-D9160BBA9E07}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21634,18 +21846,8 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4D7A62A-0CB5-48B0-A73A-0A91BCC8EAEF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3e1ffae5-f160-4019-9720-1b11bf1b81a3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{0f7d30c2-cad0-4405-8153-25a6a3313da4}" enabled="1" method="Privileged" siteId="{6c637512-c417-4e78-9d62-b61258e4b619}" contentBits="0" removed="0"/>
+  <clbl:label id="{0f7d30c2-cad0-4405-8153-25a6a3313da4}" enabled="1" method="Privileged" siteId="{6c637512-c417-4e78-9d62-b61258e4b619}" removed="0"/>
 </clbl:labelList>
 </file>
--- a/public/Data/HEMANPUNTERS.xlsx
+++ b/public/Data/HEMANPUNTERS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bturnor\Repos\seeMore\public\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAEF0170-E0A5-46D2-B033-19D78F6C50F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{99AA8D35-258A-4241-9077-27C28C887E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="8" activeTab="8" xr2:uid="{525E8989-1938-4309-A4CF-8F1D15E362FB}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="194">
   <si>
     <t>HE_MAN PUNTERS 2019</t>
   </si>
@@ -618,12 +618,6 @@
     <t>adam</t>
   </si>
   <si>
-    <t>1 leg losses as at 09/03/2026</t>
-  </si>
-  <si>
-    <t>Strikes for 2026 Season at 09/03/2026</t>
-  </si>
-  <si>
     <t>Adam</t>
   </si>
   <si>
@@ -640,6 +634,21 @@
   </si>
   <si>
     <t>Wanganeen-Milera Needed 30 or more, got 19</t>
+  </si>
+  <si>
+    <t>Jai Culley needed 17 or more disposals, got 11</t>
+  </si>
+  <si>
+    <t>Maynard needed 23 or more disposals, got 15</t>
+  </si>
+  <si>
+    <t>Peatling any time goal scoarer</t>
+  </si>
+  <si>
+    <t>1 leg losses as at 17/03/2026</t>
+  </si>
+  <si>
+    <t>Strikes for 2026 Season at 17/03/2026</t>
   </si>
 </sst>
 </file>
@@ -1414,9 +1423,6 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1435,16 +1441,25 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1462,19 +1477,13 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1493,6 +1502,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4191,7 +4204,7 @@
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
-    <col min="3" max="3" width="20.44140625" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="41.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4202,7 +4215,7 @@
       <c r="B1" t="s">
         <v>123</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>124</v>
       </c>
       <c r="D1" t="s">
@@ -4211,13 +4224,13 @@
       <c r="E1" t="s">
         <v>92</v>
       </c>
-      <c r="F1" t="str">
+      <c r="F1">
         <f t="shared" ref="F1:F13" si="0">IF(COUNTIF(A:A, E1)=0, "", SUMIF(A:A, E1, C:C))</f>
-        <v/>
+        <v>53.75</v>
       </c>
       <c r="G1">
         <f>COUNTIF(A1:A81, E1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -4227,11 +4240,11 @@
       <c r="B2" s="60">
         <v>10</v>
       </c>
-      <c r="C2" s="59">
+      <c r="C2" s="1">
         <v>358</v>
       </c>
       <c r="D2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -4252,36 +4265,36 @@
       <c r="B3" s="60">
         <v>10</v>
       </c>
-      <c r="C3" s="59">
+      <c r="C3" s="1">
         <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E3" t="s">
         <v>94</v>
       </c>
       <c r="F3">
         <f t="shared" si="0"/>
-        <v>95</v>
+        <v>226.25</v>
       </c>
       <c r="G3">
         <f>COUNTIF(A1:A81, E3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B4" s="60">
         <v>10</v>
       </c>
-      <c r="C4" s="59">
+      <c r="C4" s="1">
         <v>61.8</v>
       </c>
       <c r="D4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E4" t="s">
         <v>95</v>
@@ -4302,11 +4315,11 @@
       <c r="B5" s="59">
         <v>10</v>
       </c>
-      <c r="C5" s="59">
+      <c r="C5" s="1">
         <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E5" t="s">
         <v>93</v>
@@ -4327,11 +4340,11 @@
       <c r="B6" s="59">
         <v>10</v>
       </c>
-      <c r="C6" s="59">
+      <c r="C6" s="1">
         <v>97.5</v>
       </c>
       <c r="D6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E6" t="s">
         <v>97</v>
@@ -4346,8 +4359,18 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="60"/>
-      <c r="C7" s="60"/>
+      <c r="A7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="60">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>88.75</v>
+      </c>
+      <c r="D7" t="s">
+        <v>189</v>
+      </c>
       <c r="E7" t="s">
         <v>98</v>
       </c>
@@ -4361,23 +4384,43 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
+      <c r="A8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="60">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>53.75</v>
+      </c>
+      <c r="D8" t="s">
+        <v>190</v>
+      </c>
       <c r="E8" t="s">
         <v>89</v>
       </c>
       <c r="F8">
         <f t="shared" si="0"/>
-        <v>97.5</v>
+        <v>186.25</v>
       </c>
       <c r="G8">
         <f>COUNTIF(A2:A87, E8)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
+      <c r="A9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="60">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1">
+        <v>131.25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>191</v>
+      </c>
       <c r="E9" t="s">
         <v>96</v>
       </c>
@@ -4392,7 +4435,6 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
       <c r="E10" t="s">
         <v>120</v>
       </c>
@@ -4407,7 +4449,6 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B11" s="60"/>
-      <c r="C11" s="60"/>
       <c r="E11" t="s">
         <v>121</v>
       </c>
@@ -4422,7 +4463,6 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B12" s="60"/>
-      <c r="C12" s="59"/>
       <c r="E12" t="s">
         <v>9</v>
       </c>
@@ -4437,9 +4477,8 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B13" s="60"/>
-      <c r="C13" s="59"/>
       <c r="E13" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F13">
         <f t="shared" si="0"/>
@@ -4452,164 +4491,110 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B14" s="59"/>
-      <c r="C14" s="59"/>
       <c r="F14" s="61">
         <f>SUM(F1:F13)</f>
-        <v>707.3</v>
+        <v>981.05</v>
       </c>
       <c r="G14">
         <f>SUM(G1:G13)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" s="60"/>
-      <c r="C17" s="59"/>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" s="60"/>
-      <c r="C18" s="59"/>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" s="60"/>
-      <c r="C21" s="60"/>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" s="60"/>
-      <c r="C22" s="59"/>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" s="60"/>
-      <c r="C23" s="59"/>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C24" s="59"/>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" s="60"/>
-      <c r="C25" s="59"/>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" s="60"/>
-      <c r="C26" s="60"/>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C27" s="59"/>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" s="60"/>
-      <c r="C28" s="60"/>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C29" s="59"/>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" s="60"/>
-      <c r="C30" s="59"/>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B31" s="60"/>
-      <c r="C31" s="60"/>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B32" s="60"/>
-      <c r="C32" s="60"/>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" s="60"/>
-      <c r="C33" s="59"/>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B34" s="60"/>
-      <c r="C34" s="59"/>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B35" s="60"/>
-      <c r="C35" s="59"/>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B36" s="60"/>
-      <c r="C36" s="59"/>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C37" s="59"/>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B38" s="60"/>
-      <c r="C38" s="60"/>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C39" s="60"/>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B40" s="59"/>
-      <c r="C40" s="59"/>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B41" s="60"/>
-      <c r="C41" s="59"/>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B42" s="60"/>
-      <c r="C42" s="59"/>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B43" s="60"/>
-      <c r="C43" s="60"/>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B44" s="60"/>
-      <c r="C44" s="59"/>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B45" s="59"/>
-      <c r="C45" s="60"/>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C46" s="59"/>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="C47" s="59"/>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B48" s="60"/>
-      <c r="C48" s="59"/>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B49" s="59"/>
-      <c r="C49" s="59"/>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B50" s="60"/>
-      <c r="C50" s="60"/>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B51" s="60"/>
-      <c r="C51" s="59"/>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B52" s="60"/>
-      <c r="C52" s="59"/>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B53" s="60"/>
-      <c r="C53" s="59"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4634,50 +4619,50 @@
   <sheetData>
     <row r="1" spans="2:27" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:27" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67" t="s">
+      <c r="D2" s="73"/>
+      <c r="E2" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67" t="s">
+      <c r="F2" s="73"/>
+      <c r="G2" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67" t="s">
+      <c r="H2" s="73"/>
+      <c r="I2" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67" t="s">
+      <c r="J2" s="73"/>
+      <c r="K2" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67" t="s">
+      <c r="L2" s="73"/>
+      <c r="M2" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67" t="s">
+      <c r="N2" s="73"/>
+      <c r="O2" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67" t="s">
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67" t="s">
+      <c r="T2" s="73"/>
+      <c r="U2" s="73" t="s">
         <v>27</v>
       </c>
       <c r="V2" s="74"/>
-      <c r="W2" s="73" t="s">
+      <c r="W2" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="X2" s="67"/>
+      <c r="X2" s="73"/>
     </row>
     <row r="3" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="32" t="s">
@@ -6238,34 +6223,34 @@
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="F29" s="70" t="s">
+      <c r="F29" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="71"/>
-      <c r="H29" s="72"/>
-      <c r="I29" s="68">
+      <c r="G29" s="70"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="67">
         <f>C27+E27+G27+I27+K27+M27+O27+Q27+S27+U27</f>
         <v>2469.42</v>
       </c>
-      <c r="J29" s="69"/>
+      <c r="J29" s="68"/>
     </row>
     <row r="30" spans="2:27" x14ac:dyDescent="0.3">
       <c r="G30" s="75" t="s">
         <v>57</v>
       </c>
       <c r="H30" s="75"/>
-      <c r="I30" s="68">
+      <c r="I30" s="67">
         <f>+D27+F27+H27+J27+L27+N27+P27+R27+T27+V27</f>
         <v>1774.69</v>
       </c>
-      <c r="J30" s="69"/>
+      <c r="J30" s="68"/>
     </row>
     <row r="31" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="I31" s="68">
+      <c r="I31" s="67">
         <f>I30-I29</f>
         <v>-694.73</v>
       </c>
-      <c r="J31" s="69"/>
+      <c r="J31" s="68"/>
     </row>
     <row r="32" spans="2:27" x14ac:dyDescent="0.3">
       <c r="C32" s="1">
@@ -6314,11 +6299,11 @@
       </c>
     </row>
     <row r="34" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="I34" s="69">
+      <c r="I34" s="68">
         <f>I33+I31</f>
         <v>505.27</v>
       </c>
-      <c r="J34" s="69"/>
+      <c r="J34" s="68"/>
     </row>
     <row r="38" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C38" s="1">
@@ -6362,6 +6347,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
     <mergeCell ref="I30:J30"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="I31:J31"/>
@@ -6374,11 +6364,6 @@
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="I29:J29"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6406,50 +6391,50 @@
   <sheetData>
     <row r="1" spans="2:27" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:27" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67" t="s">
+      <c r="D2" s="73"/>
+      <c r="E2" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="77" t="s">
+      <c r="F2" s="73"/>
+      <c r="G2" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="73"/>
-      <c r="I2" s="67" t="s">
+      <c r="H2" s="72"/>
+      <c r="I2" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67" t="s">
+      <c r="J2" s="73"/>
+      <c r="K2" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67" t="s">
+      <c r="L2" s="73"/>
+      <c r="M2" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="73"/>
+      <c r="O2" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67" t="s">
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67" t="s">
+      <c r="R2" s="73"/>
+      <c r="S2" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67" t="s">
+      <c r="T2" s="73"/>
+      <c r="U2" s="73" t="s">
         <v>27</v>
       </c>
       <c r="V2" s="74"/>
-      <c r="W2" s="73" t="s">
+      <c r="W2" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="X2" s="67"/>
+      <c r="X2" s="73"/>
     </row>
     <row r="3" spans="2:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="32" t="s">
@@ -7809,34 +7794,34 @@
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="F29" s="70" t="s">
+      <c r="F29" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="71"/>
-      <c r="H29" s="72"/>
-      <c r="I29" s="68">
+      <c r="G29" s="70"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="67">
         <f>C27+E27+G27+I27+K27+M27+O27+Q27+S27+U27</f>
         <v>1788.24</v>
       </c>
-      <c r="J29" s="69"/>
+      <c r="J29" s="68"/>
     </row>
     <row r="30" spans="2:27" x14ac:dyDescent="0.3">
       <c r="G30" s="75" t="s">
         <v>57</v>
       </c>
       <c r="H30" s="75"/>
-      <c r="I30" s="68">
+      <c r="I30" s="67">
         <f>+D27+F27+H27+J27+L27+N27+P27+R27+T27+V27</f>
         <v>2492.1999999999998</v>
       </c>
-      <c r="J30" s="69"/>
+      <c r="J30" s="68"/>
     </row>
     <row r="31" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="I31" s="68">
+      <c r="I31" s="67">
         <f>I30-I29</f>
         <v>703.95999999999981</v>
       </c>
-      <c r="J31" s="69"/>
+      <c r="J31" s="68"/>
     </row>
     <row r="32" spans="2:27" x14ac:dyDescent="0.3">
       <c r="C32" s="36">
@@ -7890,11 +7875,11 @@
         <v>64</v>
       </c>
       <c r="H34" s="42"/>
-      <c r="I34" s="76">
+      <c r="I34" s="77">
         <f>I33+I31</f>
         <v>1303.9599999999998</v>
       </c>
-      <c r="J34" s="76"/>
+      <c r="J34" s="77"/>
       <c r="M34" s="33"/>
     </row>
     <row r="38" spans="3:16" x14ac:dyDescent="0.3">
@@ -7939,11 +7924,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="O2:P2"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="U2:V2"/>
@@ -7951,11 +7936,11 @@
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="M2:N2"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7984,54 +7969,54 @@
   <sheetData>
     <row r="1" spans="2:34" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:34" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67" t="s">
+      <c r="D2" s="73"/>
+      <c r="E2" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67" t="s">
+      <c r="F2" s="73"/>
+      <c r="G2" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67" t="s">
+      <c r="H2" s="73"/>
+      <c r="I2" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67" t="s">
+      <c r="J2" s="73"/>
+      <c r="K2" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67" t="s">
+      <c r="L2" s="73"/>
+      <c r="M2" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67" t="s">
+      <c r="N2" s="73"/>
+      <c r="O2" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67" t="s">
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67" t="s">
+      <c r="T2" s="73"/>
+      <c r="U2" s="73" t="s">
         <v>65</v>
       </c>
       <c r="V2" s="74"/>
-      <c r="W2" s="67" t="s">
+      <c r="W2" s="73" t="s">
         <v>66</v>
       </c>
       <c r="X2" s="74"/>
-      <c r="Y2" s="73" t="s">
+      <c r="Y2" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="Z2" s="67"/>
+      <c r="Z2" s="73"/>
     </row>
     <row r="3" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="32" t="s">
@@ -10085,34 +10070,34 @@
       </c>
     </row>
     <row r="31" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="F31" s="70" t="s">
+      <c r="F31" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="71"/>
-      <c r="H31" s="72"/>
-      <c r="I31" s="68">
+      <c r="G31" s="70"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="67">
         <f>C29+E29+G29+I29+K29+M29+O29+Q29+S29+U29+W29</f>
         <v>2521.33</v>
       </c>
-      <c r="J31" s="69"/>
+      <c r="J31" s="68"/>
     </row>
     <row r="32" spans="2:30" x14ac:dyDescent="0.3">
       <c r="G32" s="75" t="s">
         <v>57</v>
       </c>
       <c r="H32" s="75"/>
-      <c r="I32" s="68">
+      <c r="I32" s="67">
         <f>+D29+F29+H29+J29+L29+N29+P29+R29+T29+V29+X29</f>
         <v>2997.5899999999997</v>
       </c>
-      <c r="J32" s="69"/>
+      <c r="J32" s="68"/>
     </row>
     <row r="33" spans="3:17" x14ac:dyDescent="0.3">
-      <c r="I33" s="68">
+      <c r="I33" s="67">
         <f>I32-I31</f>
         <v>476.25999999999976</v>
       </c>
-      <c r="J33" s="69"/>
+      <c r="J33" s="68"/>
     </row>
     <row r="34" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C34" s="36">
@@ -10165,11 +10150,11 @@
         <v>64</v>
       </c>
       <c r="H36" s="42"/>
-      <c r="I36" s="76">
+      <c r="I36" s="77">
         <f>I35+I33</f>
         <v>2476.2599999999998</v>
       </c>
-      <c r="J36" s="76"/>
+      <c r="J36" s="77"/>
       <c r="M36" s="33"/>
     </row>
     <row r="40" spans="3:17" x14ac:dyDescent="0.3">
@@ -10214,11 +10199,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="O2:P2"/>
     <mergeCell ref="Q2:R2"/>
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="U2:V2"/>
@@ -10227,11 +10212,11 @@
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="W2:X2"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="51" orientation="landscape" r:id="rId1"/>
@@ -10260,54 +10245,54 @@
   <sheetData>
     <row r="1" spans="2:34" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:34" ht="18" x14ac:dyDescent="0.35">
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="67"/>
-      <c r="E2" s="77" t="s">
+      <c r="D2" s="73"/>
+      <c r="E2" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="73"/>
-      <c r="G2" s="67" t="s">
+      <c r="F2" s="72"/>
+      <c r="G2" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67" t="s">
+      <c r="H2" s="73"/>
+      <c r="I2" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67" t="s">
+      <c r="J2" s="73"/>
+      <c r="K2" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="67"/>
-      <c r="M2" s="77" t="s">
+      <c r="L2" s="73"/>
+      <c r="M2" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="73"/>
-      <c r="O2" s="67" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67" t="s">
+      <c r="N2" s="72"/>
+      <c r="O2" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67" t="s">
+      <c r="R2" s="73"/>
+      <c r="S2" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67" t="s">
+      <c r="T2" s="73"/>
+      <c r="U2" s="73" t="s">
         <v>65</v>
       </c>
       <c r="V2" s="74"/>
-      <c r="W2" s="67" t="s">
+      <c r="W2" s="73" t="s">
         <v>66</v>
       </c>
       <c r="X2" s="74"/>
-      <c r="Y2" s="73" t="s">
+      <c r="Y2" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="Z2" s="67"/>
+      <c r="Z2" s="73"/>
     </row>
     <row r="3" spans="2:34" x14ac:dyDescent="0.3">
       <c r="B3" s="32" t="s">
@@ -12316,34 +12301,34 @@
       </c>
     </row>
     <row r="31" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="F31" s="70" t="s">
+      <c r="F31" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="71"/>
-      <c r="H31" s="72"/>
-      <c r="I31" s="68">
+      <c r="G31" s="70"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="67">
         <f>C29+E29+G29+I29+K29+M29+O29+Q29+S29+U29+W29</f>
         <v>2462.73</v>
       </c>
-      <c r="J31" s="69"/>
+      <c r="J31" s="68"/>
     </row>
     <row r="32" spans="2:30" x14ac:dyDescent="0.3">
       <c r="G32" s="75" t="s">
         <v>57</v>
       </c>
       <c r="H32" s="75"/>
-      <c r="I32" s="68">
+      <c r="I32" s="67">
         <f>+D29+F29+H29+J29+L29+N29+P29+R29+T29+V29+X29</f>
         <v>1004.25</v>
       </c>
-      <c r="J32" s="69"/>
+      <c r="J32" s="68"/>
     </row>
     <row r="33" spans="3:25" x14ac:dyDescent="0.3">
-      <c r="I33" s="68">
+      <c r="I33" s="67">
         <f>I32-I31</f>
         <v>-1458.48</v>
       </c>
-      <c r="J33" s="69"/>
+      <c r="J33" s="68"/>
       <c r="Y33">
         <f>2167+183+5*10</f>
         <v>2400</v>
@@ -12439,11 +12424,11 @@
         <v>64</v>
       </c>
       <c r="H38" s="42"/>
-      <c r="I38" s="76">
+      <c r="I38" s="77">
         <f>I36+I33+J37</f>
         <v>322.7800000000002</v>
       </c>
-      <c r="J38" s="76"/>
+      <c r="J38" s="77"/>
       <c r="M38" s="33"/>
     </row>
     <row r="40" spans="3:25" x14ac:dyDescent="0.3">
@@ -12715,16 +12700,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
     <mergeCell ref="W2:X2"/>
     <mergeCell ref="Y2:Z2"/>
     <mergeCell ref="C2:D2"/>
@@ -12733,6 +12708,16 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="M2:N2"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="51" orientation="landscape" r:id="rId1"/>
@@ -12765,54 +12750,54 @@
   <sheetData>
     <row r="1" spans="2:34" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:34" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="73" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="67"/>
-      <c r="E2" s="77" t="s">
+      <c r="D2" s="73"/>
+      <c r="E2" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="73"/>
-      <c r="G2" s="67" t="s">
+      <c r="F2" s="72"/>
+      <c r="G2" s="73" t="s">
         <v>102</v>
       </c>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67" t="s">
+      <c r="H2" s="73"/>
+      <c r="I2" s="73" t="s">
         <v>103</v>
       </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67" t="s">
+      <c r="J2" s="73"/>
+      <c r="K2" s="73" t="s">
         <v>104</v>
       </c>
-      <c r="L2" s="67"/>
-      <c r="M2" s="77" t="s">
+      <c r="L2" s="73"/>
+      <c r="M2" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="N2" s="73"/>
-      <c r="O2" s="67" t="s">
+      <c r="N2" s="72"/>
+      <c r="O2" s="73" t="s">
         <v>106</v>
       </c>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67" t="s">
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73" t="s">
         <v>107</v>
       </c>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67" t="s">
+      <c r="R2" s="73"/>
+      <c r="S2" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67" t="s">
+      <c r="T2" s="73"/>
+      <c r="U2" s="73" t="s">
         <v>108</v>
       </c>
       <c r="V2" s="74"/>
-      <c r="W2" s="67" t="s">
+      <c r="W2" s="73" t="s">
         <v>66</v>
       </c>
       <c r="X2" s="74"/>
-      <c r="Y2" s="73" t="s">
+      <c r="Y2" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="Z2" s="67"/>
+      <c r="Z2" s="73"/>
     </row>
     <row r="3" spans="2:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="32" t="s">
@@ -14795,34 +14780,34 @@
       </c>
     </row>
     <row r="31" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="F31" s="70" t="s">
+      <c r="F31" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="71"/>
-      <c r="H31" s="72"/>
-      <c r="I31" s="68">
+      <c r="G31" s="70"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="67">
         <f>C29+E29+G29+I29+K29+M29+O29+Q29+S29+U29+W29</f>
         <v>2158</v>
       </c>
-      <c r="J31" s="69"/>
+      <c r="J31" s="68"/>
     </row>
     <row r="32" spans="2:30" x14ac:dyDescent="0.3">
       <c r="G32" s="75" t="s">
         <v>57</v>
       </c>
       <c r="H32" s="75"/>
-      <c r="I32" s="68">
+      <c r="I32" s="67">
         <f>+D29+F29+H29+J29+L29+N29+P29+R29+T29+V29+X29</f>
         <v>709.26</v>
       </c>
-      <c r="J32" s="69"/>
+      <c r="J32" s="68"/>
     </row>
     <row r="33" spans="3:25" x14ac:dyDescent="0.3">
-      <c r="I33" s="68">
+      <c r="I33" s="67">
         <f>I32-I31</f>
         <v>-1448.74</v>
       </c>
-      <c r="J33" s="69"/>
+      <c r="J33" s="68"/>
       <c r="Y33">
         <f>2167+183+5*10</f>
         <v>2400</v>
@@ -14911,11 +14896,11 @@
         <v>64</v>
       </c>
       <c r="H38" s="42"/>
-      <c r="I38" s="76">
+      <c r="I38" s="77">
         <f>I36+I33</f>
         <v>552.84999999999991</v>
       </c>
-      <c r="J38" s="76"/>
+      <c r="J38" s="77"/>
       <c r="M38" s="33"/>
     </row>
     <row r="40" spans="3:25" x14ac:dyDescent="0.3">
@@ -15217,16 +15202,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
     <mergeCell ref="W2:X2"/>
     <mergeCell ref="Y2:Z2"/>
     <mergeCell ref="C2:D2"/>
@@ -15235,6 +15210,16 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="M2:N2"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="51" orientation="landscape" r:id="rId1"/>
@@ -15270,66 +15255,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:38" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="W1" s="78"/>
-      <c r="X1" s="79"/>
+      <c r="W1" s="80"/>
+      <c r="X1" s="81"/>
     </row>
     <row r="2" spans="2:38" ht="18" x14ac:dyDescent="0.35">
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="73" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="67"/>
-      <c r="E2" s="77" t="s">
+      <c r="D2" s="73"/>
+      <c r="E2" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="73"/>
-      <c r="G2" s="67" t="s">
+      <c r="F2" s="72"/>
+      <c r="G2" s="73" t="s">
         <v>114</v>
       </c>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67" t="s">
+      <c r="H2" s="73"/>
+      <c r="I2" s="73" t="s">
         <v>115</v>
       </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67" t="s">
+      <c r="J2" s="73"/>
+      <c r="K2" s="73" t="s">
         <v>104</v>
       </c>
-      <c r="L2" s="67"/>
-      <c r="M2" s="77" t="s">
+      <c r="L2" s="73"/>
+      <c r="M2" s="76" t="s">
         <v>103</v>
       </c>
-      <c r="N2" s="73"/>
-      <c r="O2" s="67" t="s">
+      <c r="N2" s="72"/>
+      <c r="O2" s="73" t="s">
         <v>106</v>
       </c>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67" t="s">
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73" t="s">
         <v>107</v>
       </c>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67" t="s">
+      <c r="R2" s="73"/>
+      <c r="S2" s="73" t="s">
         <v>100</v>
       </c>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67" t="s">
+      <c r="T2" s="73"/>
+      <c r="U2" s="73" t="s">
         <v>108</v>
       </c>
-      <c r="V2" s="77"/>
-      <c r="W2" s="80" t="s">
+      <c r="V2" s="76"/>
+      <c r="W2" s="82" t="s">
         <v>102</v>
       </c>
-      <c r="X2" s="81"/>
-      <c r="Y2" s="80" t="s">
+      <c r="X2" s="83"/>
+      <c r="Y2" s="82" t="s">
         <v>105</v>
       </c>
-      <c r="Z2" s="82"/>
-      <c r="AA2" s="83" t="s">
+      <c r="Z2" s="84"/>
+      <c r="AA2" s="78" t="s">
         <v>66</v>
       </c>
-      <c r="AB2" s="84"/>
-      <c r="AC2" s="73" t="s">
+      <c r="AB2" s="79"/>
+      <c r="AC2" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="AD2" s="67"/>
+      <c r="AD2" s="73"/>
     </row>
     <row r="3" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B3" s="32" t="s">
@@ -17663,34 +17648,34 @@
       </c>
     </row>
     <row r="32" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="F32" s="70" t="s">
+      <c r="F32" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="G32" s="71"/>
-      <c r="H32" s="72"/>
-      <c r="I32" s="68">
+      <c r="G32" s="70"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="67">
         <f>C30+E30+G30+I30+K30+M30+O30+Q30+S30+U30+AA30+W30+Y30</f>
         <v>2648</v>
       </c>
-      <c r="J32" s="69"/>
+      <c r="J32" s="68"/>
     </row>
     <row r="33" spans="3:25" x14ac:dyDescent="0.3">
       <c r="G33" s="75" t="s">
         <v>57</v>
       </c>
       <c r="H33" s="75"/>
-      <c r="I33" s="68">
+      <c r="I33" s="67">
         <f>+D30+F30+H30+J30+L30+N30+P30+R30+T30+V30+AB30+X30+Z30</f>
         <v>1694.2299999999998</v>
       </c>
-      <c r="J33" s="69"/>
+      <c r="J33" s="68"/>
     </row>
     <row r="34" spans="3:25" x14ac:dyDescent="0.3">
-      <c r="I34" s="68">
+      <c r="I34" s="67">
         <f>I33-I32</f>
         <v>-953.77000000000021</v>
       </c>
-      <c r="J34" s="69"/>
+      <c r="J34" s="68"/>
       <c r="Y34">
         <f>2167+183+5*10</f>
         <v>2400</v>
@@ -17773,11 +17758,11 @@
         <v>64</v>
       </c>
       <c r="H39" s="42"/>
-      <c r="I39" s="76">
+      <c r="I39" s="77">
         <f>I37+I34</f>
         <v>1446.28</v>
       </c>
-      <c r="J39" s="76"/>
+      <c r="J39" s="77"/>
       <c r="M39" s="33"/>
     </row>
     <row r="41" spans="3:25" x14ac:dyDescent="0.3">
@@ -18127,6 +18112,19 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="O2:P2"/>
     <mergeCell ref="AA2:AB2"/>
     <mergeCell ref="AC2:AD2"/>
     <mergeCell ref="C2:D2"/>
@@ -18135,19 +18133,6 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="M2:N2"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="63" orientation="landscape" r:id="rId1"/>
@@ -19064,70 +19049,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:38" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="W1" s="78"/>
-      <c r="X1" s="79"/>
+      <c r="W1" s="80"/>
+      <c r="X1" s="81"/>
     </row>
     <row r="2" spans="2:38" ht="18" x14ac:dyDescent="0.35">
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="73" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="67"/>
-      <c r="E2" s="77" t="s">
+      <c r="D2" s="73"/>
+      <c r="E2" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="73"/>
-      <c r="G2" s="67" t="s">
+      <c r="F2" s="72"/>
+      <c r="G2" s="73" t="s">
         <v>114</v>
       </c>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67" t="s">
+      <c r="H2" s="73"/>
+      <c r="I2" s="73" t="s">
         <v>115</v>
       </c>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67" t="s">
+      <c r="J2" s="73"/>
+      <c r="K2" s="73" t="s">
         <v>104</v>
       </c>
-      <c r="L2" s="67"/>
-      <c r="M2" s="77" t="s">
+      <c r="L2" s="73"/>
+      <c r="M2" s="76" t="s">
         <v>103</v>
       </c>
-      <c r="N2" s="73"/>
-      <c r="O2" s="67" t="s">
+      <c r="N2" s="72"/>
+      <c r="O2" s="73" t="s">
         <v>106</v>
       </c>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67" t="s">
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73" t="s">
         <v>107</v>
       </c>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67" t="s">
+      <c r="R2" s="73"/>
+      <c r="S2" s="73" t="s">
         <v>100</v>
       </c>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67" t="s">
+      <c r="T2" s="73"/>
+      <c r="U2" s="73" t="s">
         <v>108</v>
       </c>
-      <c r="V2" s="77"/>
-      <c r="W2" s="80" t="s">
+      <c r="V2" s="76"/>
+      <c r="W2" s="82" t="s">
         <v>102</v>
       </c>
-      <c r="X2" s="81"/>
-      <c r="Y2" s="80" t="s">
+      <c r="X2" s="83"/>
+      <c r="Y2" s="82" t="s">
         <v>105</v>
       </c>
-      <c r="Z2" s="81"/>
-      <c r="AA2" s="85" t="s">
+      <c r="Z2" s="83"/>
+      <c r="AA2" s="86" t="s">
         <v>180</v>
       </c>
-      <c r="AB2" s="86"/>
-      <c r="AC2" s="83" t="s">
+      <c r="AB2" s="87"/>
+      <c r="AC2" s="78" t="s">
         <v>66</v>
       </c>
-      <c r="AD2" s="84"/>
-      <c r="AE2" s="73" t="s">
+      <c r="AD2" s="79"/>
+      <c r="AE2" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="AF2" s="67"/>
+      <c r="AF2" s="73"/>
     </row>
     <row r="3" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B3" s="32" t="s">
@@ -19348,47 +19333,63 @@
       <c r="L5" s="16"/>
       <c r="M5" s="17"/>
       <c r="N5" s="16"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="16"/>
+      <c r="O5" s="17">
+        <v>25</v>
+      </c>
+      <c r="P5" s="16">
+        <v>280</v>
+      </c>
       <c r="Q5" s="17"/>
       <c r="R5" s="16"/>
-      <c r="S5" s="17"/>
-      <c r="T5" s="16"/>
-      <c r="U5" s="15"/>
-      <c r="V5" s="20"/>
-      <c r="W5" s="15"/>
-      <c r="X5" s="20"/>
+      <c r="S5" s="17">
+        <v>25</v>
+      </c>
+      <c r="T5" s="16">
+        <v>0</v>
+      </c>
+      <c r="U5" s="15">
+        <v>25</v>
+      </c>
+      <c r="V5" s="20">
+        <v>0</v>
+      </c>
+      <c r="W5" s="15">
+        <v>25</v>
+      </c>
+      <c r="X5" s="20">
+        <v>17</v>
+      </c>
       <c r="Y5" s="15"/>
       <c r="Z5" s="20"/>
       <c r="AA5" s="15"/>
       <c r="AB5" s="20"/>
       <c r="AC5" s="17">
         <f>U5+S5+Q5+O5+M5+K5+I5+G5+E5+C5+W5+Y5</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD5" s="35">
         <f>V5+T5+R5+P5+N5+L5+J5+H5+F5+D5+X5+Z5</f>
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="AE5" s="1">
         <f>AE4+AC5</f>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF5" s="1">
         <f>AF4+AD5</f>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG5" s="1">
         <f t="shared" ref="AG5:AG29" si="1">AF5-AE5</f>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH5" s="1"/>
-      <c r="AI5" s="87" t="s">
+      <c r="AI5" s="85" t="s">
         <v>181</v>
       </c>
-      <c r="AJ5" s="87"/>
-      <c r="AK5" s="87"/>
-      <c r="AL5" s="87"/>
+      <c r="AJ5" s="85"/>
+      <c r="AK5" s="85"/>
+      <c r="AL5" s="85"/>
     </row>
     <row r="6" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B6" s="52" t="s">
@@ -19430,15 +19431,15 @@
       </c>
       <c r="AE6" s="1">
         <f t="shared" ref="AE6:AF21" si="3">AE5+AC6</f>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF6" s="1">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG6" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH6" s="1"/>
       <c r="AI6" s="43" t="s">
@@ -19494,15 +19495,15 @@
       </c>
       <c r="AE7" s="1">
         <f t="shared" si="3"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF7" s="1">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG7" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH7" s="44" t="s">
         <v>71</v>
@@ -19564,15 +19565,15 @@
       </c>
       <c r="AE8" s="1">
         <f t="shared" si="3"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF8" s="1">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG8" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH8" s="44" t="s">
         <v>72</v>
@@ -19634,15 +19635,15 @@
       </c>
       <c r="AE9" s="1">
         <f t="shared" si="3"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF9" s="1">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG9" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH9" s="44" t="s">
         <v>73</v>
@@ -19704,22 +19705,22 @@
       </c>
       <c r="AE10" s="1">
         <f t="shared" si="3"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF10" s="1">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG10" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH10" s="44" t="s">
         <v>74</v>
       </c>
       <c r="AI10" s="44">
         <f>+S30+'Punters 2024'!AE10</f>
-        <v>1379.9</v>
+        <v>1404.9</v>
       </c>
       <c r="AJ10" s="44">
         <f>+T30+'Punters 2024'!AF10</f>
@@ -19727,11 +19728,11 @@
       </c>
       <c r="AK10" s="50">
         <f t="shared" si="4"/>
-        <v>136.54999999999973</v>
+        <v>111.54999999999973</v>
       </c>
       <c r="AL10" s="45">
         <f t="shared" si="5"/>
-        <v>9.8956446119283809E-2</v>
+        <v>7.9400669086767545E-2</v>
       </c>
     </row>
     <row r="11" spans="2:38" x14ac:dyDescent="0.3">
@@ -19774,15 +19775,15 @@
       </c>
       <c r="AE11" s="1">
         <f t="shared" si="3"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF11" s="1">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG11" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH11" s="44" t="s">
         <v>75</v>
@@ -19844,22 +19845,22 @@
       </c>
       <c r="AE12" s="1">
         <f t="shared" si="3"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF12" s="1">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG12" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH12" s="44" t="s">
         <v>76</v>
       </c>
       <c r="AI12" s="44">
         <f>+U30+'Punters 2024'!AE12</f>
-        <v>1394.96</v>
+        <v>1419.96</v>
       </c>
       <c r="AJ12" s="44">
         <f>+V30+'Punters 2024'!AF12</f>
@@ -19867,11 +19868,11 @@
       </c>
       <c r="AK12" s="49">
         <f t="shared" si="4"/>
-        <v>-504.30000000000018</v>
+        <v>-529.30000000000018</v>
       </c>
       <c r="AL12" s="47">
         <f t="shared" si="5"/>
-        <v>-0.36151574238687861</v>
+        <v>-0.37275697906983307</v>
       </c>
     </row>
     <row r="13" spans="2:38" x14ac:dyDescent="0.3">
@@ -19914,15 +19915,15 @@
       </c>
       <c r="AE13" s="1">
         <f t="shared" si="3"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF13" s="1">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG13" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH13" s="44" t="s">
         <v>77</v>
@@ -19984,15 +19985,15 @@
       </c>
       <c r="AE14" s="1">
         <f t="shared" si="3"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF14" s="1">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG14" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH14" s="44" t="s">
         <v>78</v>
@@ -20054,34 +20055,34 @@
       </c>
       <c r="AE15" s="1">
         <f t="shared" si="3"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF15" s="1">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG15" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH15" s="44" t="s">
         <v>79</v>
       </c>
       <c r="AI15" s="44">
         <f>+O30+'Punters 2024'!AE15</f>
-        <v>1377.7</v>
+        <v>1402.7</v>
       </c>
       <c r="AJ15" s="44">
         <f>+P30+'Punters 2024'!AF15</f>
-        <v>1696.09</v>
+        <v>1976.09</v>
       </c>
       <c r="AK15" s="50">
         <f t="shared" si="4"/>
-        <v>318.38999999999987</v>
+        <v>573.38999999999987</v>
       </c>
       <c r="AL15" s="45">
         <f t="shared" si="5"/>
-        <v>0.23110256224141676</v>
+        <v>0.40877593213089031</v>
       </c>
     </row>
     <row r="16" spans="2:38" x14ac:dyDescent="0.3">
@@ -20124,34 +20125,34 @@
       </c>
       <c r="AE16" s="1">
         <f t="shared" si="3"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF16" s="1">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG16" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH16" s="44" t="s">
         <v>80</v>
       </c>
       <c r="AI16" s="44">
         <f>+W30+'Punters 2024'!AE16</f>
-        <v>630</v>
+        <v>655</v>
       </c>
       <c r="AJ16" s="44">
         <f>+X30+'Punters 2024'!AF16</f>
-        <v>151.25</v>
+        <v>168.25</v>
       </c>
       <c r="AK16" s="49">
         <f t="shared" si="4"/>
-        <v>-478.75</v>
+        <v>-486.75</v>
       </c>
       <c r="AL16" s="47">
         <f t="shared" si="5"/>
-        <v>-0.75992063492063489</v>
+        <v>-0.74312977099236643</v>
       </c>
     </row>
     <row r="17" spans="2:38" x14ac:dyDescent="0.3">
@@ -20194,15 +20195,15 @@
       </c>
       <c r="AE17" s="1">
         <f t="shared" si="3"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF17" s="1">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG17" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH17" s="44" t="s">
         <v>116</v>
@@ -20264,15 +20265,15 @@
       </c>
       <c r="AE18" s="1">
         <f t="shared" si="3"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF18" s="1">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG18" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH18" s="64" t="s">
         <v>117</v>
@@ -20334,15 +20335,15 @@
       </c>
       <c r="AE19" s="1">
         <f t="shared" si="3"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF19" s="1">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG19" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH19" s="62" t="s">
         <v>182</v>
@@ -20392,15 +20393,15 @@
       </c>
       <c r="AE20" s="1">
         <f t="shared" si="3"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF20" s="1">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG20" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH20" s="1"/>
     </row>
@@ -20444,15 +20445,15 @@
       </c>
       <c r="AE21" s="1">
         <f t="shared" si="3"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF21" s="1">
         <f t="shared" si="3"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG21" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH21" s="1"/>
     </row>
@@ -20496,15 +20497,15 @@
       </c>
       <c r="AE22" s="1">
         <f t="shared" ref="AE22:AF29" si="6">AE21+AC22</f>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF22" s="1">
         <f t="shared" si="6"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG22" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH22" s="1"/>
     </row>
@@ -20548,15 +20549,15 @@
       </c>
       <c r="AE23" s="1">
         <f t="shared" si="6"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF23" s="1">
         <f t="shared" si="6"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG23" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH23" s="1"/>
     </row>
@@ -20600,15 +20601,15 @@
       </c>
       <c r="AE24" s="1">
         <f t="shared" si="6"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF24" s="1">
         <f t="shared" si="6"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG24" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH24" s="1"/>
     </row>
@@ -20652,15 +20653,15 @@
       </c>
       <c r="AE25" s="1">
         <f t="shared" si="6"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF25" s="1">
         <f t="shared" si="6"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG25" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH25" s="1"/>
     </row>
@@ -20704,15 +20705,15 @@
       </c>
       <c r="AE26" s="1">
         <f t="shared" si="6"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF26" s="1">
         <f t="shared" si="6"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG26" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH26" s="1"/>
     </row>
@@ -20756,15 +20757,15 @@
       </c>
       <c r="AE27" s="1">
         <f t="shared" si="6"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF27" s="1">
         <f t="shared" si="6"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG27" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH27" s="1"/>
     </row>
@@ -20808,15 +20809,15 @@
       </c>
       <c r="AE28" s="1">
         <f t="shared" si="6"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF28" s="1">
         <f t="shared" si="6"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG28" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH28" s="1"/>
     </row>
@@ -20860,15 +20861,15 @@
       </c>
       <c r="AE29" s="1">
         <f t="shared" si="6"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AF29" s="1">
         <f t="shared" si="6"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AG29" s="1">
         <f t="shared" si="1"/>
-        <v>-91</v>
+        <v>106</v>
       </c>
       <c r="AH29" s="1"/>
     </row>
@@ -20926,11 +20927,11 @@
       </c>
       <c r="O30" s="18">
         <f t="shared" si="8"/>
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="P30" s="18">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="Q30" s="18">
         <f t="shared" si="8"/>
@@ -20942,7 +20943,7 @@
       </c>
       <c r="S30" s="18">
         <f t="shared" si="8"/>
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="T30" s="18">
         <f>SUM(T4:T29)</f>
@@ -20950,7 +20951,7 @@
       </c>
       <c r="U30" s="18">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="V30" s="21">
         <f t="shared" si="8"/>
@@ -20958,11 +20959,11 @@
       </c>
       <c r="W30" s="18">
         <f t="shared" si="8"/>
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="X30" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y30" s="18">
         <f t="shared" si="8"/>
@@ -20982,11 +20983,11 @@
       </c>
       <c r="AC30" s="29">
         <f t="shared" si="8"/>
-        <v>155</v>
+        <v>255</v>
       </c>
       <c r="AD30" s="18">
         <f t="shared" si="8"/>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="AE30" s="1"/>
     </row>
@@ -21017,7 +21018,7 @@
       </c>
       <c r="P31" s="28">
         <f>(P30-O30)/O30</f>
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31" s="28">
         <f>(R30-Q30)/Q30</f>
@@ -21033,7 +21034,7 @@
       </c>
       <c r="X31" s="28">
         <f>(X30-W30)/W30</f>
-        <v>-1</v>
+        <v>-0.51428571428571423</v>
       </c>
       <c r="Z31" s="28">
         <f>(Z30-Y30)/Y30</f>
@@ -21045,34 +21046,34 @@
       </c>
     </row>
     <row r="32" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="F32" s="70" t="s">
+      <c r="F32" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="G32" s="71"/>
-      <c r="H32" s="72"/>
-      <c r="I32" s="68">
+      <c r="G32" s="70"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="67">
         <f>C30+E30+G30+I30+K30+M30+O30+Q30+S30+U30+AA30+W30+Y30</f>
-        <v>170</v>
-      </c>
-      <c r="J32" s="69"/>
+        <v>270</v>
+      </c>
+      <c r="J32" s="68"/>
     </row>
     <row r="33" spans="3:25" x14ac:dyDescent="0.3">
       <c r="G33" s="75" t="s">
         <v>57</v>
       </c>
       <c r="H33" s="75"/>
-      <c r="I33" s="68">
+      <c r="I33" s="67">
         <f>+D30+F30+H30+J30+L30+N30+P30+R30+T30+V30+AB30+X30+Z30</f>
-        <v>64</v>
-      </c>
-      <c r="J33" s="69"/>
+        <v>361</v>
+      </c>
+      <c r="J33" s="68"/>
     </row>
     <row r="34" spans="3:25" x14ac:dyDescent="0.3">
-      <c r="I34" s="68">
+      <c r="I34" s="67">
         <f>I33-I32</f>
-        <v>-106</v>
-      </c>
-      <c r="J34" s="69"/>
+        <v>91</v>
+      </c>
+      <c r="J34" s="68"/>
       <c r="Y34">
         <f>2167+183+5*10</f>
         <v>2400</v>
@@ -21093,27 +21094,27 @@
       </c>
       <c r="I35" s="38">
         <f>O30+K30+M30+Q30</f>
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="J35" s="38">
         <f>P30+L30+N30</f>
-        <v>64</v>
+        <v>344</v>
       </c>
       <c r="K35" s="39">
         <f>J35-I35</f>
-        <v>4</v>
+        <v>259</v>
       </c>
       <c r="O35" s="40">
         <f>U30+W30+Y30+S30</f>
-        <v>40</v>
+        <v>115</v>
       </c>
       <c r="P35" s="40">
         <f>V30+X30+T30+Z30</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q35" s="41">
         <f>P35-O35</f>
-        <v>-40</v>
+        <v>-98</v>
       </c>
       <c r="X35" s="55"/>
       <c r="Y35">
@@ -21131,13 +21132,13 @@
       <c r="I36" s="38"/>
       <c r="J36" s="34">
         <f>(J35-I35)/I35</f>
-        <v>6.6666666666666666E-2</v>
+        <v>3.0470588235294116</v>
       </c>
       <c r="K36" s="39"/>
       <c r="O36" s="40"/>
       <c r="P36" s="34">
         <f>(P35-O35)/O35</f>
-        <v>-1</v>
+        <v>-0.85217391304347823</v>
       </c>
       <c r="Q36" s="41"/>
       <c r="X36" s="55"/>
@@ -21147,7 +21148,7 @@
         <v>58</v>
       </c>
       <c r="I37">
-        <v>2400.0500000000002</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="39" spans="3:25" x14ac:dyDescent="0.3">
@@ -21155,11 +21156,11 @@
         <v>64</v>
       </c>
       <c r="H39" s="42"/>
-      <c r="I39" s="76">
+      <c r="I39" s="77">
         <f>I37+I34</f>
-        <v>2294.0500000000002</v>
-      </c>
-      <c r="J39" s="76"/>
+        <v>2886</v>
+      </c>
+      <c r="J39" s="77"/>
       <c r="M39" s="33"/>
     </row>
     <row r="41" spans="3:25" x14ac:dyDescent="0.3">
@@ -21176,15 +21177,15 @@
       </c>
       <c r="I43" s="1">
         <f>O30+K30+M30</f>
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="J43" s="1">
         <f>P30+L30+N30</f>
-        <v>64</v>
+        <v>344</v>
       </c>
       <c r="O43" s="1">
         <f>U30+Q30+S30</f>
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="P43" s="1">
         <f>V30+R30+T30</f>
@@ -21198,16 +21199,16 @@
       </c>
       <c r="J44" s="33">
         <f>J43-I43</f>
-        <v>19</v>
+        <v>274</v>
       </c>
       <c r="P44" s="33">
         <f>P43-O43</f>
-        <v>-40</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="46" spans="3:25" x14ac:dyDescent="0.3">
       <c r="V46" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47" spans="3:25" x14ac:dyDescent="0.3">
@@ -21215,14 +21216,14 @@
         <v>88</v>
       </c>
       <c r="J47" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="V47" t="s">
         <v>89</v>
       </c>
       <c r="W47">
         <f>SUM('1 Leg Losses 2026'!G8)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="3:25" x14ac:dyDescent="0.3">
@@ -21287,7 +21288,7 @@
       </c>
       <c r="W50">
         <f>SUM('1 Leg Losses 2026'!G1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="4:23" x14ac:dyDescent="0.3">
@@ -21406,7 +21407,7 @@
       </c>
       <c r="E56" s="1">
         <f>SUM(X30)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J56" t="s">
         <v>89</v>
@@ -21419,7 +21420,7 @@
       </c>
       <c r="W56">
         <f>SUM('1 Leg Losses 2026'!G3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="4:23" x14ac:dyDescent="0.3">
@@ -21459,7 +21460,7 @@
         <v>0</v>
       </c>
       <c r="V58" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="W58">
         <f>SUM('1 Leg Losses 2026'!G13)</f>
@@ -21494,7 +21495,7 @@
       </c>
       <c r="E60" s="1">
         <f>SUM(P30)</f>
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="J60" t="s">
         <v>9</v>
@@ -21507,18 +21508,18 @@
       </c>
       <c r="W60">
         <f>SUM(W47:W59)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="4:23" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
       </c>
       <c r="J61" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="K61">
         <v>0</v>
@@ -21530,7 +21531,7 @@
       </c>
       <c r="E62" s="1">
         <f>SUM(E49:E60)</f>
-        <v>64</v>
+        <v>361</v>
       </c>
       <c r="J62" t="s">
         <v>99</v>
@@ -21542,19 +21543,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="AI5:AL5"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="I34:J34"/>
@@ -21565,6 +21553,19 @@
     <mergeCell ref="Y2:Z2"/>
     <mergeCell ref="F32:H32"/>
     <mergeCell ref="I32:J32"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="AI5:AL5"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AE2:AF2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="63" orientation="landscape"/>
@@ -21572,23 +21573,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="3e1ffae5-f160-4019-9720-1b11bf1b81a3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002D8393059904904F9DB82DE4B9AFABF6" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f7bafc8adbaca2e93ffc3a1da3fd32d5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="3e1ffae5-f160-4019-9720-1b11bf1b81a3" xmlns:ns4="21753bd8-bffc-4cd2-a328-982ee854c895" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8f821f56a5d2247de677e71e73e5a99e" ns3:_="" ns4:_="">
     <xsd:import namespace="3e1ffae5-f160-4019-9720-1b11bf1b81a3"/>
@@ -21809,25 +21793,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4D7A62A-0CB5-48B0-A73A-0A91BCC8EAEF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3e1ffae5-f160-4019-9720-1b11bf1b81a3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{948817D4-7F3F-493D-9D4C-B473DA03CC7E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="3e1ffae5-f160-4019-9720-1b11bf1b81a3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22BA772B-ABF0-4278-9CEF-D9160BBA9E07}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21846,6 +21829,24 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{948817D4-7F3F-493D-9D4C-B473DA03CC7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4D7A62A-0CB5-48B0-A73A-0A91BCC8EAEF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3e1ffae5-f160-4019-9720-1b11bf1b81a3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0f7d30c2-cad0-4405-8153-25a6a3313da4}" enabled="1" method="Privileged" siteId="{6c637512-c417-4e78-9d62-b61258e4b619}" removed="0"/>
